--- a/docs/kredensial/username-password-awal-natcon2026.xlsx
+++ b/docs/kredensial/username-password-awal-natcon2026.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01 Booth'!$A$3:$F$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02 Peserta'!$A$3:$H$859</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02 Peserta'!$A$3:$H$869</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +521,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>36 akun booth/sponsor + 856 akun peserta. Semua diverifikasi satu per satu ke API: 892 dari 892 berhasil login.</t>
+          <t>36 akun booth/sponsor + 866 akun peserta. Semua diverifikasi satu per satu ke API: 902 dari 902 berhasil login.</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Atas keputusan panitia. Password di bawah juga bisa diturunkan dari data yang memang sudah ada di repo (migrasi 0033/0034), jadi ini bukan paparan baru — tapi perlakukan tetap sebagai daftar kredensial.</t>
+          <t>Atas keputusan panitia. Password di bawah juga bisa diturunkan dari data yang memang sudah ada di repo (migrasi 0037/0038), jadi ini bukan paparan baru — tapi perlakukan tetap sebagai daftar kredensial.</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Database hasil seeding resmi (migrasi 0033–0036), 27 Agustus 2026. Kalau sheet peserta/booth berubah, berkas ini harus dibuat ulang.</t>
+          <t>Seed resmi dari sheet panitia revisi 28 Agustus (migrasi 0037–0038), dibuat 29 Agustus 2026. Kalau sheet peserta/booth berubah lagi, berkas ini harus dibuat ulang.</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H859"/>
+  <dimension ref="A1:H869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1907,7 +1907,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>856 akun · WIT di urutan atas · semua sudah diuji login</t>
+          <t>866 akun · WIT di urutan atas · semua sudah diuji login</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09468</t>
+          <t>NATCON-2026-09475</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09743</t>
+          <t>NATCON-2026-09750</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09727</t>
+          <t>NATCON-2026-09734</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09110</t>
+          <t>NATCON-2026-09111</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09489</t>
+          <t>NATCON-2026-09496</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09403</t>
+          <t>NATCON-2026-09409</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09820</t>
+          <t>NATCON-2026-09828</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09261</t>
+          <t>NATCON-2026-09263</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09354</t>
+          <t>NATCON-2026-09358</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09356</t>
+          <t>NATCON-2026-09360</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09597</t>
+          <t>NATCON-2026-09604</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09830</t>
+          <t>NATCON-2026-09839</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09185</t>
+          <t>NATCON-2026-09186</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09381</t>
+          <t>NATCON-2026-09385</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09270</t>
+          <t>NATCON-2026-09272</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09635</t>
+          <t>NATCON-2026-09642</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09132</t>
+          <t>NATCON-2026-09133</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09184</t>
+          <t>NATCON-2026-09185</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09853</t>
+          <t>NATCON-2026-09863</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09546</t>
+          <t>NATCON-2026-09553</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09829</t>
+          <t>NATCON-2026-09838</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09706</t>
+          <t>NATCON-2026-09713</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09616</t>
+          <t>NATCON-2026-09623</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09336</t>
+          <t>NATCON-2026-09340</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09386</t>
+          <t>NATCON-2026-09391</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09220</t>
+          <t>NATCON-2026-09221</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09552</t>
+          <t>NATCON-2026-09559</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09677</t>
+          <t>NATCON-2026-09684</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09605</t>
+          <t>NATCON-2026-09612</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09850</t>
+          <t>NATCON-2026-09860</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09199</t>
+          <t>NATCON-2026-09200</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09100</t>
+          <t>NATCON-2026-09101</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09398</t>
+          <t>NATCON-2026-09404</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09461</t>
+          <t>NATCON-2026-09468</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09332</t>
+          <t>NATCON-2026-09336</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09818</t>
+          <t>NATCON-2026-09826</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09244</t>
+          <t>NATCON-2026-09245</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09583</t>
+          <t>NATCON-2026-09590</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09313</t>
+          <t>NATCON-2026-09317</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09725</t>
+          <t>NATCON-2026-09732</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="E47" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09654</t>
+          <t>NATCON-2026-09661</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09197</t>
+          <t>NATCON-2026-09198</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09585</t>
+          <t>NATCON-2026-09592</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09114</t>
+          <t>NATCON-2026-09115</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09606</t>
+          <t>NATCON-2026-09613</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09710</t>
+          <t>NATCON-2026-09717</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09078</t>
+          <t>NATCON-2026-09079</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>171AF-256722064</t>
+          <t>171AF-256721E18</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09540</t>
+          <t>NATCON-2026-09728</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>171AF-256721E18</t>
+          <t>171AF-256722064</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09721</t>
+          <t>NATCON-2026-09547</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>171AF-256721F10</t>
+          <t>16797-225230C24</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09243</t>
+          <t>NATCON-2026-09415</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>16797-225230C24</t>
+          <t>171AF-256721F10</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09409</t>
+          <t>NATCON-2026-09244</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09083</t>
+          <t>NATCON-2026-09084</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E61" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09803</t>
+          <t>NATCON-2026-09811</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="E62" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09142</t>
+          <t>NATCON-2026-09143</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
@@ -4429,12 +4429,12 @@
       <c r="C63" s="9" t="inlineStr"/>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>171AF-256730E17</t>
+          <t>171AF-256730F99</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09140</t>
+          <t>NATCON-2026-09588</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09278</t>
+          <t>NATCON-2026-09281</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
@@ -4505,12 +4505,12 @@
       <c r="C65" s="9" t="inlineStr"/>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>171AF-256730F99</t>
+          <t>171AF-256730E17</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09581</t>
+          <t>NATCON-2026-09141</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="E66" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09195</t>
+          <t>NATCON-2026-09196</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09717</t>
+          <t>NATCON-2026-09724</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="E68" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09480</t>
+          <t>NATCON-2026-09487</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09595</t>
+          <t>NATCON-2026-09602</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09611</t>
+          <t>NATCON-2026-09618</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09121</t>
+          <t>NATCON-2026-09122</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="E72" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09073</t>
+          <t>NATCON-2026-09074</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09508</t>
+          <t>NATCON-2026-09515</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09657</t>
+          <t>NATCON-2026-09664</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09440</t>
+          <t>NATCON-2026-09447</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09457</t>
+          <t>NATCON-2026-09464</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09514</t>
+          <t>NATCON-2026-09521</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="E78" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09793</t>
+          <t>NATCON-2026-09801</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09276</t>
+          <t>NATCON-2026-09279</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09482</t>
+          <t>NATCON-2026-09489</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09430</t>
+          <t>NATCON-2026-09437</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09561</t>
+          <t>NATCON-2026-09568</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="E83" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09579</t>
+          <t>NATCON-2026-09586</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09511</t>
+          <t>NATCON-2026-09518</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09168</t>
+          <t>NATCON-2026-09169</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09755</t>
+          <t>NATCON-2026-09762</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09672</t>
+          <t>NATCON-2026-09679</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09064</t>
+          <t>NATCON-2026-09065</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09242</t>
+          <t>NATCON-2026-09243</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09484</t>
+          <t>NATCON-2026-09491</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09236</t>
+          <t>NATCON-2026-09237</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="E92" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09146</t>
+          <t>NATCON-2026-09147</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E93" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09640</t>
+          <t>NATCON-2026-09647</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09353</t>
+          <t>NATCON-2026-09357</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09664</t>
+          <t>NATCON-2026-09671</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09507</t>
+          <t>NATCON-2026-09514</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="E97" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09288</t>
+          <t>NATCON-2026-09292</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="E98" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09841</t>
+          <t>NATCON-2026-09850</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E99" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09496</t>
+          <t>NATCON-2026-09503</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09268</t>
+          <t>NATCON-2026-09270</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="E101" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09365</t>
+          <t>NATCON-2026-09369</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09396</t>
+          <t>NATCON-2026-09402</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="E103" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09707</t>
+          <t>NATCON-2026-09714</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="E104" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09744</t>
+          <t>NATCON-2026-09751</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="E105" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09240</t>
+          <t>NATCON-2026-09241</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="E106" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09817</t>
+          <t>NATCON-2026-09825</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="E107" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09415</t>
+          <t>NATCON-2026-09421</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="E108" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09207</t>
+          <t>NATCON-2026-09208</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09620</t>
+          <t>NATCON-2026-09627</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09805</t>
+          <t>NATCON-2026-09813</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09234</t>
+          <t>NATCON-2026-09235</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="E112" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09800</t>
+          <t>NATCON-2026-09808</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="E114" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09538</t>
+          <t>NATCON-2026-09545</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09629</t>
+          <t>NATCON-2026-09636</t>
         </is>
       </c>
       <c r="F115" s="10" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09187</t>
+          <t>NATCON-2026-09188</t>
         </is>
       </c>
       <c r="F116" s="10" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="E117" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09422</t>
+          <t>NATCON-2026-09428</t>
         </is>
       </c>
       <c r="F117" s="10" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="E118" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09390</t>
+          <t>NATCON-2026-09395</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="E119" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09178</t>
+          <t>NATCON-2026-09179</t>
         </is>
       </c>
       <c r="F119" s="10" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09181</t>
+          <t>NATCON-2026-09182</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="E121" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09335</t>
+          <t>NATCON-2026-09339</t>
         </is>
       </c>
       <c r="F121" s="10" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="E122" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09262</t>
+          <t>NATCON-2026-09264</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09191</t>
+          <t>NATCON-2026-09192</t>
         </is>
       </c>
       <c r="F123" s="10" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="E124" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09566</t>
+          <t>NATCON-2026-09573</t>
         </is>
       </c>
       <c r="F124" s="10" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="E125" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09333</t>
+          <t>NATCON-2026-09337</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="E126" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09074</t>
+          <t>NATCON-2026-09075</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
@@ -7090,7 +7090,7 @@
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09441</t>
+          <t>NATCON-2026-09448</t>
         </is>
       </c>
       <c r="F127" s="10" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="E128" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09452</t>
+          <t>NATCON-2026-09459</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09425</t>
+          <t>NATCON-2026-09431</t>
         </is>
       </c>
       <c r="F129" s="10" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="E131" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09257</t>
+          <t>NATCON-2026-09259</t>
         </is>
       </c>
       <c r="F131" s="10" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="E132" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09708</t>
+          <t>NATCON-2026-09715</t>
         </is>
       </c>
       <c r="F132" s="10" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="E134" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09734</t>
+          <t>NATCON-2026-09741</t>
         </is>
       </c>
       <c r="F134" s="10" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="E135" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09551</t>
+          <t>NATCON-2026-09558</t>
         </is>
       </c>
       <c r="F135" s="10" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="E136" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09141</t>
+          <t>NATCON-2026-09142</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09773</t>
+          <t>NATCON-2026-09781</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="E138" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09779</t>
+          <t>NATCON-2026-09787</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="E139" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09518</t>
+          <t>NATCON-2026-09525</t>
         </is>
       </c>
       <c r="F139" s="10" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="E140" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09762</t>
+          <t>NATCON-2026-09769</t>
         </is>
       </c>
       <c r="F140" s="10" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="E141" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09665</t>
+          <t>NATCON-2026-09672</t>
         </is>
       </c>
       <c r="F141" s="10" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="E142" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09388</t>
+          <t>NATCON-2026-09393</t>
         </is>
       </c>
       <c r="F142" s="10" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="E143" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09554</t>
+          <t>NATCON-2026-09561</t>
         </is>
       </c>
       <c r="F143" s="10" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09109</t>
+          <t>NATCON-2026-09110</t>
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09737</t>
+          <t>NATCON-2026-09744</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
@@ -7888,7 +7888,7 @@
       </c>
       <c r="E146" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09421</t>
+          <t>NATCON-2026-09427</t>
         </is>
       </c>
       <c r="F146" s="10" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="E147" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09750</t>
+          <t>NATCON-2026-09757</t>
         </is>
       </c>
       <c r="F147" s="10" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="E149" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09400</t>
+          <t>NATCON-2026-09406</t>
         </is>
       </c>
       <c r="F149" s="10" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="E150" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09486</t>
+          <t>NATCON-2026-09493</t>
         </is>
       </c>
       <c r="F150" s="10" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09512</t>
+          <t>NATCON-2026-09519</t>
         </is>
       </c>
       <c r="F151" s="10" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="E152" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09770</t>
+          <t>NATCON-2026-09778</t>
         </is>
       </c>
       <c r="F152" s="10" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E153" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09152</t>
+          <t>NATCON-2026-09153</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="E154" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09260</t>
+          <t>NATCON-2026-09262</t>
         </is>
       </c>
       <c r="F154" s="10" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="E155" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09650</t>
+          <t>NATCON-2026-09657</t>
         </is>
       </c>
       <c r="F155" s="10" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="E156" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09619</t>
+          <t>NATCON-2026-09626</t>
         </is>
       </c>
       <c r="F156" s="10" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="E157" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09658</t>
+          <t>NATCON-2026-09665</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09608</t>
+          <t>NATCON-2026-09615</t>
         </is>
       </c>
       <c r="F158" s="10" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="E160" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09416</t>
+          <t>NATCON-2026-09422</t>
         </is>
       </c>
       <c r="F160" s="10" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="E161" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09718</t>
+          <t>NATCON-2026-09725</t>
         </is>
       </c>
       <c r="F161" s="10" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="E162" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09179</t>
+          <t>NATCON-2026-09180</t>
         </is>
       </c>
       <c r="F162" s="10" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="E163" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09726</t>
+          <t>NATCON-2026-09733</t>
         </is>
       </c>
       <c r="F163" s="10" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="E164" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09275</t>
+          <t>NATCON-2026-09278</t>
         </is>
       </c>
       <c r="F164" s="10" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="E165" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09380</t>
+          <t>NATCON-2026-09384</t>
         </is>
       </c>
       <c r="F165" s="10" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="E166" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09571</t>
+          <t>NATCON-2026-09578</t>
         </is>
       </c>
       <c r="F166" s="10" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="E167" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09382</t>
+          <t>NATCON-2026-09386</t>
         </is>
       </c>
       <c r="F167" s="10" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="E168" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09436</t>
+          <t>NATCON-2026-09443</t>
         </is>
       </c>
       <c r="F168" s="10" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="E169" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09213</t>
+          <t>NATCON-2026-09214</t>
         </is>
       </c>
       <c r="F169" s="10" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="E170" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09609</t>
+          <t>NATCON-2026-09616</t>
         </is>
       </c>
       <c r="F170" s="10" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="E171" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09444</t>
+          <t>NATCON-2026-09451</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09374</t>
+          <t>NATCON-2026-09378</t>
         </is>
       </c>
       <c r="F172" s="10" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="E173" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09647</t>
+          <t>NATCON-2026-09654</t>
         </is>
       </c>
       <c r="F173" s="10" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="E176" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09826</t>
+          <t>NATCON-2026-09834</t>
         </is>
       </c>
       <c r="F176" s="10" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="E177" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09785</t>
+          <t>NATCON-2026-09793</t>
         </is>
       </c>
       <c r="F177" s="10" t="inlineStr">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="E178" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09497</t>
+          <t>NATCON-2026-09504</t>
         </is>
       </c>
       <c r="F178" s="10" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="E179" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09369</t>
+          <t>NATCON-2026-09373</t>
         </is>
       </c>
       <c r="F179" s="10" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="E180" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09265</t>
+          <t>NATCON-2026-09267</t>
         </is>
       </c>
       <c r="F180" s="10" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="E181" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09080</t>
+          <t>NATCON-2026-09081</t>
         </is>
       </c>
       <c r="F181" s="10" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="E182" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09483</t>
+          <t>NATCON-2026-09490</t>
         </is>
       </c>
       <c r="F182" s="10" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="E183" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09144</t>
+          <t>NATCON-2026-09145</t>
         </is>
       </c>
       <c r="F183" s="10" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09175</t>
+          <t>NATCON-2026-09176</t>
         </is>
       </c>
       <c r="F185" s="10" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="E186" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09190</t>
+          <t>NATCON-2026-09191</t>
         </is>
       </c>
       <c r="F186" s="10" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="E187" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09610</t>
+          <t>NATCON-2026-09617</t>
         </is>
       </c>
       <c r="F187" s="10" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09251</t>
+          <t>NATCON-2026-09253</t>
         </is>
       </c>
       <c r="F188" s="10" t="inlineStr">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="E189" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09474</t>
+          <t>NATCON-2026-09481</t>
         </is>
       </c>
       <c r="F189" s="10" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="E190" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09557</t>
+          <t>NATCON-2026-09564</t>
         </is>
       </c>
       <c r="F190" s="10" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="E191" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09694</t>
+          <t>NATCON-2026-09701</t>
         </is>
       </c>
       <c r="F191" s="10" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="E192" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09070</t>
+          <t>NATCON-2026-09071</t>
         </is>
       </c>
       <c r="F192" s="10" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="E193" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09732</t>
+          <t>NATCON-2026-09739</t>
         </is>
       </c>
       <c r="F193" s="10" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="E194" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09271</t>
+          <t>NATCON-2026-09273</t>
         </is>
       </c>
       <c r="F194" s="10" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="E195" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09527</t>
+          <t>NATCON-2026-09534</t>
         </is>
       </c>
       <c r="F195" s="10" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="E196" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09171</t>
+          <t>NATCON-2026-09172</t>
         </is>
       </c>
       <c r="F196" s="10" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="E197" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09759</t>
+          <t>NATCON-2026-09766</t>
         </is>
       </c>
       <c r="F197" s="10" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="E198" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09633</t>
+          <t>NATCON-2026-09640</t>
         </is>
       </c>
       <c r="F198" s="10" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="E199" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09391</t>
+          <t>NATCON-2026-09396</t>
         </is>
       </c>
       <c r="F199" s="10" t="inlineStr">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="E200" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09237</t>
+          <t>NATCON-2026-09238</t>
         </is>
       </c>
       <c r="F200" s="10" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="E201" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09689</t>
+          <t>NATCON-2026-09696</t>
         </is>
       </c>
       <c r="F201" s="10" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09625</t>
+          <t>NATCON-2026-09632</t>
         </is>
       </c>
       <c r="F202" s="10" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="E203" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09165</t>
+          <t>NATCON-2026-09166</t>
         </is>
       </c>
       <c r="F203" s="10" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="E204" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09668</t>
+          <t>NATCON-2026-09675</t>
         </is>
       </c>
       <c r="F204" s="10" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09556</t>
+          <t>NATCON-2026-09563</t>
         </is>
       </c>
       <c r="F205" s="10" t="inlineStr">
@@ -10372,7 +10372,7 @@
       </c>
       <c r="E206" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09166</t>
+          <t>NATCON-2026-09167</t>
         </is>
       </c>
       <c r="F206" s="10" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="E207" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09085</t>
+          <t>NATCON-2026-09086</t>
         </is>
       </c>
       <c r="F207" s="10" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="E208" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09491</t>
+          <t>NATCON-2026-09498</t>
         </is>
       </c>
       <c r="F208" s="10" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="E210" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09662</t>
+          <t>NATCON-2026-09669</t>
         </is>
       </c>
       <c r="F210" s="10" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="E211" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09801</t>
+          <t>NATCON-2026-09809</t>
         </is>
       </c>
       <c r="F211" s="10" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="E212" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09272</t>
+          <t>NATCON-2026-09274</t>
         </is>
       </c>
       <c r="F212" s="10" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="E213" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09690</t>
+          <t>NATCON-2026-09697</t>
         </is>
       </c>
       <c r="F213" s="10" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="E214" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09769</t>
+          <t>NATCON-2026-09776</t>
         </is>
       </c>
       <c r="F214" s="10" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="E215" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09231</t>
+          <t>NATCON-2026-09232</t>
         </is>
       </c>
       <c r="F215" s="10" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="E216" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09601</t>
+          <t>NATCON-2026-09608</t>
         </is>
       </c>
       <c r="F216" s="10" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="E217" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09545</t>
+          <t>NATCON-2026-09552</t>
         </is>
       </c>
       <c r="F217" s="10" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="E218" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09246</t>
+          <t>NATCON-2026-09247</t>
         </is>
       </c>
       <c r="F218" s="10" t="inlineStr">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="E219" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09279</t>
+          <t>NATCON-2026-09282</t>
         </is>
       </c>
       <c r="F219" s="10" t="inlineStr">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="E220" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09475</t>
+          <t>NATCON-2026-09482</t>
         </is>
       </c>
       <c r="F220" s="10" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09526</t>
+          <t>NATCON-2026-09533</t>
         </is>
       </c>
       <c r="F221" s="10" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="E222" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09588</t>
+          <t>NATCON-2026-09595</t>
         </is>
       </c>
       <c r="F222" s="10" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09302</t>
+          <t>NATCON-2026-09306</t>
         </is>
       </c>
       <c r="F223" s="10" t="inlineStr">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09383</t>
+          <t>NATCON-2026-09387</t>
         </is>
       </c>
       <c r="F225" s="10" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09410</t>
+          <t>NATCON-2026-09416</t>
         </is>
       </c>
       <c r="F226" s="10" t="inlineStr">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09281</t>
+          <t>NATCON-2026-09284</t>
         </is>
       </c>
       <c r="F227" s="10" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09131</t>
+          <t>NATCON-2026-09132</t>
         </is>
       </c>
       <c r="F228" s="10" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09771</t>
+          <t>NATCON-2026-09779</t>
         </is>
       </c>
       <c r="F229" s="10" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09097</t>
+          <t>NATCON-2026-09098</t>
         </is>
       </c>
       <c r="F230" s="10" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09701</t>
+          <t>NATCON-2026-09708</t>
         </is>
       </c>
       <c r="F231" s="10" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09516</t>
+          <t>NATCON-2026-09523</t>
         </is>
       </c>
       <c r="F232" s="10" t="inlineStr">
@@ -11482,7 +11482,7 @@
       </c>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09586</t>
+          <t>NATCON-2026-09593</t>
         </is>
       </c>
       <c r="F233" s="10" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09697</t>
+          <t>NATCON-2026-09704</t>
         </is>
       </c>
       <c r="F234" s="10" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09580</t>
+          <t>NATCON-2026-09587</t>
         </is>
       </c>
       <c r="F235" s="10" t="inlineStr">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="E237" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09681</t>
+          <t>NATCON-2026-09688</t>
         </is>
       </c>
       <c r="F237" s="10" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="E239" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09136</t>
+          <t>NATCON-2026-09137</t>
         </is>
       </c>
       <c r="F239" s="10" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="E240" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09362</t>
+          <t>NATCON-2026-09366</t>
         </is>
       </c>
       <c r="F240" s="10" t="inlineStr">
@@ -11810,7 +11810,7 @@
       </c>
       <c r="E241" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09796</t>
+          <t>NATCON-2026-09804</t>
         </is>
       </c>
       <c r="F241" s="10" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09703</t>
+          <t>NATCON-2026-09710</t>
         </is>
       </c>
       <c r="F242" s="10" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="E243" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09505</t>
+          <t>NATCON-2026-09512</t>
         </is>
       </c>
       <c r="F243" s="10" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09855</t>
+          <t>NATCON-2026-09865</t>
         </is>
       </c>
       <c r="F244" s="10" t="inlineStr">
@@ -11978,7 +11978,7 @@
       </c>
       <c r="E245" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09116</t>
+          <t>NATCON-2026-09117</t>
         </is>
       </c>
       <c r="F245" s="10" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="E246" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09318</t>
+          <t>NATCON-2026-09322</t>
         </is>
       </c>
       <c r="F246" s="10" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09290</t>
+          <t>NATCON-2026-09294</t>
         </is>
       </c>
       <c r="F247" s="10" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="E248" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09729</t>
+          <t>NATCON-2026-09736</t>
         </is>
       </c>
       <c r="F248" s="10" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="E249" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09617</t>
+          <t>NATCON-2026-09624</t>
         </is>
       </c>
       <c r="F249" s="10" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="E250" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09565</t>
+          <t>NATCON-2026-09572</t>
         </is>
       </c>
       <c r="F250" s="10" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="E251" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09339</t>
+          <t>NATCON-2026-09343</t>
         </is>
       </c>
       <c r="F251" s="10" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="E252" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09340</t>
+          <t>NATCON-2026-09344</t>
         </is>
       </c>
       <c r="F252" s="10" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="E253" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09558</t>
+          <t>NATCON-2026-09565</t>
         </is>
       </c>
       <c r="F253" s="10" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="E254" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09437</t>
+          <t>NATCON-2026-09444</t>
         </is>
       </c>
       <c r="F254" s="10" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="E255" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09150</t>
+          <t>NATCON-2026-09151</t>
         </is>
       </c>
       <c r="F255" s="10" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09458</t>
+          <t>NATCON-2026-09465</t>
         </is>
       </c>
       <c r="F256" s="10" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09741</t>
+          <t>NATCON-2026-09748</t>
         </is>
       </c>
       <c r="F257" s="10" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09495</t>
+          <t>NATCON-2026-09502</t>
         </is>
       </c>
       <c r="F258" s="10" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09330</t>
+          <t>NATCON-2026-09334</t>
         </is>
       </c>
       <c r="F259" s="10" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09118</t>
+          <t>NATCON-2026-09119</t>
         </is>
       </c>
       <c r="F260" s="10" t="inlineStr">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09747</t>
+          <t>NATCON-2026-09754</t>
         </is>
       </c>
       <c r="F261" s="10" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09634</t>
+          <t>NATCON-2026-09641</t>
         </is>
       </c>
       <c r="F262" s="10" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09245</t>
+          <t>NATCON-2026-09246</t>
         </is>
       </c>
       <c r="F263" s="10" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09553</t>
+          <t>NATCON-2026-09560</t>
         </is>
       </c>
       <c r="F264" s="10" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09515</t>
+          <t>NATCON-2026-09522</t>
         </is>
       </c>
       <c r="F265" s="10" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09537</t>
+          <t>NATCON-2026-09544</t>
         </is>
       </c>
       <c r="F266" s="10" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09671</t>
+          <t>NATCON-2026-09678</t>
         </is>
       </c>
       <c r="F267" s="10" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09459</t>
+          <t>NATCON-2026-09466</t>
         </is>
       </c>
       <c r="F268" s="10" t="inlineStr">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09788</t>
+          <t>NATCON-2026-09796</t>
         </is>
       </c>
       <c r="F269" s="10" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09077</t>
+          <t>NATCON-2026-09078</t>
         </is>
       </c>
       <c r="F270" s="10" t="inlineStr">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09301</t>
+          <t>NATCON-2026-09305</t>
         </is>
       </c>
       <c r="F271" s="10" t="inlineStr">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09614</t>
+          <t>NATCON-2026-09621</t>
         </is>
       </c>
       <c r="F272" s="10" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="E273" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09782</t>
+          <t>NATCON-2026-09790</t>
         </is>
       </c>
       <c r="F273" s="10" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="E274" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09598</t>
+          <t>NATCON-2026-09605</t>
         </is>
       </c>
       <c r="F274" s="10" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09147</t>
+          <t>NATCON-2026-09148</t>
         </is>
       </c>
       <c r="F275" s="10" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="E277" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09129</t>
+          <t>NATCON-2026-09130</t>
         </is>
       </c>
       <c r="F277" s="10" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="E278" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09067</t>
+          <t>NATCON-2026-09068</t>
         </is>
       </c>
       <c r="F278" s="10" t="inlineStr">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="E279" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09392</t>
+          <t>NATCON-2026-09397</t>
         </is>
       </c>
       <c r="F279" s="10" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="E280" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09442</t>
+          <t>NATCON-2026-09449</t>
         </is>
       </c>
       <c r="F280" s="10" t="inlineStr">
@@ -13446,7 +13446,7 @@
       </c>
       <c r="E281" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09174</t>
+          <t>NATCON-2026-09175</t>
         </is>
       </c>
       <c r="F281" s="10" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="E282" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09193</t>
+          <t>NATCON-2026-09194</t>
         </is>
       </c>
       <c r="F282" s="10" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="E285" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09576</t>
+          <t>NATCON-2026-09583</t>
         </is>
       </c>
       <c r="F285" s="10" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09127</t>
+          <t>NATCON-2026-09128</t>
         </is>
       </c>
       <c r="F286" s="10" t="inlineStr">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="E287" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09831</t>
+          <t>NATCON-2026-09840</t>
         </is>
       </c>
       <c r="F287" s="10" t="inlineStr">
@@ -13740,7 +13740,7 @@
       </c>
       <c r="E288" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09569</t>
+          <t>NATCON-2026-09576</t>
         </is>
       </c>
       <c r="F288" s="10" t="inlineStr">
@@ -13782,7 +13782,7 @@
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09163</t>
+          <t>NATCON-2026-09164</t>
         </is>
       </c>
       <c r="F289" s="10" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="E290" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09149</t>
+          <t>NATCON-2026-09150</t>
         </is>
       </c>
       <c r="F290" s="10" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09252</t>
+          <t>NATCON-2026-09254</t>
         </is>
       </c>
       <c r="F292" s="10" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09308</t>
+          <t>NATCON-2026-09312</t>
         </is>
       </c>
       <c r="F293" s="10" t="inlineStr">
@@ -13992,7 +13992,7 @@
       </c>
       <c r="E294" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09367</t>
+          <t>NATCON-2026-09371</t>
         </is>
       </c>
       <c r="F294" s="10" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="E295" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09283</t>
+          <t>NATCON-2026-09286</t>
         </is>
       </c>
       <c r="F295" s="10" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09683</t>
+          <t>NATCON-2026-09690</t>
         </is>
       </c>
       <c r="F296" s="10" t="inlineStr">
@@ -14114,7 +14114,7 @@
       </c>
       <c r="E297" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09389</t>
+          <t>NATCON-2026-09394</t>
         </is>
       </c>
       <c r="F297" s="10" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="E298" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09157</t>
+          <t>NATCON-2026-09158</t>
         </is>
       </c>
       <c r="F298" s="10" t="inlineStr">
@@ -14198,7 +14198,7 @@
       </c>
       <c r="E299" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09784</t>
+          <t>NATCON-2026-09792</t>
         </is>
       </c>
       <c r="F299" s="10" t="inlineStr">
@@ -14240,7 +14240,7 @@
       </c>
       <c r="E300" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09326</t>
+          <t>NATCON-2026-09330</t>
         </is>
       </c>
       <c r="F300" s="10" t="inlineStr">
@@ -14282,7 +14282,7 @@
       </c>
       <c r="E301" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09088</t>
+          <t>NATCON-2026-09089</t>
         </is>
       </c>
       <c r="F301" s="10" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="E302" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09167</t>
+          <t>NATCON-2026-09168</t>
         </is>
       </c>
       <c r="F302" s="10" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="E304" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09305</t>
+          <t>NATCON-2026-09309</t>
         </is>
       </c>
       <c r="F304" s="10" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="E305" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09343</t>
+          <t>NATCON-2026-09347</t>
         </is>
       </c>
       <c r="F305" s="10" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="E306" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09852</t>
+          <t>NATCON-2026-09862</t>
         </is>
       </c>
       <c r="F306" s="10" t="inlineStr">
@@ -14534,7 +14534,7 @@
       </c>
       <c r="E307" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09411</t>
+          <t>NATCON-2026-09417</t>
         </is>
       </c>
       <c r="F307" s="10" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="E308" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09848</t>
+          <t>NATCON-2026-09857</t>
         </is>
       </c>
       <c r="F308" s="10" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="E309" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09493</t>
+          <t>NATCON-2026-09500</t>
         </is>
       </c>
       <c r="F309" s="10" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09211</t>
+          <t>NATCON-2026-09212</t>
         </is>
       </c>
       <c r="F310" s="10" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="E311" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09674</t>
+          <t>NATCON-2026-09681</t>
         </is>
       </c>
       <c r="F311" s="10" t="inlineStr">
@@ -14744,7 +14744,7 @@
       </c>
       <c r="E312" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09549</t>
+          <t>NATCON-2026-09556</t>
         </is>
       </c>
       <c r="F312" s="10" t="inlineStr">
@@ -14786,7 +14786,7 @@
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09345</t>
+          <t>NATCON-2026-09349</t>
         </is>
       </c>
       <c r="F313" s="10" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="E314" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09808</t>
+          <t>NATCON-2026-09816</t>
         </is>
       </c>
       <c r="F314" s="10" t="inlineStr">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="E316" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09294</t>
+          <t>NATCON-2026-09298</t>
         </is>
       </c>
       <c r="F316" s="10" t="inlineStr">
@@ -14954,7 +14954,7 @@
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09210</t>
+          <t>NATCON-2026-09211</t>
         </is>
       </c>
       <c r="F317" s="10" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="E318" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09499</t>
+          <t>NATCON-2026-09506</t>
         </is>
       </c>
       <c r="F318" s="10" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="E319" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09851</t>
+          <t>NATCON-2026-09861</t>
         </is>
       </c>
       <c r="F319" s="10" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="E320" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09248</t>
+          <t>NATCON-2026-09249</t>
         </is>
       </c>
       <c r="F320" s="10" t="inlineStr">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="E321" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09143</t>
+          <t>NATCON-2026-09144</t>
         </is>
       </c>
       <c r="F321" s="10" t="inlineStr">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="E322" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09806</t>
+          <t>NATCON-2026-09814</t>
         </is>
       </c>
       <c r="F322" s="10" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="E323" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09687</t>
+          <t>NATCON-2026-09694</t>
         </is>
       </c>
       <c r="F323" s="10" t="inlineStr">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="E324" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09738</t>
+          <t>NATCON-2026-09745</t>
         </is>
       </c>
       <c r="F324" s="10" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="E325" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09253</t>
+          <t>NATCON-2026-09255</t>
         </is>
       </c>
       <c r="F325" s="10" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="E326" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09572</t>
+          <t>NATCON-2026-09579</t>
         </is>
       </c>
       <c r="F326" s="10" t="inlineStr">
@@ -15403,12 +15403,12 @@
       <c r="C328" s="9" t="inlineStr"/>
       <c r="D328" s="9" t="inlineStr">
         <is>
-          <t>171AF-252B90B14</t>
+          <t>171AF-252B90C56</t>
         </is>
       </c>
       <c r="E328" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09327</t>
+          <t>NATCON-2026-09529</t>
         </is>
       </c>
       <c r="F328" s="10" t="inlineStr">
@@ -15441,12 +15441,12 @@
       <c r="C329" s="9" t="inlineStr"/>
       <c r="D329" s="9" t="inlineStr">
         <is>
-          <t>171AF-252B90C56</t>
+          <t>171AF-252B90B14</t>
         </is>
       </c>
       <c r="E329" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09522</t>
+          <t>NATCON-2026-09331</t>
         </is>
       </c>
       <c r="F329" s="10" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09555</t>
+          <t>NATCON-2026-09562</t>
         </is>
       </c>
       <c r="F331" s="10" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="E333" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09170</t>
+          <t>NATCON-2026-09171</t>
         </is>
       </c>
       <c r="F333" s="10" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09653</t>
+          <t>NATCON-2026-09660</t>
         </is>
       </c>
       <c r="F334" s="10" t="inlineStr">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="E335" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09849</t>
+          <t>NATCON-2026-09859</t>
         </is>
       </c>
       <c r="F335" s="10" t="inlineStr">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="E336" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09462</t>
+          <t>NATCON-2026-09469</t>
         </is>
       </c>
       <c r="F336" s="10" t="inlineStr">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="E337" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09224</t>
+          <t>NATCON-2026-09225</t>
         </is>
       </c>
       <c r="F337" s="10" t="inlineStr">
@@ -15820,7 +15820,7 @@
       </c>
       <c r="E338" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09795</t>
+          <t>NATCON-2026-09803</t>
         </is>
       </c>
       <c r="F338" s="10" t="inlineStr">
@@ -15862,7 +15862,7 @@
       </c>
       <c r="E339" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09424</t>
+          <t>NATCON-2026-09430</t>
         </is>
       </c>
       <c r="F339" s="10" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="E340" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09173</t>
+          <t>NATCON-2026-09174</t>
         </is>
       </c>
       <c r="F340" s="10" t="inlineStr">
@@ -15946,7 +15946,7 @@
       </c>
       <c r="E341" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09751</t>
+          <t>NATCON-2026-09758</t>
         </is>
       </c>
       <c r="F341" s="10" t="inlineStr">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="E342" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09776</t>
+          <t>NATCON-2026-09784</t>
         </is>
       </c>
       <c r="F342" s="10" t="inlineStr">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="E343" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09560</t>
+          <t>NATCON-2026-09567</t>
         </is>
       </c>
       <c r="F343" s="10" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="E344" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09419</t>
+          <t>NATCON-2026-09425</t>
         </is>
       </c>
       <c r="F344" s="10" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="E345" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09446</t>
+          <t>NATCON-2026-09453</t>
         </is>
       </c>
       <c r="F345" s="10" t="inlineStr">
@@ -16156,7 +16156,7 @@
       </c>
       <c r="E346" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09218</t>
+          <t>NATCON-2026-09219</t>
         </is>
       </c>
       <c r="F346" s="10" t="inlineStr">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="E347" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09698</t>
+          <t>NATCON-2026-09705</t>
         </is>
       </c>
       <c r="F347" s="10" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="E348" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09599</t>
+          <t>NATCON-2026-09606</t>
         </is>
       </c>
       <c r="F348" s="10" t="inlineStr">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="E349" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09355</t>
+          <t>NATCON-2026-09359</t>
         </is>
       </c>
       <c r="F349" s="10" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="E350" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09533</t>
+          <t>NATCON-2026-09540</t>
         </is>
       </c>
       <c r="F350" s="10" t="inlineStr">
@@ -16366,7 +16366,7 @@
       </c>
       <c r="E351" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09562</t>
+          <t>NATCON-2026-09569</t>
         </is>
       </c>
       <c r="F351" s="10" t="inlineStr">
@@ -16408,7 +16408,7 @@
       </c>
       <c r="E352" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09250</t>
+          <t>NATCON-2026-09251</t>
         </is>
       </c>
       <c r="F352" s="10" t="inlineStr">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="E353" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09204</t>
+          <t>NATCON-2026-09205</t>
         </is>
       </c>
       <c r="F353" s="10" t="inlineStr">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="E354" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09764</t>
+          <t>NATCON-2026-09771</t>
         </is>
       </c>
       <c r="F354" s="10" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="E355" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09322</t>
+          <t>NATCON-2026-09326</t>
         </is>
       </c>
       <c r="F355" s="10" t="inlineStr">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="E356" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09359</t>
+          <t>NATCON-2026-09363</t>
         </is>
       </c>
       <c r="F356" s="10" t="inlineStr">
@@ -16610,7 +16610,7 @@
       </c>
       <c r="E357" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09473</t>
+          <t>NATCON-2026-09480</t>
         </is>
       </c>
       <c r="F357" s="10" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="E358" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09377</t>
+          <t>NATCON-2026-09381</t>
         </is>
       </c>
       <c r="F358" s="10" t="inlineStr">
@@ -16694,7 +16694,7 @@
       </c>
       <c r="E359" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09285</t>
+          <t>NATCON-2026-09289</t>
         </is>
       </c>
       <c r="F359" s="10" t="inlineStr">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="E360" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09266</t>
+          <t>NATCON-2026-09268</t>
         </is>
       </c>
       <c r="F360" s="10" t="inlineStr">
@@ -16778,7 +16778,7 @@
       </c>
       <c r="E361" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09775</t>
+          <t>NATCON-2026-09783</t>
         </is>
       </c>
       <c r="F361" s="10" t="inlineStr">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="E362" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09384</t>
+          <t>NATCON-2026-09389</t>
         </is>
       </c>
       <c r="F362" s="10" t="inlineStr">
@@ -16854,7 +16854,7 @@
       </c>
       <c r="E363" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09069</t>
+          <t>NATCON-2026-09070</t>
         </is>
       </c>
       <c r="F363" s="10" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="E364" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09331</t>
+          <t>NATCON-2026-09335</t>
         </is>
       </c>
       <c r="F364" s="10" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="E365" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09794</t>
+          <t>NATCON-2026-09802</t>
         </is>
       </c>
       <c r="F365" s="10" t="inlineStr">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="E366" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09235</t>
+          <t>NATCON-2026-09236</t>
         </is>
       </c>
       <c r="F366" s="10" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="E367" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09297</t>
+          <t>NATCON-2026-09301</t>
         </is>
       </c>
       <c r="F367" s="10" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="E368" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09226</t>
+          <t>NATCON-2026-09227</t>
         </is>
       </c>
       <c r="F368" s="10" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="E369" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09177</t>
+          <t>NATCON-2026-09178</t>
         </is>
       </c>
       <c r="F369" s="10" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="E370" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09618</t>
+          <t>NATCON-2026-09625</t>
         </is>
       </c>
       <c r="F370" s="10" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="E371" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09816</t>
+          <t>NATCON-2026-09824</t>
         </is>
       </c>
       <c r="F371" s="10" t="inlineStr">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="E373" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09492</t>
+          <t>NATCON-2026-09499</t>
         </is>
       </c>
       <c r="F373" s="10" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="E374" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09797</t>
+          <t>NATCON-2026-09805</t>
         </is>
       </c>
       <c r="F374" s="10" t="inlineStr">
@@ -17354,7 +17354,7 @@
       </c>
       <c r="E375" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09105</t>
+          <t>NATCON-2026-09106</t>
         </is>
       </c>
       <c r="F375" s="10" t="inlineStr">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="E376" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09203</t>
+          <t>NATCON-2026-09204</t>
         </is>
       </c>
       <c r="F376" s="10" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="E378" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09429</t>
+          <t>NATCON-2026-09436</t>
         </is>
       </c>
       <c r="F378" s="10" t="inlineStr">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="E379" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09649</t>
+          <t>NATCON-2026-09656</t>
         </is>
       </c>
       <c r="F379" s="10" t="inlineStr">
@@ -17564,7 +17564,7 @@
       </c>
       <c r="E380" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09563</t>
+          <t>NATCON-2026-09570</t>
         </is>
       </c>
       <c r="F380" s="10" t="inlineStr">
@@ -17606,7 +17606,7 @@
       </c>
       <c r="E381" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09477</t>
+          <t>NATCON-2026-09484</t>
         </is>
       </c>
       <c r="F381" s="10" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="E383" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09754</t>
+          <t>NATCON-2026-09761</t>
         </is>
       </c>
       <c r="F383" s="10" t="inlineStr">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="E384" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09735</t>
+          <t>NATCON-2026-09742</t>
         </is>
       </c>
       <c r="F384" s="10" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="E386" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09684</t>
+          <t>NATCON-2026-09691</t>
         </is>
       </c>
       <c r="F386" s="10" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="E387" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09385</t>
+          <t>NATCON-2026-09390</t>
         </is>
       </c>
       <c r="F387" s="10" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="E388" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09404</t>
+          <t>NATCON-2026-09410</t>
         </is>
       </c>
       <c r="F388" s="10" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="E389" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09406</t>
+          <t>NATCON-2026-09412</t>
         </is>
       </c>
       <c r="F389" s="10" t="inlineStr">
@@ -17984,7 +17984,7 @@
       </c>
       <c r="E390" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09361</t>
+          <t>NATCON-2026-09365</t>
         </is>
       </c>
       <c r="F390" s="10" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="E391" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09517</t>
+          <t>NATCON-2026-09524</t>
         </is>
       </c>
       <c r="F391" s="10" t="inlineStr">
@@ -18068,7 +18068,7 @@
       </c>
       <c r="E392" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09524</t>
+          <t>NATCON-2026-09531</t>
         </is>
       </c>
       <c r="F392" s="10" t="inlineStr">
@@ -18106,7 +18106,7 @@
       </c>
       <c r="E393" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09264</t>
+          <t>NATCON-2026-09266</t>
         </is>
       </c>
       <c r="F393" s="10" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="E394" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09766</t>
+          <t>NATCON-2026-09773</t>
         </is>
       </c>
       <c r="F394" s="10" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="E395" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09337</t>
+          <t>NATCON-2026-09341</t>
         </is>
       </c>
       <c r="F395" s="10" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="E397" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09568</t>
+          <t>NATCON-2026-09575</t>
         </is>
       </c>
       <c r="F397" s="10" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="E398" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09822</t>
+          <t>NATCON-2026-09830</t>
         </is>
       </c>
       <c r="F398" s="10" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="E399" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09772</t>
+          <t>NATCON-2026-09780</t>
         </is>
       </c>
       <c r="F399" s="10" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="E400" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09449</t>
+          <t>NATCON-2026-09456</t>
         </is>
       </c>
       <c r="F400" s="10" t="inlineStr">
@@ -18430,7 +18430,7 @@
       </c>
       <c r="E401" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09402</t>
+          <t>NATCON-2026-09408</t>
         </is>
       </c>
       <c r="F401" s="10" t="inlineStr">
@@ -18472,7 +18472,7 @@
       </c>
       <c r="E402" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09096</t>
+          <t>NATCON-2026-09097</t>
         </is>
       </c>
       <c r="F402" s="10" t="inlineStr">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="E403" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09342</t>
+          <t>NATCON-2026-09346</t>
         </is>
       </c>
       <c r="F403" s="10" t="inlineStr">
@@ -18556,7 +18556,7 @@
       </c>
       <c r="E404" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09543</t>
+          <t>NATCON-2026-09550</t>
         </is>
       </c>
       <c r="F404" s="10" t="inlineStr">
@@ -18598,7 +18598,7 @@
       </c>
       <c r="E405" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09490</t>
+          <t>NATCON-2026-09497</t>
         </is>
       </c>
       <c r="F405" s="10" t="inlineStr">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="E406" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09622</t>
+          <t>NATCON-2026-09629</t>
         </is>
       </c>
       <c r="F406" s="10" t="inlineStr">
@@ -18682,7 +18682,7 @@
       </c>
       <c r="E407" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09120</t>
+          <t>NATCON-2026-09121</t>
         </is>
       </c>
       <c r="F407" s="10" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="E408" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09108</t>
+          <t>NATCON-2026-09109</t>
         </is>
       </c>
       <c r="F408" s="10" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="E409" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09366</t>
+          <t>NATCON-2026-09370</t>
         </is>
       </c>
       <c r="F409" s="10" t="inlineStr">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="E410" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09809</t>
+          <t>NATCON-2026-09817</t>
         </is>
       </c>
       <c r="F410" s="10" t="inlineStr">
@@ -18850,7 +18850,7 @@
       </c>
       <c r="E411" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09602</t>
+          <t>NATCON-2026-09609</t>
         </is>
       </c>
       <c r="F411" s="10" t="inlineStr">
@@ -18892,7 +18892,7 @@
       </c>
       <c r="E412" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09086</t>
+          <t>NATCON-2026-09087</t>
         </is>
       </c>
       <c r="F412" s="10" t="inlineStr">
@@ -18934,7 +18934,7 @@
       </c>
       <c r="E413" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09651</t>
+          <t>NATCON-2026-09658</t>
         </is>
       </c>
       <c r="F413" s="10" t="inlineStr">
@@ -19018,7 +19018,7 @@
       </c>
       <c r="E415" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09471</t>
+          <t>NATCON-2026-09478</t>
         </is>
       </c>
       <c r="F415" s="10" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="E416" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09722</t>
+          <t>NATCON-2026-09729</t>
         </is>
       </c>
       <c r="F416" s="10" t="inlineStr">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="E417" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09081</t>
+          <t>NATCON-2026-09082</t>
         </is>
       </c>
       <c r="F417" s="10" t="inlineStr">
@@ -19140,7 +19140,7 @@
       </c>
       <c r="E418" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09535</t>
+          <t>NATCON-2026-09542</t>
         </is>
       </c>
       <c r="F418" s="10" t="inlineStr">
@@ -19182,7 +19182,7 @@
       </c>
       <c r="E419" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09435</t>
+          <t>NATCON-2026-09442</t>
         </is>
       </c>
       <c r="F419" s="10" t="inlineStr">
@@ -19224,7 +19224,7 @@
       </c>
       <c r="E420" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09061</t>
+          <t>NATCON-2026-09062</t>
         </is>
       </c>
       <c r="F420" s="10" t="inlineStr">
@@ -19308,7 +19308,7 @@
       </c>
       <c r="E422" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09845</t>
+          <t>NATCON-2026-09854</t>
         </is>
       </c>
       <c r="F422" s="10" t="inlineStr">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="E423" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09350</t>
+          <t>NATCON-2026-09354</t>
         </is>
       </c>
       <c r="F423" s="10" t="inlineStr">
@@ -19392,7 +19392,7 @@
       </c>
       <c r="E424" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09592</t>
+          <t>NATCON-2026-09599</t>
         </is>
       </c>
       <c r="F424" s="10" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="E425" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09378</t>
+          <t>NATCON-2026-09382</t>
         </is>
       </c>
       <c r="F425" s="10" t="inlineStr">
@@ -19476,7 +19476,7 @@
       </c>
       <c r="E426" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09138</t>
+          <t>NATCON-2026-09139</t>
         </is>
       </c>
       <c r="F426" s="10" t="inlineStr">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="E427" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09307</t>
+          <t>NATCON-2026-09311</t>
         </is>
       </c>
       <c r="F427" s="10" t="inlineStr">
@@ -19560,7 +19560,7 @@
       </c>
       <c r="E428" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09417</t>
+          <t>NATCON-2026-09423</t>
         </is>
       </c>
       <c r="F428" s="10" t="inlineStr">
@@ -19602,7 +19602,7 @@
       </c>
       <c r="E429" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09222</t>
+          <t>NATCON-2026-09223</t>
         </is>
       </c>
       <c r="F429" s="10" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="E430" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09189</t>
+          <t>NATCON-2026-09190</t>
         </is>
       </c>
       <c r="F430" s="10" t="inlineStr">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="E431" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09573</t>
+          <t>NATCON-2026-09580</t>
         </is>
       </c>
       <c r="F431" s="10" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="E432" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09777</t>
+          <t>NATCON-2026-09785</t>
         </is>
       </c>
       <c r="F432" s="10" t="inlineStr">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="E433" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09590</t>
+          <t>NATCON-2026-09597</t>
         </is>
       </c>
       <c r="F433" s="10" t="inlineStr">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="E434" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09208</t>
+          <t>NATCON-2026-09209</t>
         </is>
       </c>
       <c r="F434" s="10" t="inlineStr">
@@ -19850,7 +19850,7 @@
       </c>
       <c r="E435" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09217</t>
+          <t>NATCON-2026-09218</t>
         </is>
       </c>
       <c r="F435" s="10" t="inlineStr">
@@ -19892,7 +19892,7 @@
       </c>
       <c r="E436" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09306</t>
+          <t>NATCON-2026-09310</t>
         </is>
       </c>
       <c r="F436" s="10" t="inlineStr">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="E437" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09692</t>
+          <t>NATCON-2026-09699</t>
         </is>
       </c>
       <c r="F437" s="10" t="inlineStr">
@@ -19976,7 +19976,7 @@
       </c>
       <c r="E438" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09719</t>
+          <t>NATCON-2026-09726</t>
         </is>
       </c>
       <c r="F438" s="10" t="inlineStr">
@@ -20018,7 +20018,7 @@
       </c>
       <c r="E439" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09637</t>
+          <t>NATCON-2026-09644</t>
         </is>
       </c>
       <c r="F439" s="10" t="inlineStr">
@@ -20060,7 +20060,7 @@
       </c>
       <c r="E440" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09663</t>
+          <t>NATCON-2026-09670</t>
         </is>
       </c>
       <c r="F440" s="10" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="E441" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09655</t>
+          <t>NATCON-2026-09662</t>
         </is>
       </c>
       <c r="F441" s="10" t="inlineStr">
@@ -20144,7 +20144,7 @@
       </c>
       <c r="E442" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09612</t>
+          <t>NATCON-2026-09619</t>
         </is>
       </c>
       <c r="F442" s="10" t="inlineStr">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="E443" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09623</t>
+          <t>NATCON-2026-09630</t>
         </is>
       </c>
       <c r="F443" s="10" t="inlineStr">
@@ -20228,7 +20228,7 @@
       </c>
       <c r="E444" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09148</t>
+          <t>NATCON-2026-09149</t>
         </is>
       </c>
       <c r="F444" s="10" t="inlineStr">
@@ -20270,7 +20270,7 @@
       </c>
       <c r="E445" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09447</t>
+          <t>NATCON-2026-09454</t>
         </is>
       </c>
       <c r="F445" s="10" t="inlineStr">
@@ -20312,7 +20312,7 @@
       </c>
       <c r="E446" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09659</t>
+          <t>NATCON-2026-09666</t>
         </is>
       </c>
       <c r="F446" s="10" t="inlineStr">
@@ -20354,7 +20354,7 @@
       </c>
       <c r="E447" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09317</t>
+          <t>NATCON-2026-09321</t>
         </is>
       </c>
       <c r="F447" s="10" t="inlineStr">
@@ -20396,7 +20396,7 @@
       </c>
       <c r="E448" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09321</t>
+          <t>NATCON-2026-09325</t>
         </is>
       </c>
       <c r="F448" s="10" t="inlineStr">
@@ -20438,7 +20438,7 @@
       </c>
       <c r="E449" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09202</t>
+          <t>NATCON-2026-09203</t>
         </is>
       </c>
       <c r="F449" s="10" t="inlineStr">
@@ -20480,7 +20480,7 @@
       </c>
       <c r="E450" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09295</t>
+          <t>NATCON-2026-09299</t>
         </is>
       </c>
       <c r="F450" s="10" t="inlineStr">
@@ -20522,7 +20522,7 @@
       </c>
       <c r="E451" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09761</t>
+          <t>NATCON-2026-09768</t>
         </is>
       </c>
       <c r="F451" s="10" t="inlineStr">
@@ -20564,7 +20564,7 @@
       </c>
       <c r="E452" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09103</t>
+          <t>NATCON-2026-09104</t>
         </is>
       </c>
       <c r="F452" s="10" t="inlineStr">
@@ -20606,7 +20606,7 @@
       </c>
       <c r="E453" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09705</t>
+          <t>NATCON-2026-09712</t>
         </is>
       </c>
       <c r="F453" s="10" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="E454" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09414</t>
+          <t>NATCON-2026-09420</t>
         </is>
       </c>
       <c r="F454" s="10" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="E455" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09364</t>
+          <t>NATCON-2026-09368</t>
         </is>
       </c>
       <c r="F455" s="10" t="inlineStr">
@@ -20732,7 +20732,7 @@
       </c>
       <c r="E456" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09428</t>
+          <t>NATCON-2026-09434</t>
         </is>
       </c>
       <c r="F456" s="10" t="inlineStr">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="E457" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09370</t>
+          <t>NATCON-2026-09374</t>
         </is>
       </c>
       <c r="F457" s="10" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="E458" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09439</t>
+          <t>NATCON-2026-09446</t>
         </is>
       </c>
       <c r="F458" s="10" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="E459" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09371</t>
+          <t>NATCON-2026-09375</t>
         </is>
       </c>
       <c r="F459" s="10" t="inlineStr">
@@ -20896,7 +20896,7 @@
       </c>
       <c r="E460" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09368</t>
+          <t>NATCON-2026-09372</t>
         </is>
       </c>
       <c r="F460" s="10" t="inlineStr">
@@ -20934,7 +20934,7 @@
       </c>
       <c r="E461" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09192</t>
+          <t>NATCON-2026-09193</t>
         </is>
       </c>
       <c r="F461" s="10" t="inlineStr">
@@ -20976,7 +20976,7 @@
       </c>
       <c r="E462" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09379</t>
+          <t>NATCON-2026-09383</t>
         </is>
       </c>
       <c r="F462" s="10" t="inlineStr">
@@ -21018,7 +21018,7 @@
       </c>
       <c r="E463" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09745</t>
+          <t>NATCON-2026-09752</t>
         </is>
       </c>
       <c r="F463" s="10" t="inlineStr">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="E464" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09630</t>
+          <t>NATCON-2026-09637</t>
         </is>
       </c>
       <c r="F464" s="10" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="E465" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09209</t>
+          <t>NATCON-2026-09210</t>
         </is>
       </c>
       <c r="F465" s="10" t="inlineStr">
@@ -21136,7 +21136,7 @@
       </c>
       <c r="E466" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09476</t>
+          <t>NATCON-2026-09483</t>
         </is>
       </c>
       <c r="F466" s="10" t="inlineStr">
@@ -21174,7 +21174,7 @@
       </c>
       <c r="E467" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09676</t>
+          <t>NATCON-2026-09683</t>
         </is>
       </c>
       <c r="F467" s="10" t="inlineStr">
@@ -21212,7 +21212,7 @@
       </c>
       <c r="E468" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09757</t>
+          <t>NATCON-2026-09764</t>
         </is>
       </c>
       <c r="F468" s="10" t="inlineStr">
@@ -21250,7 +21250,7 @@
       </c>
       <c r="E469" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09577</t>
+          <t>NATCON-2026-09584</t>
         </is>
       </c>
       <c r="F469" s="10" t="inlineStr">
@@ -21292,7 +21292,7 @@
       </c>
       <c r="E470" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09454</t>
+          <t>NATCON-2026-09461</t>
         </is>
       </c>
       <c r="F470" s="10" t="inlineStr">
@@ -21334,7 +21334,7 @@
       </c>
       <c r="E471" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09488</t>
+          <t>NATCON-2026-09495</t>
         </is>
       </c>
       <c r="F471" s="10" t="inlineStr">
@@ -21372,7 +21372,7 @@
       </c>
       <c r="E472" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09613</t>
+          <t>NATCON-2026-09620</t>
         </is>
       </c>
       <c r="F472" s="10" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="E473" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09615</t>
+          <t>NATCON-2026-09622</t>
         </is>
       </c>
       <c r="F473" s="10" t="inlineStr">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="E474" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09228</t>
+          <t>NATCON-2026-09229</t>
         </is>
       </c>
       <c r="F474" s="10" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="E475" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09487</t>
+          <t>NATCON-2026-09494</t>
         </is>
       </c>
       <c r="F475" s="10" t="inlineStr">
@@ -21540,7 +21540,7 @@
       </c>
       <c r="E476" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09159</t>
+          <t>NATCON-2026-09160</t>
         </is>
       </c>
       <c r="F476" s="10" t="inlineStr">
@@ -21578,7 +21578,7 @@
       </c>
       <c r="E477" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09539</t>
+          <t>NATCON-2026-09546</t>
         </is>
       </c>
       <c r="F477" s="10" t="inlineStr">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="E478" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09135</t>
+          <t>NATCON-2026-09136</t>
         </is>
       </c>
       <c r="F478" s="10" t="inlineStr">
@@ -21662,7 +21662,7 @@
       </c>
       <c r="E479" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09172</t>
+          <t>NATCON-2026-09173</t>
         </is>
       </c>
       <c r="F479" s="10" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="E480" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09509</t>
+          <t>NATCON-2026-09516</t>
         </is>
       </c>
       <c r="F480" s="10" t="inlineStr">
@@ -21742,7 +21742,7 @@
       </c>
       <c r="E481" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09688</t>
+          <t>NATCON-2026-09695</t>
         </is>
       </c>
       <c r="F481" s="10" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="E482" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09749</t>
+          <t>NATCON-2026-09756</t>
         </is>
       </c>
       <c r="F482" s="10" t="inlineStr">
@@ -21826,7 +21826,7 @@
       </c>
       <c r="E483" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09678</t>
+          <t>NATCON-2026-09685</t>
         </is>
       </c>
       <c r="F483" s="10" t="inlineStr">
@@ -21868,7 +21868,7 @@
       </c>
       <c r="E484" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09154</t>
+          <t>NATCON-2026-09155</t>
         </is>
       </c>
       <c r="F484" s="10" t="inlineStr">
@@ -21910,7 +21910,7 @@
       </c>
       <c r="E485" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09709</t>
+          <t>NATCON-2026-09716</t>
         </is>
       </c>
       <c r="F485" s="10" t="inlineStr">
@@ -21948,7 +21948,7 @@
       </c>
       <c r="E486" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09062</t>
+          <t>NATCON-2026-09063</t>
         </is>
       </c>
       <c r="F486" s="10" t="inlineStr">
@@ -21990,7 +21990,7 @@
       </c>
       <c r="E487" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09523</t>
+          <t>NATCON-2026-09530</t>
         </is>
       </c>
       <c r="F487" s="10" t="inlineStr">
@@ -22032,7 +22032,7 @@
       </c>
       <c r="E488" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09376</t>
+          <t>NATCON-2026-09380</t>
         </is>
       </c>
       <c r="F488" s="10" t="inlineStr">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="E489" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09107</t>
+          <t>NATCON-2026-09108</t>
         </is>
       </c>
       <c r="F489" s="10" t="inlineStr">
@@ -22116,7 +22116,7 @@
       </c>
       <c r="E490" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09704</t>
+          <t>NATCON-2026-09711</t>
         </is>
       </c>
       <c r="F490" s="10" t="inlineStr">
@@ -22158,7 +22158,7 @@
       </c>
       <c r="E491" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09134</t>
+          <t>NATCON-2026-09135</t>
         </is>
       </c>
       <c r="F491" s="10" t="inlineStr">
@@ -22242,7 +22242,7 @@
       </c>
       <c r="E493" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09847</t>
+          <t>NATCON-2026-09856</t>
         </is>
       </c>
       <c r="F493" s="10" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="E494" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09559</t>
+          <t>NATCON-2026-09566</t>
         </is>
       </c>
       <c r="F494" s="10" t="inlineStr">
@@ -22322,7 +22322,7 @@
       </c>
       <c r="E495" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09102</t>
+          <t>NATCON-2026-09103</t>
         </is>
       </c>
       <c r="F495" s="10" t="inlineStr">
@@ -22364,7 +22364,7 @@
       </c>
       <c r="E496" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09686</t>
+          <t>NATCON-2026-09693</t>
         </is>
       </c>
       <c r="F496" s="10" t="inlineStr">
@@ -22402,7 +22402,7 @@
       </c>
       <c r="E497" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09768</t>
+          <t>NATCON-2026-09775</t>
         </is>
       </c>
       <c r="F497" s="10" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="E498" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09323</t>
+          <t>NATCON-2026-09327</t>
         </is>
       </c>
       <c r="F498" s="10" t="inlineStr">
@@ -22478,7 +22478,7 @@
       </c>
       <c r="E499" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09408</t>
+          <t>NATCON-2026-09414</t>
         </is>
       </c>
       <c r="F499" s="10" t="inlineStr">
@@ -22520,7 +22520,7 @@
       </c>
       <c r="E500" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09075</t>
+          <t>NATCON-2026-09076</t>
         </is>
       </c>
       <c r="F500" s="10" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="E501" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09550</t>
+          <t>NATCON-2026-09557</t>
         </is>
       </c>
       <c r="F501" s="10" t="inlineStr">
@@ -22646,7 +22646,7 @@
       </c>
       <c r="E503" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09500</t>
+          <t>NATCON-2026-09507</t>
         </is>
       </c>
       <c r="F503" s="10" t="inlineStr">
@@ -22688,7 +22688,7 @@
       </c>
       <c r="E504" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09536</t>
+          <t>NATCON-2026-09543</t>
         </is>
       </c>
       <c r="F504" s="10" t="inlineStr">
@@ -22730,7 +22730,7 @@
       </c>
       <c r="E505" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09466</t>
+          <t>NATCON-2026-09473</t>
         </is>
       </c>
       <c r="F505" s="10" t="inlineStr">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="E506" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09357</t>
+          <t>NATCON-2026-09361</t>
         </is>
       </c>
       <c r="F506" s="10" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="E507" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09604</t>
+          <t>NATCON-2026-09611</t>
         </is>
       </c>
       <c r="F507" s="10" t="inlineStr">
@@ -22856,7 +22856,7 @@
       </c>
       <c r="E508" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09341</t>
+          <t>NATCON-2026-09345</t>
         </is>
       </c>
       <c r="F508" s="10" t="inlineStr">
@@ -22898,7 +22898,7 @@
       </c>
       <c r="E509" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09828</t>
+          <t>NATCON-2026-09837</t>
         </is>
       </c>
       <c r="F509" s="10" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="E510" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09255</t>
+          <t>NATCON-2026-09257</t>
         </is>
       </c>
       <c r="F510" s="10" t="inlineStr">
@@ -22982,7 +22982,7 @@
       </c>
       <c r="E511" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09299</t>
+          <t>NATCON-2026-09303</t>
         </is>
       </c>
       <c r="F511" s="10" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="E512" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09675</t>
+          <t>NATCON-2026-09682</t>
         </is>
       </c>
       <c r="F512" s="10" t="inlineStr">
@@ -23066,7 +23066,7 @@
       </c>
       <c r="E513" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09158</t>
+          <t>NATCON-2026-09159</t>
         </is>
       </c>
       <c r="F513" s="10" t="inlineStr">
@@ -23108,7 +23108,7 @@
       </c>
       <c r="E514" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09578</t>
+          <t>NATCON-2026-09585</t>
         </is>
       </c>
       <c r="F514" s="10" t="inlineStr">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="E515" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09186</t>
+          <t>NATCON-2026-09187</t>
         </is>
       </c>
       <c r="F515" s="10" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="E516" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09842</t>
+          <t>NATCON-2026-09851</t>
         </is>
       </c>
       <c r="F516" s="10" t="inlineStr">
@@ -23234,7 +23234,7 @@
       </c>
       <c r="E517" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09544</t>
+          <t>NATCON-2026-09551</t>
         </is>
       </c>
       <c r="F517" s="10" t="inlineStr">
@@ -23276,7 +23276,7 @@
       </c>
       <c r="E518" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09125</t>
+          <t>NATCON-2026-09126</t>
         </is>
       </c>
       <c r="F518" s="10" t="inlineStr">
@@ -23318,7 +23318,7 @@
       </c>
       <c r="E519" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09111</t>
+          <t>NATCON-2026-09112</t>
         </is>
       </c>
       <c r="F519" s="10" t="inlineStr">
@@ -23360,7 +23360,7 @@
       </c>
       <c r="E520" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09541</t>
+          <t>NATCON-2026-09548</t>
         </is>
       </c>
       <c r="F520" s="10" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="E521" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09320</t>
+          <t>NATCON-2026-09324</t>
         </is>
       </c>
       <c r="F521" s="10" t="inlineStr">
@@ -23444,7 +23444,7 @@
       </c>
       <c r="E522" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09542</t>
+          <t>NATCON-2026-09549</t>
         </is>
       </c>
       <c r="F522" s="10" t="inlineStr">
@@ -23486,7 +23486,7 @@
       </c>
       <c r="E523" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09445</t>
+          <t>NATCON-2026-09452</t>
         </is>
       </c>
       <c r="F523" s="10" t="inlineStr">
@@ -23528,7 +23528,7 @@
       </c>
       <c r="E524" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09641</t>
+          <t>NATCON-2026-09648</t>
         </is>
       </c>
       <c r="F524" s="10" t="inlineStr">
@@ -23570,7 +23570,7 @@
       </c>
       <c r="E525" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09269</t>
+          <t>NATCON-2026-09271</t>
         </is>
       </c>
       <c r="F525" s="10" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="E526" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09155</t>
+          <t>NATCON-2026-09156</t>
         </is>
       </c>
       <c r="F526" s="10" t="inlineStr">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="E527" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09660</t>
+          <t>NATCON-2026-09667</t>
         </is>
       </c>
       <c r="F527" s="10" t="inlineStr">
@@ -23696,7 +23696,7 @@
       </c>
       <c r="E528" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09513</t>
+          <t>NATCON-2026-09520</t>
         </is>
       </c>
       <c r="F528" s="10" t="inlineStr">
@@ -23738,7 +23738,7 @@
       </c>
       <c r="E529" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09723</t>
+          <t>NATCON-2026-09730</t>
         </is>
       </c>
       <c r="F529" s="10" t="inlineStr">
@@ -23780,7 +23780,7 @@
       </c>
       <c r="E530" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09296</t>
+          <t>NATCON-2026-09300</t>
         </is>
       </c>
       <c r="F530" s="10" t="inlineStr">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="E531" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09126</t>
+          <t>NATCON-2026-09127</t>
         </is>
       </c>
       <c r="F531" s="10" t="inlineStr">
@@ -23860,7 +23860,7 @@
       </c>
       <c r="E532" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09098</t>
+          <t>NATCON-2026-09099</t>
         </is>
       </c>
       <c r="F532" s="10" t="inlineStr">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="E533" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09314</t>
+          <t>NATCON-2026-09318</t>
         </is>
       </c>
       <c r="F533" s="10" t="inlineStr">
@@ -23944,7 +23944,7 @@
       </c>
       <c r="E534" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09258</t>
+          <t>NATCON-2026-09260</t>
         </is>
       </c>
       <c r="F534" s="10" t="inlineStr">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="E535" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09347</t>
+          <t>NATCON-2026-09351</t>
         </is>
       </c>
       <c r="F535" s="10" t="inlineStr">
@@ -24028,7 +24028,7 @@
       </c>
       <c r="E536" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09832</t>
+          <t>NATCON-2026-09841</t>
         </is>
       </c>
       <c r="F536" s="10" t="inlineStr">
@@ -24070,7 +24070,7 @@
       </c>
       <c r="E537" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09286</t>
+          <t>NATCON-2026-09290</t>
         </is>
       </c>
       <c r="F537" s="10" t="inlineStr">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="E538" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09503</t>
+          <t>NATCON-2026-09510</t>
         </is>
       </c>
       <c r="F538" s="10" t="inlineStr">
@@ -24154,7 +24154,7 @@
       </c>
       <c r="E539" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09072</t>
+          <t>NATCON-2026-09073</t>
         </is>
       </c>
       <c r="F539" s="10" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="E540" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09638</t>
+          <t>NATCON-2026-09645</t>
         </is>
       </c>
       <c r="F540" s="10" t="inlineStr">
@@ -24276,7 +24276,7 @@
       </c>
       <c r="E542" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09113</t>
+          <t>NATCON-2026-09114</t>
         </is>
       </c>
       <c r="F542" s="10" t="inlineStr">
@@ -24318,7 +24318,7 @@
       </c>
       <c r="E543" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09469</t>
+          <t>NATCON-2026-09476</t>
         </is>
       </c>
       <c r="F543" s="10" t="inlineStr">
@@ -24360,7 +24360,7 @@
       </c>
       <c r="E544" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09310</t>
+          <t>NATCON-2026-09314</t>
         </is>
       </c>
       <c r="F544" s="10" t="inlineStr">
@@ -24398,7 +24398,7 @@
       </c>
       <c r="E545" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09338</t>
+          <t>NATCON-2026-09342</t>
         </is>
       </c>
       <c r="F545" s="10" t="inlineStr">
@@ -24440,7 +24440,7 @@
       </c>
       <c r="E546" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09837</t>
+          <t>NATCON-2026-09846</t>
         </is>
       </c>
       <c r="F546" s="10" t="inlineStr">
@@ -24478,7 +24478,7 @@
       </c>
       <c r="E547" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09151</t>
+          <t>NATCON-2026-09152</t>
         </is>
       </c>
       <c r="F547" s="10" t="inlineStr">
@@ -24520,7 +24520,7 @@
       </c>
       <c r="E548" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09298</t>
+          <t>NATCON-2026-09302</t>
         </is>
       </c>
       <c r="F548" s="10" t="inlineStr">
@@ -24562,7 +24562,7 @@
       </c>
       <c r="E549" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09420</t>
+          <t>NATCON-2026-09426</t>
         </is>
       </c>
       <c r="F549" s="10" t="inlineStr">
@@ -24604,7 +24604,7 @@
       </c>
       <c r="E550" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09418</t>
+          <t>NATCON-2026-09424</t>
         </is>
       </c>
       <c r="F550" s="10" t="inlineStr">
@@ -24646,7 +24646,7 @@
       </c>
       <c r="E551" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09472</t>
+          <t>NATCON-2026-09479</t>
         </is>
       </c>
       <c r="F551" s="10" t="inlineStr">
@@ -24688,7 +24688,7 @@
       </c>
       <c r="E552" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09229</t>
+          <t>NATCON-2026-09230</t>
         </is>
       </c>
       <c r="F552" s="10" t="inlineStr">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="E553" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09130</t>
+          <t>NATCON-2026-09131</t>
         </is>
       </c>
       <c r="F553" s="10" t="inlineStr">
@@ -24772,7 +24772,7 @@
       </c>
       <c r="E554" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09180</t>
+          <t>NATCON-2026-09181</t>
         </is>
       </c>
       <c r="F554" s="10" t="inlineStr">
@@ -24814,7 +24814,7 @@
       </c>
       <c r="E555" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09198</t>
+          <t>NATCON-2026-09199</t>
         </is>
       </c>
       <c r="F555" s="10" t="inlineStr">
@@ -24856,7 +24856,7 @@
       </c>
       <c r="E556" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09413</t>
+          <t>NATCON-2026-09419</t>
         </is>
       </c>
       <c r="F556" s="10" t="inlineStr">
@@ -24898,7 +24898,7 @@
       </c>
       <c r="E557" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09667</t>
+          <t>NATCON-2026-09674</t>
         </is>
       </c>
       <c r="F557" s="10" t="inlineStr">
@@ -24940,7 +24940,7 @@
       </c>
       <c r="E558" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09813</t>
+          <t>NATCON-2026-09821</t>
         </is>
       </c>
       <c r="F558" s="10" t="inlineStr">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="E559" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09481</t>
+          <t>NATCON-2026-09488</t>
         </is>
       </c>
       <c r="F559" s="10" t="inlineStr">
@@ -25066,7 +25066,7 @@
       </c>
       <c r="E561" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09063</t>
+          <t>NATCON-2026-09064</t>
         </is>
       </c>
       <c r="F561" s="10" t="inlineStr">
@@ -25108,7 +25108,7 @@
       </c>
       <c r="E562" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09780</t>
+          <t>NATCON-2026-09788</t>
         </is>
       </c>
       <c r="F562" s="10" t="inlineStr">
@@ -25150,7 +25150,7 @@
       </c>
       <c r="E563" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09802</t>
+          <t>NATCON-2026-09810</t>
         </is>
       </c>
       <c r="F563" s="10" t="inlineStr">
@@ -25192,7 +25192,7 @@
       </c>
       <c r="E564" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09679</t>
+          <t>NATCON-2026-09686</t>
         </is>
       </c>
       <c r="F564" s="10" t="inlineStr">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="E565" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09123</t>
+          <t>NATCON-2026-09124</t>
         </is>
       </c>
       <c r="F565" s="10" t="inlineStr">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="E566" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09836</t>
+          <t>NATCON-2026-09845</t>
         </is>
       </c>
       <c r="F566" s="10" t="inlineStr">
@@ -25310,7 +25310,7 @@
       </c>
       <c r="E567" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09351</t>
+          <t>NATCON-2026-09355</t>
         </is>
       </c>
       <c r="F567" s="10" t="inlineStr">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="E568" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09652</t>
+          <t>NATCON-2026-09659</t>
         </is>
       </c>
       <c r="F568" s="10" t="inlineStr">
@@ -25390,7 +25390,7 @@
       </c>
       <c r="E569" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09312</t>
+          <t>NATCON-2026-09316</t>
         </is>
       </c>
       <c r="F569" s="10" t="inlineStr">
@@ -25432,7 +25432,7 @@
       </c>
       <c r="E570" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09325</t>
+          <t>NATCON-2026-09329</t>
         </is>
       </c>
       <c r="F570" s="10" t="inlineStr">
@@ -25474,7 +25474,7 @@
       </c>
       <c r="E571" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09215</t>
+          <t>NATCON-2026-09216</t>
         </is>
       </c>
       <c r="F571" s="10" t="inlineStr">
@@ -25516,7 +25516,7 @@
       </c>
       <c r="E572" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09628</t>
+          <t>NATCON-2026-09635</t>
         </is>
       </c>
       <c r="F572" s="10" t="inlineStr">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="E573" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09277</t>
+          <t>NATCON-2026-09280</t>
         </is>
       </c>
       <c r="F573" s="10" t="inlineStr">
@@ -25600,7 +25600,7 @@
       </c>
       <c r="E574" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09748</t>
+          <t>NATCON-2026-09755</t>
         </is>
       </c>
       <c r="F574" s="10" t="inlineStr">
@@ -25638,7 +25638,7 @@
       </c>
       <c r="E575" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09196</t>
+          <t>NATCON-2026-09197</t>
         </is>
       </c>
       <c r="F575" s="10" t="inlineStr">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="E576" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09304</t>
+          <t>NATCON-2026-09308</t>
         </is>
       </c>
       <c r="F576" s="10" t="inlineStr">
@@ -25722,7 +25722,7 @@
       </c>
       <c r="E577" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09455</t>
+          <t>NATCON-2026-09462</t>
         </is>
       </c>
       <c r="F577" s="10" t="inlineStr">
@@ -25764,7 +25764,7 @@
       </c>
       <c r="E578" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09145</t>
+          <t>NATCON-2026-09146</t>
         </is>
       </c>
       <c r="F578" s="10" t="inlineStr">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="E579" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09643</t>
+          <t>NATCON-2026-09650</t>
         </is>
       </c>
       <c r="F579" s="10" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="E580" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09470</t>
+          <t>NATCON-2026-09477</t>
         </is>
       </c>
       <c r="F580" s="10" t="inlineStr">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="E581" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09183</t>
+          <t>NATCON-2026-09184</t>
         </is>
       </c>
       <c r="F581" s="10" t="inlineStr">
@@ -25924,7 +25924,7 @@
       </c>
       <c r="E582" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09821</t>
+          <t>NATCON-2026-09829</t>
         </is>
       </c>
       <c r="F582" s="10" t="inlineStr">
@@ -25966,7 +25966,7 @@
       </c>
       <c r="E583" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09846</t>
+          <t>NATCON-2026-09855</t>
         </is>
       </c>
       <c r="F583" s="10" t="inlineStr">
@@ -26008,7 +26008,7 @@
       </c>
       <c r="E584" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09232</t>
+          <t>NATCON-2026-09233</t>
         </is>
       </c>
       <c r="F584" s="10" t="inlineStr">
@@ -26050,7 +26050,7 @@
       </c>
       <c r="E585" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09567</t>
+          <t>NATCON-2026-09574</t>
         </is>
       </c>
       <c r="F585" s="10" t="inlineStr">
@@ -26092,7 +26092,7 @@
       </c>
       <c r="E586" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09644</t>
+          <t>NATCON-2026-09651</t>
         </is>
       </c>
       <c r="F586" s="10" t="inlineStr">
@@ -26130,7 +26130,7 @@
       </c>
       <c r="E587" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09714</t>
+          <t>NATCON-2026-09721</t>
         </is>
       </c>
       <c r="F587" s="10" t="inlineStr">
@@ -26172,7 +26172,7 @@
       </c>
       <c r="E588" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09443</t>
+          <t>NATCON-2026-09450</t>
         </is>
       </c>
       <c r="F588" s="10" t="inlineStr">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="E590" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09834</t>
+          <t>NATCON-2026-09843</t>
         </is>
       </c>
       <c r="F590" s="10" t="inlineStr">
@@ -26298,7 +26298,7 @@
       </c>
       <c r="E591" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09407</t>
+          <t>NATCON-2026-09413</t>
         </is>
       </c>
       <c r="F591" s="10" t="inlineStr">
@@ -26340,7 +26340,7 @@
       </c>
       <c r="E592" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09282</t>
+          <t>NATCON-2026-09285</t>
         </is>
       </c>
       <c r="F592" s="10" t="inlineStr">
@@ -26382,7 +26382,7 @@
       </c>
       <c r="E593" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09669</t>
+          <t>NATCON-2026-09676</t>
         </is>
       </c>
       <c r="F593" s="10" t="inlineStr">
@@ -26424,7 +26424,7 @@
       </c>
       <c r="E594" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09465</t>
+          <t>NATCON-2026-09472</t>
         </is>
       </c>
       <c r="F594" s="10" t="inlineStr">
@@ -26508,7 +26508,7 @@
       </c>
       <c r="E596" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09071</t>
+          <t>NATCON-2026-09072</t>
         </is>
       </c>
       <c r="F596" s="10" t="inlineStr">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="E597" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09724</t>
+          <t>NATCON-2026-09731</t>
         </is>
       </c>
       <c r="F597" s="10" t="inlineStr">
@@ -26634,7 +26634,7 @@
       </c>
       <c r="E599" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09334</t>
+          <t>NATCON-2026-09338</t>
         </is>
       </c>
       <c r="F599" s="10" t="inlineStr">
@@ -26676,7 +26676,7 @@
       </c>
       <c r="E600" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09426</t>
+          <t>NATCON-2026-09432</t>
         </is>
       </c>
       <c r="F600" s="10" t="inlineStr">
@@ -26714,7 +26714,7 @@
       </c>
       <c r="E601" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09254</t>
+          <t>NATCON-2026-09256</t>
         </is>
       </c>
       <c r="F601" s="10" t="inlineStr">
@@ -26756,7 +26756,7 @@
       </c>
       <c r="E602" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09456</t>
+          <t>NATCON-2026-09463</t>
         </is>
       </c>
       <c r="F602" s="10" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="E604" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09106</t>
+          <t>NATCON-2026-09107</t>
         </is>
       </c>
       <c r="F604" s="10" t="inlineStr">
@@ -26878,7 +26878,7 @@
       </c>
       <c r="E605" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09733</t>
+          <t>NATCON-2026-09740</t>
         </is>
       </c>
       <c r="F605" s="10" t="inlineStr">
@@ -26920,7 +26920,7 @@
       </c>
       <c r="E606" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09316</t>
+          <t>NATCON-2026-09320</t>
         </is>
       </c>
       <c r="F606" s="10" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="E607" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09128</t>
+          <t>NATCON-2026-09129</t>
         </is>
       </c>
       <c r="F607" s="10" t="inlineStr">
@@ -27004,7 +27004,7 @@
       </c>
       <c r="E608" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09765</t>
+          <t>NATCON-2026-09772</t>
         </is>
       </c>
       <c r="F608" s="10" t="inlineStr">
@@ -27046,7 +27046,7 @@
       </c>
       <c r="E609" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09673</t>
+          <t>NATCON-2026-09680</t>
         </is>
       </c>
       <c r="F609" s="10" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="E610" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09274</t>
+          <t>NATCON-2026-09277</t>
         </is>
       </c>
       <c r="F610" s="10" t="inlineStr">
@@ -27130,7 +27130,7 @@
       </c>
       <c r="E611" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09412</t>
+          <t>NATCON-2026-09418</t>
         </is>
       </c>
       <c r="F611" s="10" t="inlineStr">
@@ -27172,7 +27172,7 @@
       </c>
       <c r="E612" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09758</t>
+          <t>NATCON-2026-09765</t>
         </is>
       </c>
       <c r="F612" s="10" t="inlineStr">
@@ -27214,7 +27214,7 @@
       </c>
       <c r="E613" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09582</t>
+          <t>NATCON-2026-09589</t>
         </is>
       </c>
       <c r="F613" s="10" t="inlineStr">
@@ -27256,7 +27256,7 @@
       </c>
       <c r="E614" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09247</t>
+          <t>NATCON-2026-09248</t>
         </is>
       </c>
       <c r="F614" s="10" t="inlineStr">
@@ -27298,7 +27298,7 @@
       </c>
       <c r="E615" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09570</t>
+          <t>NATCON-2026-09577</t>
         </is>
       </c>
       <c r="F615" s="10" t="inlineStr">
@@ -27340,7 +27340,7 @@
       </c>
       <c r="E616" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09223</t>
+          <t>NATCON-2026-09224</t>
         </is>
       </c>
       <c r="F616" s="10" t="inlineStr">
@@ -27378,7 +27378,7 @@
       </c>
       <c r="E617" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09783</t>
+          <t>NATCON-2026-09791</t>
         </is>
       </c>
       <c r="F617" s="10" t="inlineStr">
@@ -27420,7 +27420,7 @@
       </c>
       <c r="E618" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09799</t>
+          <t>NATCON-2026-09807</t>
         </is>
       </c>
       <c r="F618" s="10" t="inlineStr">
@@ -27462,7 +27462,7 @@
       </c>
       <c r="E619" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09713</t>
+          <t>NATCON-2026-09720</t>
         </is>
       </c>
       <c r="F619" s="10" t="inlineStr">
@@ -27504,7 +27504,7 @@
       </c>
       <c r="E620" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09645</t>
+          <t>NATCON-2026-09652</t>
         </is>
       </c>
       <c r="F620" s="10" t="inlineStr">
@@ -27588,7 +27588,7 @@
       </c>
       <c r="E622" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09133</t>
+          <t>NATCON-2026-09134</t>
         </is>
       </c>
       <c r="F622" s="10" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="E623" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09584</t>
+          <t>NATCON-2026-09591</t>
         </is>
       </c>
       <c r="F623" s="10" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="E624" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09300</t>
+          <t>NATCON-2026-09304</t>
         </is>
       </c>
       <c r="F624" s="10" t="inlineStr">
@@ -27710,7 +27710,7 @@
       </c>
       <c r="E625" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09838</t>
+          <t>NATCON-2026-09847</t>
         </is>
       </c>
       <c r="F625" s="10" t="inlineStr">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="E626" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09742</t>
+          <t>NATCON-2026-09749</t>
         </is>
       </c>
       <c r="F626" s="10" t="inlineStr">
@@ -27786,7 +27786,7 @@
       </c>
       <c r="E627" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09205</t>
+          <t>NATCON-2026-09206</t>
         </is>
       </c>
       <c r="F627" s="10" t="inlineStr">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="E628" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09510</t>
+          <t>NATCON-2026-09517</t>
         </is>
       </c>
       <c r="F628" s="10" t="inlineStr">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="E629" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09119</t>
+          <t>NATCON-2026-09120</t>
         </is>
       </c>
       <c r="F629" s="10" t="inlineStr">
@@ -27904,7 +27904,7 @@
       </c>
       <c r="E630" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09596</t>
+          <t>NATCON-2026-09603</t>
         </is>
       </c>
       <c r="F630" s="10" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="E631" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09161</t>
+          <t>NATCON-2026-09162</t>
         </is>
       </c>
       <c r="F631" s="10" t="inlineStr">
@@ -27984,7 +27984,7 @@
       </c>
       <c r="E632" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09746</t>
+          <t>NATCON-2026-09753</t>
         </is>
       </c>
       <c r="F632" s="10" t="inlineStr">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="E633" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09587</t>
+          <t>NATCON-2026-09594</t>
         </is>
       </c>
       <c r="F633" s="10" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="E634" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09854</t>
+          <t>NATCON-2026-09864</t>
         </is>
       </c>
       <c r="F634" s="10" t="inlineStr">
@@ -28102,7 +28102,7 @@
       </c>
       <c r="E635" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09626</t>
+          <t>NATCON-2026-09633</t>
         </is>
       </c>
       <c r="F635" s="10" t="inlineStr">
@@ -28178,7 +28178,7 @@
       </c>
       <c r="E637" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09230</t>
+          <t>NATCON-2026-09231</t>
         </is>
       </c>
       <c r="F637" s="10" t="inlineStr">
@@ -28216,7 +28216,7 @@
       </c>
       <c r="E638" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09711</t>
+          <t>NATCON-2026-09718</t>
         </is>
       </c>
       <c r="F638" s="10" t="inlineStr">
@@ -28292,7 +28292,7 @@
       </c>
       <c r="E640" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09548</t>
+          <t>NATCON-2026-09555</t>
         </is>
       </c>
       <c r="F640" s="10" t="inlineStr">
@@ -28330,7 +28330,7 @@
       </c>
       <c r="E641" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09303</t>
+          <t>NATCON-2026-09307</t>
         </is>
       </c>
       <c r="F641" s="10" t="inlineStr">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="E642" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09153</t>
+          <t>NATCON-2026-09154</t>
         </is>
       </c>
       <c r="F642" s="10" t="inlineStr">
@@ -28406,7 +28406,7 @@
       </c>
       <c r="E643" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09433</t>
+          <t>NATCON-2026-09440</t>
         </is>
       </c>
       <c r="F643" s="10" t="inlineStr">
@@ -28444,7 +28444,7 @@
       </c>
       <c r="E644" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09363</t>
+          <t>NATCON-2026-09367</t>
         </is>
       </c>
       <c r="F644" s="10" t="inlineStr">
@@ -28482,7 +28482,7 @@
       </c>
       <c r="E645" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09632</t>
+          <t>NATCON-2026-09639</t>
         </is>
       </c>
       <c r="F645" s="10" t="inlineStr">
@@ -28524,7 +28524,7 @@
       </c>
       <c r="E646" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09162</t>
+          <t>NATCON-2026-09163</t>
         </is>
       </c>
       <c r="F646" s="10" t="inlineStr">
@@ -28566,7 +28566,7 @@
       </c>
       <c r="E647" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09373</t>
+          <t>NATCON-2026-09377</t>
         </is>
       </c>
       <c r="F647" s="10" t="inlineStr">
@@ -28604,7 +28604,7 @@
       </c>
       <c r="E648" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09670</t>
+          <t>NATCON-2026-09677</t>
         </is>
       </c>
       <c r="F648" s="10" t="inlineStr">
@@ -28688,7 +28688,7 @@
       </c>
       <c r="E650" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09819</t>
+          <t>NATCON-2026-09827</t>
         </is>
       </c>
       <c r="F650" s="10" t="inlineStr">
@@ -28730,7 +28730,7 @@
       </c>
       <c r="E651" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09082</t>
+          <t>NATCON-2026-09083</t>
         </is>
       </c>
       <c r="F651" s="10" t="inlineStr">
@@ -28772,7 +28772,7 @@
       </c>
       <c r="E652" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09789</t>
+          <t>NATCON-2026-09797</t>
         </is>
       </c>
       <c r="F652" s="10" t="inlineStr">
@@ -28856,7 +28856,7 @@
       </c>
       <c r="E654" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09624</t>
+          <t>NATCON-2026-09631</t>
         </is>
       </c>
       <c r="F654" s="10" t="inlineStr">
@@ -28898,7 +28898,7 @@
       </c>
       <c r="E655" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09287</t>
+          <t>NATCON-2026-09291</t>
         </is>
       </c>
       <c r="F655" s="10" t="inlineStr">
@@ -28940,7 +28940,7 @@
       </c>
       <c r="E656" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09280</t>
+          <t>NATCON-2026-09283</t>
         </is>
       </c>
       <c r="F656" s="10" t="inlineStr">
@@ -28982,7 +28982,7 @@
       </c>
       <c r="E657" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09346</t>
+          <t>NATCON-2026-09350</t>
         </is>
       </c>
       <c r="F657" s="10" t="inlineStr">
@@ -29024,7 +29024,7 @@
       </c>
       <c r="E658" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09661</t>
+          <t>NATCON-2026-09668</t>
         </is>
       </c>
       <c r="F658" s="10" t="inlineStr">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="E659" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09093</t>
+          <t>NATCON-2026-09094</t>
         </is>
       </c>
       <c r="F659" s="10" t="inlineStr">
@@ -29108,7 +29108,7 @@
       </c>
       <c r="E660" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09639</t>
+          <t>NATCON-2026-09646</t>
         </is>
       </c>
       <c r="F660" s="10" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="E661" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09532</t>
+          <t>NATCON-2026-09539</t>
         </is>
       </c>
       <c r="F661" s="10" t="inlineStr">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="E662" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09781</t>
+          <t>NATCON-2026-09789</t>
         </is>
       </c>
       <c r="F662" s="10" t="inlineStr">
@@ -29230,7 +29230,7 @@
       </c>
       <c r="E663" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09122</t>
+          <t>NATCON-2026-09123</t>
         </is>
       </c>
       <c r="F663" s="10" t="inlineStr">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="E664" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09256</t>
+          <t>NATCON-2026-09258</t>
         </is>
       </c>
       <c r="F664" s="10" t="inlineStr">
@@ -29310,7 +29310,7 @@
       </c>
       <c r="E665" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09642</t>
+          <t>NATCON-2026-09649</t>
         </is>
       </c>
       <c r="F665" s="10" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="E666" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09115</t>
+          <t>NATCON-2026-09116</t>
         </is>
       </c>
       <c r="F666" s="10" t="inlineStr">
@@ -29394,7 +29394,7 @@
       </c>
       <c r="E667" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09293</t>
+          <t>NATCON-2026-09297</t>
         </is>
       </c>
       <c r="F667" s="10" t="inlineStr">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="E668" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09241</t>
+          <t>NATCON-2026-09242</t>
         </is>
       </c>
       <c r="F668" s="10" t="inlineStr">
@@ -29478,7 +29478,7 @@
       </c>
       <c r="E669" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09833</t>
+          <t>NATCON-2026-09842</t>
         </is>
       </c>
       <c r="F669" s="10" t="inlineStr">
@@ -29520,7 +29520,7 @@
       </c>
       <c r="E670" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09091</t>
+          <t>NATCON-2026-09092</t>
         </is>
       </c>
       <c r="F670" s="10" t="inlineStr">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="E671" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09358</t>
+          <t>NATCON-2026-09362</t>
         </is>
       </c>
       <c r="F671" s="10" t="inlineStr">
@@ -29604,7 +29604,7 @@
       </c>
       <c r="E672" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09790</t>
+          <t>NATCON-2026-09798</t>
         </is>
       </c>
       <c r="F672" s="10" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="E673" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09621</t>
+          <t>NATCON-2026-09628</t>
         </is>
       </c>
       <c r="F673" s="10" t="inlineStr">
@@ -29688,7 +29688,7 @@
       </c>
       <c r="E674" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09575</t>
+          <t>NATCON-2026-09582</t>
         </is>
       </c>
       <c r="F674" s="10" t="inlineStr">
@@ -29730,7 +29730,7 @@
       </c>
       <c r="E675" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09397</t>
+          <t>NATCON-2026-09403</t>
         </is>
       </c>
       <c r="F675" s="10" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="E676" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09699</t>
+          <t>NATCON-2026-09706</t>
         </is>
       </c>
       <c r="F676" s="10" t="inlineStr">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="E677" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09448</t>
+          <t>NATCON-2026-09455</t>
         </is>
       </c>
       <c r="F677" s="10" t="inlineStr">
@@ -29852,7 +29852,7 @@
       </c>
       <c r="E678" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09839</t>
+          <t>NATCON-2026-09848</t>
         </is>
       </c>
       <c r="F678" s="10" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="E679" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09752</t>
+          <t>NATCON-2026-09759</t>
         </is>
       </c>
       <c r="F679" s="10" t="inlineStr">
@@ -29936,7 +29936,7 @@
       </c>
       <c r="E680" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09099</t>
+          <t>NATCON-2026-09100</t>
         </is>
       </c>
       <c r="F680" s="10" t="inlineStr">
@@ -29978,7 +29978,7 @@
       </c>
       <c r="E681" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09267</t>
+          <t>NATCON-2026-09269</t>
         </is>
       </c>
       <c r="F681" s="10" t="inlineStr">
@@ -30020,7 +30020,7 @@
       </c>
       <c r="E682" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09169</t>
+          <t>NATCON-2026-09170</t>
         </is>
       </c>
       <c r="F682" s="10" t="inlineStr">
@@ -30058,7 +30058,7 @@
       </c>
       <c r="E683" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09607</t>
+          <t>NATCON-2026-09614</t>
         </is>
       </c>
       <c r="F683" s="10" t="inlineStr">
@@ -30100,7 +30100,7 @@
       </c>
       <c r="E684" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09401</t>
+          <t>NATCON-2026-09407</t>
         </is>
       </c>
       <c r="F684" s="10" t="inlineStr">
@@ -30142,7 +30142,7 @@
       </c>
       <c r="E685" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09344</t>
+          <t>NATCON-2026-09348</t>
         </is>
       </c>
       <c r="F685" s="10" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="E686" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09798</t>
+          <t>NATCON-2026-09806</t>
         </is>
       </c>
       <c r="F686" s="10" t="inlineStr">
@@ -30226,7 +30226,7 @@
       </c>
       <c r="E687" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09827</t>
+          <t>NATCON-2026-09836</t>
         </is>
       </c>
       <c r="F687" s="10" t="inlineStr">
@@ -30268,7 +30268,7 @@
       </c>
       <c r="E688" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09431</t>
+          <t>NATCON-2026-09438</t>
         </is>
       </c>
       <c r="F688" s="10" t="inlineStr">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="E689" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09394</t>
+          <t>NATCON-2026-09400</t>
         </is>
       </c>
       <c r="F689" s="10" t="inlineStr">
@@ -30352,7 +30352,7 @@
       </c>
       <c r="E690" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09814</t>
+          <t>NATCON-2026-09822</t>
         </is>
       </c>
       <c r="F690" s="10" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="E691" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09520</t>
+          <t>NATCON-2026-09527</t>
         </is>
       </c>
       <c r="F691" s="10" t="inlineStr">
@@ -30436,7 +30436,7 @@
       </c>
       <c r="E692" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09736</t>
+          <t>NATCON-2026-09743</t>
         </is>
       </c>
       <c r="F692" s="10" t="inlineStr">
@@ -30478,7 +30478,7 @@
       </c>
       <c r="E693" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09225</t>
+          <t>NATCON-2026-09226</t>
         </is>
       </c>
       <c r="F693" s="10" t="inlineStr">
@@ -30520,7 +30520,7 @@
       </c>
       <c r="E694" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09066</t>
+          <t>NATCON-2026-09067</t>
         </is>
       </c>
       <c r="F694" s="10" t="inlineStr">
@@ -30562,7 +30562,7 @@
       </c>
       <c r="E695" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09534</t>
+          <t>NATCON-2026-09541</t>
         </is>
       </c>
       <c r="F695" s="10" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="E696" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09311</t>
+          <t>NATCON-2026-09315</t>
         </is>
       </c>
       <c r="F696" s="10" t="inlineStr">
@@ -30688,7 +30688,7 @@
       </c>
       <c r="E698" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09811</t>
+          <t>NATCON-2026-09819</t>
         </is>
       </c>
       <c r="F698" s="10" t="inlineStr">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="E699" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09501</t>
+          <t>NATCON-2026-09508</t>
         </is>
       </c>
       <c r="F699" s="10" t="inlineStr">
@@ -30772,7 +30772,7 @@
       </c>
       <c r="E700" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09453</t>
+          <t>NATCON-2026-09460</t>
         </is>
       </c>
       <c r="F700" s="10" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="E701" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09682</t>
+          <t>NATCON-2026-09689</t>
         </is>
       </c>
       <c r="F701" s="10" t="inlineStr">
@@ -30856,7 +30856,7 @@
       </c>
       <c r="E702" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09740</t>
+          <t>NATCON-2026-09747</t>
         </is>
       </c>
       <c r="F702" s="10" t="inlineStr">
@@ -30898,7 +30898,7 @@
       </c>
       <c r="E703" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09530</t>
+          <t>NATCON-2026-09537</t>
         </is>
       </c>
       <c r="F703" s="10" t="inlineStr">
@@ -30940,7 +30940,7 @@
       </c>
       <c r="E704" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09319</t>
+          <t>NATCON-2026-09323</t>
         </is>
       </c>
       <c r="F704" s="10" t="inlineStr">
@@ -30978,7 +30978,7 @@
       </c>
       <c r="E705" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09763</t>
+          <t>NATCON-2026-09770</t>
         </is>
       </c>
       <c r="F705" s="10" t="inlineStr">
@@ -31020,7 +31020,7 @@
       </c>
       <c r="E706" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09089</t>
+          <t>NATCON-2026-09090</t>
         </is>
       </c>
       <c r="F706" s="10" t="inlineStr">
@@ -31057,12 +31057,12 @@
       </c>
       <c r="D707" s="9" t="inlineStr">
         <is>
-          <t>171AF-25672D024</t>
+          <t>171AF-25672D135</t>
         </is>
       </c>
       <c r="E707" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09451</t>
+          <t>NATCON-2026-09207</t>
         </is>
       </c>
       <c r="F707" s="10" t="inlineStr">
@@ -31099,17 +31099,17 @@
       </c>
       <c r="D708" s="9" t="inlineStr">
         <is>
-          <t>171AF-25672D135</t>
+          <t>16C6C-23DEEA058</t>
         </is>
       </c>
       <c r="E708" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09206</t>
+          <t>NATCON-2026-09844</t>
         </is>
       </c>
       <c r="F708" s="10" t="inlineStr">
         <is>
-          <t>leonard.rosandy@elistec.com</t>
+          <t>leonardrosandy@gmail.com</t>
         </is>
       </c>
       <c r="G708" s="10" t="inlineStr">
@@ -31146,7 +31146,7 @@
       </c>
       <c r="E709" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09156</t>
+          <t>NATCON-2026-09157</t>
         </is>
       </c>
       <c r="F709" s="10" t="inlineStr">
@@ -31183,17 +31183,17 @@
       </c>
       <c r="D710" s="9" t="inlineStr">
         <is>
-          <t>16C6C-23DEEA058</t>
+          <t>171AF-25672D024</t>
         </is>
       </c>
       <c r="E710" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09835</t>
+          <t>NATCON-2026-09458</t>
         </is>
       </c>
       <c r="F710" s="10" t="inlineStr">
         <is>
-          <t>leonardrosandy@gmail.com</t>
+          <t>leonard.rosandy@elistec.com</t>
         </is>
       </c>
       <c r="G710" s="10" t="inlineStr">
@@ -31226,7 +31226,7 @@
       </c>
       <c r="E711" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09810</t>
+          <t>NATCON-2026-09818</t>
         </is>
       </c>
       <c r="F711" s="10" t="inlineStr">
@@ -31268,7 +31268,7 @@
       </c>
       <c r="E712" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09387</t>
+          <t>NATCON-2026-09392</t>
         </is>
       </c>
       <c r="F712" s="10" t="inlineStr">
@@ -31310,7 +31310,7 @@
       </c>
       <c r="E713" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09753</t>
+          <t>NATCON-2026-09760</t>
         </is>
       </c>
       <c r="F713" s="10" t="inlineStr">
@@ -31352,7 +31352,7 @@
       </c>
       <c r="E714" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09791</t>
+          <t>NATCON-2026-09799</t>
         </is>
       </c>
       <c r="F714" s="10" t="inlineStr">
@@ -31394,7 +31394,7 @@
       </c>
       <c r="E715" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09696</t>
+          <t>NATCON-2026-09703</t>
         </is>
       </c>
       <c r="F715" s="10" t="inlineStr">
@@ -31436,7 +31436,7 @@
       </c>
       <c r="E716" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09521</t>
+          <t>NATCON-2026-09528</t>
         </is>
       </c>
       <c r="F716" s="10" t="inlineStr">
@@ -31478,7 +31478,7 @@
       </c>
       <c r="E717" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09787</t>
+          <t>NATCON-2026-09795</t>
         </is>
       </c>
       <c r="F717" s="10" t="inlineStr">
@@ -31520,7 +31520,7 @@
       </c>
       <c r="E718" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09124</t>
+          <t>NATCON-2026-09125</t>
         </is>
       </c>
       <c r="F718" s="10" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="E719" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09815</t>
+          <t>NATCON-2026-09823</t>
         </is>
       </c>
       <c r="F719" s="10" t="inlineStr">
@@ -31604,7 +31604,7 @@
       </c>
       <c r="E720" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09767</t>
+          <t>NATCON-2026-09774</t>
         </is>
       </c>
       <c r="F720" s="10" t="inlineStr">
@@ -31646,7 +31646,7 @@
       </c>
       <c r="E721" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09636</t>
+          <t>NATCON-2026-09643</t>
         </is>
       </c>
       <c r="F721" s="10" t="inlineStr">
@@ -31688,7 +31688,7 @@
       </c>
       <c r="E722" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09739</t>
+          <t>NATCON-2026-09746</t>
         </is>
       </c>
       <c r="F722" s="10" t="inlineStr">
@@ -31768,7 +31768,7 @@
       </c>
       <c r="E724" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09756</t>
+          <t>NATCON-2026-09763</t>
         </is>
       </c>
       <c r="F724" s="10" t="inlineStr">
@@ -31810,7 +31810,7 @@
       </c>
       <c r="E725" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09068</t>
+          <t>NATCON-2026-09069</t>
         </is>
       </c>
       <c r="F725" s="10" t="inlineStr">
@@ -31852,7 +31852,7 @@
       </c>
       <c r="E726" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09700</t>
+          <t>NATCON-2026-09707</t>
         </is>
       </c>
       <c r="F726" s="10" t="inlineStr">
@@ -31894,7 +31894,7 @@
       </c>
       <c r="E727" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09324</t>
+          <t>NATCON-2026-09328</t>
         </is>
       </c>
       <c r="F727" s="10" t="inlineStr">
@@ -31936,7 +31936,7 @@
       </c>
       <c r="E728" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09840</t>
+          <t>NATCON-2026-09849</t>
         </is>
       </c>
       <c r="F728" s="10" t="inlineStr">
@@ -31974,7 +31974,7 @@
       </c>
       <c r="E729" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09591</t>
+          <t>NATCON-2026-09598</t>
         </is>
       </c>
       <c r="F729" s="10" t="inlineStr">
@@ -32016,7 +32016,7 @@
       </c>
       <c r="E730" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09212</t>
+          <t>NATCON-2026-09213</t>
         </is>
       </c>
       <c r="F730" s="10" t="inlineStr">
@@ -32058,7 +32058,7 @@
       </c>
       <c r="E731" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09434</t>
+          <t>NATCON-2026-09441</t>
         </is>
       </c>
       <c r="F731" s="10" t="inlineStr">
@@ -32100,7 +32100,7 @@
       </c>
       <c r="E732" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09716</t>
+          <t>NATCON-2026-09723</t>
         </is>
       </c>
       <c r="F732" s="10" t="inlineStr">
@@ -32142,7 +32142,7 @@
       </c>
       <c r="E733" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09273</t>
+          <t>NATCON-2026-09275</t>
         </is>
       </c>
       <c r="F733" s="10" t="inlineStr">
@@ -32184,7 +32184,7 @@
       </c>
       <c r="E734" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09593</t>
+          <t>NATCON-2026-09600</t>
         </is>
       </c>
       <c r="F734" s="10" t="inlineStr">
@@ -32226,7 +32226,7 @@
       </c>
       <c r="E735" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09249</t>
+          <t>NATCON-2026-09250</t>
         </is>
       </c>
       <c r="F735" s="10" t="inlineStr">
@@ -32268,7 +32268,7 @@
       </c>
       <c r="E736" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09117</t>
+          <t>NATCON-2026-09118</t>
         </is>
       </c>
       <c r="F736" s="10" t="inlineStr">
@@ -32310,7 +32310,7 @@
       </c>
       <c r="E737" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09656</t>
+          <t>NATCON-2026-09663</t>
         </is>
       </c>
       <c r="F737" s="10" t="inlineStr">
@@ -32394,7 +32394,7 @@
       </c>
       <c r="E739" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09844</t>
+          <t>NATCON-2026-09853</t>
         </is>
       </c>
       <c r="F739" s="10" t="inlineStr">
@@ -32436,7 +32436,7 @@
       </c>
       <c r="E740" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09685</t>
+          <t>NATCON-2026-09692</t>
         </is>
       </c>
       <c r="F740" s="10" t="inlineStr">
@@ -32478,7 +32478,7 @@
       </c>
       <c r="E741" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09259</t>
+          <t>NATCON-2026-09261</t>
         </is>
       </c>
       <c r="F741" s="10" t="inlineStr">
@@ -32520,7 +32520,7 @@
       </c>
       <c r="E742" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09603</t>
+          <t>NATCON-2026-09610</t>
         </is>
       </c>
       <c r="F742" s="10" t="inlineStr">
@@ -32562,7 +32562,7 @@
       </c>
       <c r="E743" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09467</t>
+          <t>NATCON-2026-09474</t>
         </is>
       </c>
       <c r="F743" s="10" t="inlineStr">
@@ -32604,7 +32604,7 @@
       </c>
       <c r="E744" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09427</t>
+          <t>NATCON-2026-09433</t>
         </is>
       </c>
       <c r="F744" s="10" t="inlineStr">
@@ -32646,7 +32646,7 @@
       </c>
       <c r="E745" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09079</t>
+          <t>NATCON-2026-09080</t>
         </is>
       </c>
       <c r="F745" s="10" t="inlineStr">
@@ -32688,7 +32688,7 @@
       </c>
       <c r="E746" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09094</t>
+          <t>NATCON-2026-09095</t>
         </is>
       </c>
       <c r="F746" s="10" t="inlineStr">
@@ -32730,7 +32730,7 @@
       </c>
       <c r="E747" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09432</t>
+          <t>NATCON-2026-09439</t>
         </is>
       </c>
       <c r="F747" s="10" t="inlineStr">
@@ -32772,7 +32772,7 @@
       </c>
       <c r="E748" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09547</t>
+          <t>NATCON-2026-09554</t>
         </is>
       </c>
       <c r="F748" s="10" t="inlineStr">
@@ -32856,7 +32856,7 @@
       </c>
       <c r="E750" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09182</t>
+          <t>NATCON-2026-09183</t>
         </is>
       </c>
       <c r="F750" s="10" t="inlineStr">
@@ -32898,7 +32898,7 @@
       </c>
       <c r="E751" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09760</t>
+          <t>NATCON-2026-09767</t>
         </is>
       </c>
       <c r="F751" s="10" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="E752" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09214</t>
+          <t>NATCON-2026-09215</t>
         </is>
       </c>
       <c r="F752" s="10" t="inlineStr">
@@ -32982,7 +32982,7 @@
       </c>
       <c r="E753" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09176</t>
+          <t>NATCON-2026-09177</t>
         </is>
       </c>
       <c r="F753" s="10" t="inlineStr">
@@ -33024,7 +33024,7 @@
       </c>
       <c r="E754" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09691</t>
+          <t>NATCON-2026-09698</t>
         </is>
       </c>
       <c r="F754" s="10" t="inlineStr">
@@ -33066,7 +33066,7 @@
       </c>
       <c r="E755" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09506</t>
+          <t>NATCON-2026-09513</t>
         </is>
       </c>
       <c r="F755" s="10" t="inlineStr">
@@ -33108,7 +33108,7 @@
       </c>
       <c r="E756" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09525</t>
+          <t>NATCON-2026-09532</t>
         </is>
       </c>
       <c r="F756" s="10" t="inlineStr">
@@ -33146,7 +33146,7 @@
       </c>
       <c r="E757" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09087</t>
+          <t>NATCON-2026-09088</t>
         </is>
       </c>
       <c r="F757" s="10" t="inlineStr">
@@ -33188,7 +33188,7 @@
       </c>
       <c r="E758" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09238</t>
+          <t>NATCON-2026-09239</t>
         </is>
       </c>
       <c r="F758" s="10" t="inlineStr">
@@ -33230,7 +33230,7 @@
       </c>
       <c r="E759" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09715</t>
+          <t>NATCON-2026-09722</t>
         </is>
       </c>
       <c r="F759" s="10" t="inlineStr">
@@ -33272,7 +33272,7 @@
       </c>
       <c r="E760" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09627</t>
+          <t>NATCON-2026-09634</t>
         </is>
       </c>
       <c r="F760" s="10" t="inlineStr">
@@ -33314,7 +33314,7 @@
       </c>
       <c r="E761" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09728</t>
+          <t>NATCON-2026-09735</t>
         </is>
       </c>
       <c r="F761" s="10" t="inlineStr">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="E762" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09824</t>
+          <t>NATCON-2026-09832</t>
         </is>
       </c>
       <c r="F762" s="10" t="inlineStr">
@@ -33398,7 +33398,7 @@
       </c>
       <c r="E763" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09464</t>
+          <t>NATCON-2026-09471</t>
         </is>
       </c>
       <c r="F763" s="10" t="inlineStr">
@@ -33440,7 +33440,7 @@
       </c>
       <c r="E764" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09090</t>
+          <t>NATCON-2026-09091</t>
         </is>
       </c>
       <c r="F764" s="10" t="inlineStr">
@@ -33482,7 +33482,7 @@
       </c>
       <c r="E765" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09160</t>
+          <t>NATCON-2026-09161</t>
         </is>
       </c>
       <c r="F765" s="10" t="inlineStr">
@@ -33524,7 +33524,7 @@
       </c>
       <c r="E766" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09594</t>
+          <t>NATCON-2026-09601</t>
         </is>
       </c>
       <c r="F766" s="10" t="inlineStr">
@@ -33608,7 +33608,7 @@
       </c>
       <c r="E768" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09804</t>
+          <t>NATCON-2026-09812</t>
         </is>
       </c>
       <c r="F768" s="10" t="inlineStr">
@@ -33692,7 +33692,7 @@
       </c>
       <c r="E770" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09680</t>
+          <t>NATCON-2026-09687</t>
         </is>
       </c>
       <c r="F770" s="10" t="inlineStr">
@@ -33734,7 +33734,7 @@
       </c>
       <c r="E771" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09631</t>
+          <t>NATCON-2026-09638</t>
         </is>
       </c>
       <c r="F771" s="10" t="inlineStr">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="E772" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09375</t>
+          <t>NATCON-2026-09379</t>
         </is>
       </c>
       <c r="F772" s="10" t="inlineStr">
@@ -33818,7 +33818,7 @@
       </c>
       <c r="E773" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09405</t>
+          <t>NATCON-2026-09411</t>
         </is>
       </c>
       <c r="F773" s="10" t="inlineStr">
@@ -33860,7 +33860,7 @@
       </c>
       <c r="E774" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09092</t>
+          <t>NATCON-2026-09093</t>
         </is>
       </c>
       <c r="F774" s="10" t="inlineStr">
@@ -33902,7 +33902,7 @@
       </c>
       <c r="E775" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09564</t>
+          <t>NATCON-2026-09571</t>
         </is>
       </c>
       <c r="F775" s="10" t="inlineStr">
@@ -33944,7 +33944,7 @@
       </c>
       <c r="E776" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09823</t>
+          <t>NATCON-2026-09831</t>
         </is>
       </c>
       <c r="F776" s="10" t="inlineStr">
@@ -33986,7 +33986,7 @@
       </c>
       <c r="E777" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09812</t>
+          <t>NATCON-2026-09820</t>
         </is>
       </c>
       <c r="F777" s="10" t="inlineStr">
@@ -34028,7 +34028,7 @@
       </c>
       <c r="E778" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09139</t>
+          <t>NATCON-2026-09140</t>
         </is>
       </c>
       <c r="F778" s="10" t="inlineStr">
@@ -34066,7 +34066,7 @@
       </c>
       <c r="E779" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09774</t>
+          <t>NATCON-2026-09782</t>
         </is>
       </c>
       <c r="F779" s="10" t="inlineStr">
@@ -34108,7 +34108,7 @@
       </c>
       <c r="E780" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09194</t>
+          <t>NATCON-2026-09195</t>
         </is>
       </c>
       <c r="F780" s="10" t="inlineStr">
@@ -34150,7 +34150,7 @@
       </c>
       <c r="E781" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09239</t>
+          <t>NATCON-2026-09240</t>
         </is>
       </c>
       <c r="F781" s="10" t="inlineStr">
@@ -34192,7 +34192,7 @@
       </c>
       <c r="E782" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09438</t>
+          <t>NATCON-2026-09445</t>
         </is>
       </c>
       <c r="F782" s="10" t="inlineStr">
@@ -34234,7 +34234,7 @@
       </c>
       <c r="E783" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09856</t>
+          <t>NATCON-2026-09866</t>
         </is>
       </c>
       <c r="F783" s="10" t="inlineStr">
@@ -34276,7 +34276,7 @@
       </c>
       <c r="E784" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09792</t>
+          <t>NATCON-2026-09800</t>
         </is>
       </c>
       <c r="F784" s="10" t="inlineStr">
@@ -34360,7 +34360,7 @@
       </c>
       <c r="E786" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09101</t>
+          <t>NATCON-2026-09102</t>
         </is>
       </c>
       <c r="F786" s="10" t="inlineStr">
@@ -34402,7 +34402,7 @@
       </c>
       <c r="E787" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09600</t>
+          <t>NATCON-2026-09607</t>
         </is>
       </c>
       <c r="F787" s="10" t="inlineStr">
@@ -34444,7 +34444,7 @@
       </c>
       <c r="E788" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09200</t>
+          <t>NATCON-2026-09201</t>
         </is>
       </c>
       <c r="F788" s="10" t="inlineStr">
@@ -34482,7 +34482,7 @@
       </c>
       <c r="E789" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09395</t>
+          <t>NATCON-2026-09401</t>
         </is>
       </c>
       <c r="F789" s="10" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="E790" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09233</t>
+          <t>NATCON-2026-09234</t>
         </is>
       </c>
       <c r="F790" s="10" t="inlineStr">
@@ -34566,7 +34566,7 @@
       </c>
       <c r="E791" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09529</t>
+          <t>NATCON-2026-09536</t>
         </is>
       </c>
       <c r="F791" s="10" t="inlineStr">
@@ -34608,7 +34608,7 @@
       </c>
       <c r="E792" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09095</t>
+          <t>NATCON-2026-09096</t>
         </is>
       </c>
       <c r="F792" s="10" t="inlineStr">
@@ -34692,7 +34692,7 @@
       </c>
       <c r="E794" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09648</t>
+          <t>NATCON-2026-09655</t>
         </is>
       </c>
       <c r="F794" s="10" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="E795" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09478</t>
+          <t>NATCON-2026-09485</t>
         </is>
       </c>
       <c r="F795" s="10" t="inlineStr">
@@ -34776,7 +34776,7 @@
       </c>
       <c r="E796" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09112</t>
+          <t>NATCON-2026-09113</t>
         </is>
       </c>
       <c r="F796" s="10" t="inlineStr">
@@ -34860,7 +34860,7 @@
       </c>
       <c r="E798" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09463</t>
+          <t>NATCON-2026-09470</t>
         </is>
       </c>
       <c r="F798" s="10" t="inlineStr">
@@ -34898,7 +34898,7 @@
       </c>
       <c r="E799" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09450</t>
+          <t>NATCON-2026-09457</t>
         </is>
       </c>
       <c r="F799" s="10" t="inlineStr">
@@ -34940,7 +34940,7 @@
       </c>
       <c r="E800" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09786</t>
+          <t>NATCON-2026-09794</t>
         </is>
       </c>
       <c r="F800" s="10" t="inlineStr">
@@ -34982,7 +34982,7 @@
       </c>
       <c r="E801" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09666</t>
+          <t>NATCON-2026-09673</t>
         </is>
       </c>
       <c r="F801" s="10" t="inlineStr">
@@ -35024,7 +35024,7 @@
       </c>
       <c r="E802" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09315</t>
+          <t>NATCON-2026-09319</t>
         </is>
       </c>
       <c r="F802" s="10" t="inlineStr">
@@ -35066,7 +35066,7 @@
       </c>
       <c r="E803" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09646</t>
+          <t>NATCON-2026-09653</t>
         </is>
       </c>
       <c r="F803" s="10" t="inlineStr">
@@ -35108,7 +35108,7 @@
       </c>
       <c r="E804" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09712</t>
+          <t>NATCON-2026-09719</t>
         </is>
       </c>
       <c r="F804" s="10" t="inlineStr">
@@ -35150,7 +35150,7 @@
       </c>
       <c r="E805" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09164</t>
+          <t>NATCON-2026-09165</t>
         </is>
       </c>
       <c r="F805" s="10" t="inlineStr">
@@ -35188,7 +35188,7 @@
       </c>
       <c r="E806" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09188</t>
+          <t>NATCON-2026-09189</t>
         </is>
       </c>
       <c r="F806" s="10" t="inlineStr">
@@ -35230,7 +35230,7 @@
       </c>
       <c r="E807" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09201</t>
+          <t>NATCON-2026-09202</t>
         </is>
       </c>
       <c r="F807" s="10" t="inlineStr">
@@ -35268,7 +35268,7 @@
       </c>
       <c r="E808" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09460</t>
+          <t>NATCON-2026-09467</t>
         </is>
       </c>
       <c r="F808" s="10" t="inlineStr">
@@ -35306,7 +35306,7 @@
       </c>
       <c r="E809" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09731</t>
+          <t>NATCON-2026-09738</t>
         </is>
       </c>
       <c r="F809" s="10" t="inlineStr">
@@ -35344,7 +35344,7 @@
       </c>
       <c r="E810" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09216</t>
+          <t>NATCON-2026-09217</t>
         </is>
       </c>
       <c r="F810" s="10" t="inlineStr">
@@ -35382,7 +35382,7 @@
       </c>
       <c r="E811" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09292</t>
+          <t>NATCON-2026-09296</t>
         </is>
       </c>
       <c r="F811" s="10" t="inlineStr">
@@ -35420,7 +35420,7 @@
       </c>
       <c r="E812" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09485</t>
+          <t>NATCON-2026-09492</t>
         </is>
       </c>
       <c r="F812" s="10" t="inlineStr">
@@ -35458,7 +35458,7 @@
       </c>
       <c r="E813" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09349</t>
+          <t>NATCON-2026-09353</t>
         </is>
       </c>
       <c r="F813" s="10" t="inlineStr">
@@ -35496,7 +35496,7 @@
       </c>
       <c r="E814" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09263</t>
+          <t>NATCON-2026-09265</t>
         </is>
       </c>
       <c r="F814" s="10" t="inlineStr">
@@ -35534,7 +35534,7 @@
       </c>
       <c r="E815" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09574</t>
+          <t>NATCON-2026-09581</t>
         </is>
       </c>
       <c r="F815" s="10" t="inlineStr">
@@ -35572,7 +35572,7 @@
       </c>
       <c r="E816" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09825</t>
+          <t>NATCON-2026-09833</t>
         </is>
       </c>
       <c r="F816" s="10" t="inlineStr">
@@ -35648,7 +35648,7 @@
       </c>
       <c r="E818" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09372</t>
+          <t>NATCON-2026-09376</t>
         </is>
       </c>
       <c r="F818" s="10" t="inlineStr">
@@ -35686,7 +35686,7 @@
       </c>
       <c r="E819" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09104</t>
+          <t>NATCON-2026-09105</t>
         </is>
       </c>
       <c r="F819" s="10" t="inlineStr">
@@ -35724,7 +35724,7 @@
       </c>
       <c r="E820" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09519</t>
+          <t>NATCON-2026-09526</t>
         </is>
       </c>
       <c r="F820" s="10" t="inlineStr">
@@ -35762,7 +35762,7 @@
       </c>
       <c r="E821" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09076</t>
+          <t>NATCON-2026-09077</t>
         </is>
       </c>
       <c r="F821" s="10" t="inlineStr">
@@ -35804,7 +35804,7 @@
       </c>
       <c r="E822" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09137</t>
+          <t>NATCON-2026-09138</t>
         </is>
       </c>
       <c r="F822" s="10" t="inlineStr">
@@ -35846,7 +35846,7 @@
       </c>
       <c r="E823" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09360</t>
+          <t>NATCON-2026-09364</t>
         </is>
       </c>
       <c r="F823" s="10" t="inlineStr">
@@ -35884,7 +35884,7 @@
       </c>
       <c r="E824" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09329</t>
+          <t>NATCON-2026-09333</t>
         </is>
       </c>
       <c r="F824" s="10" t="inlineStr">
@@ -35926,7 +35926,7 @@
       </c>
       <c r="E825" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09289</t>
+          <t>NATCON-2026-09293</t>
         </is>
       </c>
       <c r="F825" s="10" t="inlineStr">
@@ -35968,7 +35968,7 @@
       </c>
       <c r="E826" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09807</t>
+          <t>NATCON-2026-09815</t>
         </is>
       </c>
       <c r="F826" s="10" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="E827" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09720</t>
+          <t>NATCON-2026-09727</t>
         </is>
       </c>
       <c r="F827" s="10" t="inlineStr">
@@ -36052,7 +36052,7 @@
       </c>
       <c r="E828" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09504</t>
+          <t>NATCON-2026-09511</t>
         </is>
       </c>
       <c r="F828" s="10" t="inlineStr">
@@ -36136,7 +36136,7 @@
       </c>
       <c r="E830" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09498</t>
+          <t>NATCON-2026-09505</t>
         </is>
       </c>
       <c r="F830" s="10" t="inlineStr">
@@ -36178,7 +36178,7 @@
       </c>
       <c r="E831" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09221</t>
+          <t>NATCON-2026-09222</t>
         </is>
       </c>
       <c r="F831" s="10" t="inlineStr">
@@ -36258,7 +36258,7 @@
       </c>
       <c r="E833" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09065</t>
+          <t>NATCON-2026-09066</t>
         </is>
       </c>
       <c r="F833" s="10" t="inlineStr">
@@ -36300,7 +36300,7 @@
       </c>
       <c r="E834" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09348</t>
+          <t>NATCON-2026-09352</t>
         </is>
       </c>
       <c r="F834" s="10" t="inlineStr">
@@ -36342,7 +36342,7 @@
       </c>
       <c r="E835" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09730</t>
+          <t>NATCON-2026-09737</t>
         </is>
       </c>
       <c r="F835" s="10" t="inlineStr">
@@ -36384,7 +36384,7 @@
       </c>
       <c r="E836" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09352</t>
+          <t>NATCON-2026-09356</t>
         </is>
       </c>
       <c r="F836" s="10" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="E837" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09843</t>
+          <t>NATCON-2026-09852</t>
         </is>
       </c>
       <c r="F837" s="10" t="inlineStr">
@@ -36464,7 +36464,7 @@
       </c>
       <c r="E838" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09084</t>
+          <t>NATCON-2026-09085</t>
         </is>
       </c>
       <c r="F838" s="10" t="inlineStr">
@@ -36506,7 +36506,7 @@
       </c>
       <c r="E839" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09393</t>
+          <t>NATCON-2026-09399</t>
         </is>
       </c>
       <c r="F839" s="10" t="inlineStr">
@@ -36544,7 +36544,7 @@
       </c>
       <c r="E840" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09291</t>
+          <t>NATCON-2026-09295</t>
         </is>
       </c>
       <c r="F840" s="10" t="inlineStr">
@@ -36586,7 +36586,7 @@
       </c>
       <c r="E841" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09494</t>
+          <t>NATCON-2026-09501</t>
         </is>
       </c>
       <c r="F841" s="10" t="inlineStr">
@@ -36628,7 +36628,7 @@
       </c>
       <c r="E842" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09702</t>
+          <t>NATCON-2026-09709</t>
         </is>
       </c>
       <c r="F842" s="10" t="inlineStr">
@@ -36670,7 +36670,7 @@
       </c>
       <c r="E843" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09528</t>
+          <t>NATCON-2026-09535</t>
         </is>
       </c>
       <c r="F843" s="10" t="inlineStr">
@@ -36712,7 +36712,7 @@
       </c>
       <c r="E844" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09479</t>
+          <t>NATCON-2026-09486</t>
         </is>
       </c>
       <c r="F844" s="10" t="inlineStr">
@@ -36754,7 +36754,7 @@
       </c>
       <c r="E845" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09399</t>
+          <t>NATCON-2026-09405</t>
         </is>
       </c>
       <c r="F845" s="10" t="inlineStr">
@@ -36796,7 +36796,7 @@
       </c>
       <c r="E846" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09328</t>
+          <t>NATCON-2026-09332</t>
         </is>
       </c>
       <c r="F846" s="10" t="inlineStr">
@@ -36838,7 +36838,7 @@
       </c>
       <c r="E847" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09423</t>
+          <t>NATCON-2026-09429</t>
         </is>
       </c>
       <c r="F847" s="10" t="inlineStr">
@@ -36876,7 +36876,7 @@
       </c>
       <c r="E848" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09531</t>
+          <t>NATCON-2026-09538</t>
         </is>
       </c>
       <c r="F848" s="10" t="inlineStr">
@@ -36914,7 +36914,7 @@
       </c>
       <c r="E849" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09219</t>
+          <t>NATCON-2026-09220</t>
         </is>
       </c>
       <c r="F849" s="10" t="inlineStr">
@@ -36936,7 +36936,7 @@
     <row r="850">
       <c r="A850" s="9" t="inlineStr">
         <is>
-          <t>Eugene Sebastian Adiwena</t>
+          <t>Audrey Pradhita</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -36944,29 +36944,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C850" s="9" t="inlineStr">
-        <is>
-          <t>Kantor Hukum Olga K Santoso</t>
-        </is>
-      </c>
+      <c r="C850" s="9" t="inlineStr"/>
       <c r="D850" s="9" t="inlineStr">
         <is>
-          <t>22317-24E2FC461</t>
+          <t>20780-25863F390</t>
         </is>
       </c>
       <c r="E850" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09778</t>
+          <t>NATCON-2026-09777</t>
         </is>
       </c>
       <c r="F850" s="10" t="inlineStr">
         <is>
-          <t>olgaksantoso@cbn.net.id</t>
+          <t>audrey.pradhita@vardhana.id</t>
         </is>
       </c>
       <c r="G850" s="10" t="inlineStr">
         <is>
-          <t>eugene</t>
+          <t>audrey</t>
         </is>
       </c>
       <c r="H850" s="11" t="inlineStr">
@@ -36978,7 +36974,7 @@
     <row r="851">
       <c r="A851" s="9" t="inlineStr">
         <is>
-          <t>Fadillah satria gama</t>
+          <t>Bingar Egidius Situmorang</t>
         </is>
       </c>
       <c r="B851" s="9" t="inlineStr">
@@ -36989,22 +36985,22 @@
       <c r="C851" s="9" t="inlineStr"/>
       <c r="D851" s="9" t="inlineStr">
         <is>
-          <t>22317-252E9BB33</t>
+          <t>20780-25863D140</t>
         </is>
       </c>
       <c r="E851" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09056</t>
+          <t>NATCON-2026-09061</t>
         </is>
       </c>
       <c r="F851" s="10" t="inlineStr">
         <is>
-          <t>fadilprojectkopi@gmail.com</t>
+          <t>egi.situmorang@mustika-ratu.co.id</t>
         </is>
       </c>
       <c r="G851" s="10" t="inlineStr">
         <is>
-          <t>fadillah</t>
+          <t>bingar</t>
         </is>
       </c>
       <c r="H851" s="11" t="inlineStr">
@@ -37016,7 +37012,7 @@
     <row r="852">
       <c r="A852" s="9" t="inlineStr">
         <is>
-          <t>Hendry Oei</t>
+          <t>Dayang Melati</t>
         </is>
       </c>
       <c r="B852" s="9" t="inlineStr">
@@ -37027,22 +37023,22 @@
       <c r="C852" s="9" t="inlineStr"/>
       <c r="D852" s="9" t="inlineStr">
         <is>
-          <t>22317-252E9BF49</t>
+          <t>20780-258647159</t>
         </is>
       </c>
       <c r="E852" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09502</t>
+          <t>NATCON-2026-09435</t>
         </is>
       </c>
       <c r="F852" s="10" t="inlineStr">
         <is>
-          <t>contact@edenstudio.mov</t>
+          <t>dayang.dynamic@gmail.com</t>
         </is>
       </c>
       <c r="G852" s="10" t="inlineStr">
         <is>
-          <t>hendry</t>
+          <t>dayang</t>
         </is>
       </c>
       <c r="H852" s="11" t="inlineStr">
@@ -37054,7 +37050,7 @@
     <row r="853">
       <c r="A853" s="9" t="inlineStr">
         <is>
-          <t>Henri winata</t>
+          <t>Dewi Irma Kusvianty</t>
         </is>
       </c>
       <c r="B853" s="9" t="inlineStr">
@@ -37065,22 +37061,22 @@
       <c r="C853" s="9" t="inlineStr"/>
       <c r="D853" s="9" t="inlineStr">
         <is>
-          <t>22317-2526C5C61</t>
+          <t>20780-25863E572</t>
         </is>
       </c>
       <c r="E853" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09695</t>
+          <t>NATCON-2026-09252</t>
         </is>
       </c>
       <c r="F853" s="10" t="inlineStr">
         <is>
-          <t>jessicatasrifyie@gmail.com</t>
+          <t>dewi.irma@gmail.com</t>
         </is>
       </c>
       <c r="G853" s="10" t="inlineStr">
         <is>
-          <t>henri</t>
+          <t>dewi</t>
         </is>
       </c>
       <c r="H853" s="11" t="inlineStr">
@@ -37092,7 +37088,7 @@
     <row r="854">
       <c r="A854" s="9" t="inlineStr">
         <is>
-          <t>MING TAI TSAI</t>
+          <t>Eugene Sebastian Adiwena</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -37100,25 +37096,29 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C854" s="9" t="inlineStr"/>
+      <c r="C854" s="9" t="inlineStr">
+        <is>
+          <t>Kantor Hukum Olga K Santoso</t>
+        </is>
+      </c>
       <c r="D854" s="9" t="inlineStr">
         <is>
-          <t>16796-253F51E12</t>
+          <t>22317-24E2FC461</t>
         </is>
       </c>
       <c r="E854" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09284</t>
+          <t>NATCON-2026-09786</t>
         </is>
       </c>
       <c r="F854" s="10" t="inlineStr">
         <is>
-          <t>unv69666851@gmail.com</t>
+          <t>olgaksantoso@cbn.net.id</t>
         </is>
       </c>
       <c r="G854" s="10" t="inlineStr">
         <is>
-          <t>ming</t>
+          <t>eugene</t>
         </is>
       </c>
       <c r="H854" s="11" t="inlineStr">
@@ -37130,7 +37130,7 @@
     <row r="855">
       <c r="A855" s="9" t="inlineStr">
         <is>
-          <t>Meta Melvina</t>
+          <t>Fadillah satria gama</t>
         </is>
       </c>
       <c r="B855" s="9" t="inlineStr">
@@ -37141,22 +37141,22 @@
       <c r="C855" s="9" t="inlineStr"/>
       <c r="D855" s="9" t="inlineStr">
         <is>
-          <t>22317-252E9BC80</t>
+          <t>22317-252E9BB33</t>
         </is>
       </c>
       <c r="E855" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09060</t>
+          <t>NATCON-2026-09056</t>
         </is>
       </c>
       <c r="F855" s="10" t="inlineStr">
         <is>
-          <t>drgiselameta31@yahoo.com</t>
+          <t>fadilprojectkopi@gmail.com</t>
         </is>
       </c>
       <c r="G855" s="10" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>fadillah</t>
         </is>
       </c>
       <c r="H855" s="11" t="inlineStr">
@@ -37168,7 +37168,7 @@
     <row r="856">
       <c r="A856" s="9" t="inlineStr">
         <is>
-          <t>Muhammad Rizky</t>
+          <t>Fenny Octavia</t>
         </is>
       </c>
       <c r="B856" s="9" t="inlineStr">
@@ -37176,29 +37176,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C856" s="9" t="inlineStr">
-        <is>
-          <t>PT Zona Kreatif Indonesia</t>
-        </is>
-      </c>
+      <c r="C856" s="9" t="inlineStr"/>
       <c r="D856" s="9" t="inlineStr">
         <is>
-          <t>171AF-23D496182</t>
+          <t>20780-25863A496</t>
         </is>
       </c>
       <c r="E856" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09589</t>
+          <t>NATCON-2026-09276</t>
         </is>
       </c>
       <c r="F856" s="10" t="inlineStr">
         <is>
-          <t>rizky@zonakreatif.id</t>
+          <t>admin@knfo.co.id</t>
         </is>
       </c>
       <c r="G856" s="10" t="inlineStr">
         <is>
-          <t>muhammad</t>
+          <t>fenny</t>
         </is>
       </c>
       <c r="H856" s="11" t="inlineStr">
@@ -37210,7 +37206,7 @@
     <row r="857">
       <c r="A857" s="9" t="inlineStr">
         <is>
-          <t>Robby Arief Sumarko</t>
+          <t>Hendry Oei</t>
         </is>
       </c>
       <c r="B857" s="9" t="inlineStr">
@@ -37221,22 +37217,22 @@
       <c r="C857" s="9" t="inlineStr"/>
       <c r="D857" s="9" t="inlineStr">
         <is>
-          <t>22317-252B90F51</t>
+          <t>22317-252E9BF49</t>
         </is>
       </c>
       <c r="E857" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09227</t>
+          <t>NATCON-2026-09509</t>
         </is>
       </c>
       <c r="F857" s="10" t="inlineStr">
         <is>
-          <t>justine.ossel@gmail.com</t>
+          <t>contact@edenstudio.mov</t>
         </is>
       </c>
       <c r="G857" s="10" t="inlineStr">
         <is>
-          <t>robby</t>
+          <t>hendry</t>
         </is>
       </c>
       <c r="H857" s="11" t="inlineStr">
@@ -37248,7 +37244,7 @@
     <row r="858">
       <c r="A858" s="9" t="inlineStr">
         <is>
-          <t>Stephen Soo</t>
+          <t>Henri winata</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -37259,22 +37255,22 @@
       <c r="C858" s="9" t="inlineStr"/>
       <c r="D858" s="9" t="inlineStr">
         <is>
-          <t>20781-254877E83</t>
+          <t>22317-2526C5C61</t>
         </is>
       </c>
       <c r="E858" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09309</t>
+          <t>NATCON-2026-09702</t>
         </is>
       </c>
       <c r="F858" s="10" t="inlineStr">
         <is>
-          <t>stephen@ecosil.com.my</t>
+          <t>jessicatasrifyie@gmail.com</t>
         </is>
       </c>
       <c r="G858" s="10" t="inlineStr">
         <is>
-          <t>stephen</t>
+          <t>henri</t>
         </is>
       </c>
       <c r="H858" s="11" t="inlineStr">
@@ -37286,7 +37282,7 @@
     <row r="859">
       <c r="A859" s="9" t="inlineStr">
         <is>
-          <t>Tiansong Shi</t>
+          <t>Jovian Alvin</t>
         </is>
       </c>
       <c r="B859" s="9" t="inlineStr">
@@ -37297,32 +37293,416 @@
       <c r="C859" s="9" t="inlineStr"/>
       <c r="D859" s="9" t="inlineStr">
         <is>
+          <t>20780-25864C571</t>
+        </is>
+      </c>
+      <c r="E859" s="9" t="inlineStr">
+        <is>
+          <t>NATCON-2026-09388</t>
+        </is>
+      </c>
+      <c r="F859" s="10" t="inlineStr">
+        <is>
+          <t>jovian@fortu.co.id</t>
+        </is>
+      </c>
+      <c r="G859" s="10" t="inlineStr">
+        <is>
+          <t>jovian</t>
+        </is>
+      </c>
+      <c r="H859" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="9" t="inlineStr">
+        <is>
+          <t>MING TAI TSAI</t>
+        </is>
+      </c>
+      <c r="B860" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C860" s="9" t="inlineStr"/>
+      <c r="D860" s="9" t="inlineStr">
+        <is>
+          <t>16796-253F51E12</t>
+        </is>
+      </c>
+      <c r="E860" s="9" t="inlineStr">
+        <is>
+          <t>NATCON-2026-09287</t>
+        </is>
+      </c>
+      <c r="F860" s="10" t="inlineStr">
+        <is>
+          <t>unv69666851@gmail.com</t>
+        </is>
+      </c>
+      <c r="G860" s="10" t="inlineStr">
+        <is>
+          <t>ming</t>
+        </is>
+      </c>
+      <c r="H860" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="9" t="inlineStr">
+        <is>
+          <t>Meta Melvina</t>
+        </is>
+      </c>
+      <c r="B861" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C861" s="9" t="inlineStr"/>
+      <c r="D861" s="9" t="inlineStr">
+        <is>
+          <t>22317-252E9BC80</t>
+        </is>
+      </c>
+      <c r="E861" s="9" t="inlineStr">
+        <is>
+          <t>NATCON-2026-09060</t>
+        </is>
+      </c>
+      <c r="F861" s="10" t="inlineStr">
+        <is>
+          <t>drgiselameta31@yahoo.com</t>
+        </is>
+      </c>
+      <c r="G861" s="10" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="H861" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="9" t="inlineStr">
+        <is>
+          <t>Muhammad Rizky</t>
+        </is>
+      </c>
+      <c r="B862" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C862" s="9" t="inlineStr">
+        <is>
+          <t>PT Zona Kreatif Indonesia</t>
+        </is>
+      </c>
+      <c r="D862" s="9" t="inlineStr">
+        <is>
+          <t>171AF-23D496182</t>
+        </is>
+      </c>
+      <c r="E862" s="9" t="inlineStr">
+        <is>
+          <t>NATCON-2026-09596</t>
+        </is>
+      </c>
+      <c r="F862" s="10" t="inlineStr">
+        <is>
+          <t>rizky@zonakreatif.id</t>
+        </is>
+      </c>
+      <c r="G862" s="10" t="inlineStr">
+        <is>
+          <t>muhammad</t>
+        </is>
+      </c>
+      <c r="H862" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="9" t="inlineStr">
+        <is>
+          <t>Robby Arief Sumarko</t>
+        </is>
+      </c>
+      <c r="B863" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C863" s="9" t="inlineStr"/>
+      <c r="D863" s="9" t="inlineStr">
+        <is>
+          <t>22317-252B90F51</t>
+        </is>
+      </c>
+      <c r="E863" s="9" t="inlineStr">
+        <is>
+          <t>NATCON-2026-09228</t>
+        </is>
+      </c>
+      <c r="F863" s="10" t="inlineStr">
+        <is>
+          <t>justine.ossel@gmail.com</t>
+        </is>
+      </c>
+      <c r="G863" s="10" t="inlineStr">
+        <is>
+          <t>robby</t>
+        </is>
+      </c>
+      <c r="H863" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="9" t="inlineStr">
+        <is>
+          <t>Stefanus Nicholas Gosaria</t>
+        </is>
+      </c>
+      <c r="B864" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C864" s="9" t="inlineStr"/>
+      <c r="D864" s="9" t="inlineStr">
+        <is>
+          <t>20780-25864FF57</t>
+        </is>
+      </c>
+      <c r="E864" s="9" t="inlineStr">
+        <is>
+          <t>NATCON-2026-09835</t>
+        </is>
+      </c>
+      <c r="F864" s="10" t="inlineStr">
+        <is>
+          <t>nicholasgosaria@gmail.com</t>
+        </is>
+      </c>
+      <c r="G864" s="10" t="inlineStr">
+        <is>
+          <t>stefanus</t>
+        </is>
+      </c>
+      <c r="H864" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="9" t="inlineStr">
+        <is>
+          <t>Stephen Soo</t>
+        </is>
+      </c>
+      <c r="B865" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C865" s="9" t="inlineStr"/>
+      <c r="D865" s="9" t="inlineStr">
+        <is>
+          <t>20781-254877E83</t>
+        </is>
+      </c>
+      <c r="E865" s="9" t="inlineStr">
+        <is>
+          <t>NATCON-2026-09313</t>
+        </is>
+      </c>
+      <c r="F865" s="10" t="inlineStr">
+        <is>
+          <t>stephen@ecosil.com.my</t>
+        </is>
+      </c>
+      <c r="G865" s="10" t="inlineStr">
+        <is>
+          <t>stephen</t>
+        </is>
+      </c>
+      <c r="H865" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="9" t="inlineStr">
+        <is>
+          <t>Tiansong Shi</t>
+        </is>
+      </c>
+      <c r="B866" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C866" s="9" t="inlineStr"/>
+      <c r="D866" s="9" t="inlineStr">
+        <is>
           <t>20781-2545B9380</t>
         </is>
       </c>
-      <c r="E859" s="9" t="inlineStr">
-        <is>
-          <t>NATCON-2026-09693</t>
-        </is>
-      </c>
-      <c r="F859" s="10" t="inlineStr">
+      <c r="E866" s="9" t="inlineStr">
+        <is>
+          <t>NATCON-2026-09700</t>
+        </is>
+      </c>
+      <c r="F866" s="10" t="inlineStr">
         <is>
           <t>275435943@qq.com</t>
         </is>
       </c>
-      <c r="G859" s="10" t="inlineStr">
+      <c r="G866" s="10" t="inlineStr">
         <is>
           <t>tiansong</t>
         </is>
       </c>
-      <c r="H859" s="11" t="inlineStr">
+      <c r="H866" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="9" t="inlineStr">
+        <is>
+          <t>Vera Vania</t>
+        </is>
+      </c>
+      <c r="B867" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C867" s="9" t="inlineStr"/>
+      <c r="D867" s="9" t="inlineStr">
+        <is>
+          <t>20780-25864B236</t>
+        </is>
+      </c>
+      <c r="E867" s="9" t="inlineStr">
+        <is>
+          <t>NATCON-2026-09398</t>
+        </is>
+      </c>
+      <c r="F867" s="10" t="inlineStr">
+        <is>
+          <t>veravania.mrt@gmail.com</t>
+        </is>
+      </c>
+      <c r="G867" s="10" t="inlineStr">
+        <is>
+          <t>vera</t>
+        </is>
+      </c>
+      <c r="H867" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="9" t="inlineStr">
+        <is>
+          <t>Yola Istianty Marga L</t>
+        </is>
+      </c>
+      <c r="B868" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C868" s="9" t="inlineStr"/>
+      <c r="D868" s="9" t="inlineStr">
+        <is>
+          <t>20780-25864ED22</t>
+        </is>
+      </c>
+      <c r="E868" s="9" t="inlineStr">
+        <is>
+          <t>NATCON-2026-09858</t>
+        </is>
+      </c>
+      <c r="F868" s="10" t="inlineStr">
+        <is>
+          <t>yola@pt-sml.com</t>
+        </is>
+      </c>
+      <c r="G868" s="10" t="inlineStr">
+        <is>
+          <t>yola</t>
+        </is>
+      </c>
+      <c r="H868" s="11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="9" t="inlineStr">
+        <is>
+          <t>Yosua Christian Setiawan</t>
+        </is>
+      </c>
+      <c r="B869" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C869" s="9" t="inlineStr"/>
+      <c r="D869" s="9" t="inlineStr">
+        <is>
+          <t>20780-25863C052</t>
+        </is>
+      </c>
+      <c r="E869" s="9" t="inlineStr">
+        <is>
+          <t>NATCON-2026-09288</t>
+        </is>
+      </c>
+      <c r="F869" s="10" t="inlineStr">
+        <is>
+          <t>contact@ygnpartners.com</t>
+        </is>
+      </c>
+      <c r="G869" s="10" t="inlineStr">
+        <is>
+          <t>yosua</t>
+        </is>
+      </c>
+      <c r="H869" s="11" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H859"/>
+  <autoFilter ref="A3:H869"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/kredensial/username-password-awal-natcon2026.xlsx
+++ b/docs/kredensial/username-password-awal-natcon2026.xlsx
@@ -106,8 +106,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -516,66 +516,75 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>PASSWORD AWALNYA SATU UNTUK SEMUA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>natcon2026 — peserta, booth, sponsor, panitia, semuanya. Cukup satu kalimat untuk dijelaskan di meja registrasi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Wajib ganti</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Password itu hanya membuka pintu SEKALI. Saat login pertama, aplikasi meminta setiap orang membuat password sendiri sebelum bisa memakai fitur apa pun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>Isi</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>36 akun booth/sponsor + 866 akun peserta. Semua diverifikasi satu per satu ke API: 902 dari 902 berhasil login.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Aturan booth</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Login booth-&lt;kode&gt;@natcon.id — password awal: nama perusahaan + kode booth, huruf kecil, hanya huruf &amp; angka. WIT.ID di A14 → booth-a14@natcon.id / witida14.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Aturan peserta</t>
-        </is>
-      </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Login: email yang didaftarkan — password awal: nama chapter + nama depan, huruf kecil tanpa spasi. Chapter Heritage, Abraham Sebastian → heritageabraham. Peserta tanpa chapter (kolom '—') memakai nama depan saja.</t>
+          <t>36 akun booth/sponsor + 866 akun peserta. Yang membedakan tiap baris hanya alamat login-nya. Semua diverifikasi satu per satu ke API: 902 dari 902 berhasil.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="n"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Login booth</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>booth-&lt;kode booth&gt;@natcon.id — WIT.ID di A14 → booth-a14@natcon.id</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SEMUANYA HURUF KECIL</t>
+          <t>Login peserta</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Email maupun password. Kalau keyboard HP mengapitalkan huruf pertama, aplikasi tetap menerimanya selama akun masih memakai password awal ini.</t>
+          <t>email yang didaftarkan saat beli tiket</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Wajib ganti</t>
+          <t>Semuanya huruf kecil</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Password di sini hanya membuka pintu SEKALI. Saat login pertama, aplikasi meminta pengguna membuat password sendiri sebelum bisa memakai fitur apa pun.</t>
+          <t>Email maupun password. Kalau keyboard HP mengapitalkan huruf pertama, aplikasi tetap menerimanya selama akun masih memakai password awal.</t>
         </is>
       </c>
     </row>
@@ -583,26 +592,26 @@
       <c r="B11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Berkas ini ada di repo publik</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Atas keputusan panitia. Password di bawah juga bisa diturunkan dari data yang memang sudah ada di repo (migrasi 0037/0038), jadi ini bukan paparan baru — tapi perlakukan tetap sebagai daftar kredensial.</t>
+          <t>Atas keputusan panitia. Dengan satu password untuk semua, yang perlu dijaga justru daftar EMAIL-nya: siapa pun yang tahu password ini bisa masuk sebagai peserta yang belum pernah login. Dorong semua orang login sedini mungkin.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Kalau bocor sebelum acara</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Kalau perlu dibatalkan</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Ganti dengan menjalankan ulang generator seed, atau reset per akun dari panel admin.</t>
+          <t>Ganti SEED_PASSWORD lalu restart API — semua akun yang belum login ikut berubah.</t>
         </is>
       </c>
     </row>
@@ -610,45 +619,26 @@
       <c r="B14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Cara sosialisasi</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Urutan</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Booth: cetak sheet 01, potong per baris, serahkan saat briefing.</t>
+          <t>Yang berkaitan dengan WIT ada di urutan paling atas pada kedua sheet.</t>
         </is>
       </c>
     </row>
     <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Dibuat dari</t>
+        </is>
+      </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Peserta: kirim per orang (WA/email masing-masing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Urutan</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Yang berkaitan dengan WIT ada di urutan paling atas pada kedua sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Dibuat dari</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Seed resmi dari sheet panitia revisi 28 Agustus (migrasi 0037–0038), dibuat 29 Agustus 2026. Kalau sheet peserta/booth berubah lagi, berkas ini harus dibuat ulang.</t>
+          <t>Seed resmi sheet panitia revisi 28 Agustus, dibuat 29 Agustus 2026.</t>
         </is>
       </c>
     </row>
@@ -670,7 +660,7 @@
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -684,7 +674,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>36 akun · WIT.ID dan sponsor di urutan atas · semua sudah diuji login</t>
+          <t>36 akun · semua password awal sama: natcon2026</t>
         </is>
       </c>
     </row>
@@ -743,7 +733,7 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>witida14</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
@@ -775,7 +765,7 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>biomedikab1</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -807,7 +797,7 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>parahitadiagnosticcenterb2</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F6" s="11" t="inlineStr">
@@ -839,7 +829,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>prosnapb3</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -871,7 +861,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>troyalmedicalinkpharmalabptaromabathiindonesiac1</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F8" s="11" t="inlineStr">
@@ -903,7 +893,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>sscxinternationala1</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -935,7 +925,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>pttanameramitrasentosaa10</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -967,7 +957,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>ptforbisasiaindonesiaa15</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
@@ -999,7 +989,7 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>cvwirabuanasaktia16</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
@@ -1031,7 +1021,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>onetaxcmpteltda17</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1063,7 +1053,7 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>grasiacarea18a20</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -1095,7 +1085,7 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>sinarprintingptsinarmediakreasia19</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1127,7 +1117,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>ptorientallogisticsindonesiaa2</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -1159,7 +1149,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>paperida22</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
@@ -1191,7 +1181,7 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>inharmonypreventiveclinica23</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -1223,7 +1213,7 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>ptdocumentacorporatechnologya24</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -1255,7 +1245,7 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>lisannaonlineaccountingtaxconsultanta25</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
@@ -1287,7 +1277,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>ptzonakreatifindonesiaa27</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -1319,7 +1309,7 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>ptvenamona3</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
@@ -1351,7 +1341,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>icubeinvoicekepta30</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -1383,7 +1373,7 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>ptnoritaflexindoa31</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
@@ -1415,7 +1405,7 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>alpswillspteltda32</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -1447,7 +1437,7 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>bookingtogoa33</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -1479,7 +1469,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>paksmm2hsdnbhda34</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -1511,7 +1501,7 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>cvtrianabintanga36</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
@@ -1543,7 +1533,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>lekapttissorindonesiaa37</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -1575,7 +1565,7 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>cvitprosolutionsa38</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
@@ -1607,7 +1597,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>toffeedeva4</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -1639,7 +1629,7 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>pttsnariestamajayaa42</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -1671,7 +1661,7 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>ptcreativemediaindonesiaa43</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -1703,7 +1693,7 @@
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>ketapangindahhotela44</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
@@ -1735,7 +1725,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>ptbelanjasegarindonesiaa46</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -1767,7 +1757,7 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>alphaleadersa47a48</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
@@ -1799,7 +1789,7 @@
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>doxadigitala5</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -1831,7 +1821,7 @@
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>ptnaturalspirita6</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -1863,7 +1853,7 @@
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>ptgunanusaeramandiritbka9</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -1893,7 +1883,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1907,7 +1897,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>866 akun · WIT di urutan atas · semua sudah diuji login</t>
+          <t>866 akun · semua password awal sama: natcon2026</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1976,7 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>growilham</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
@@ -2028,7 +2018,7 @@
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>riseirfan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -2070,7 +2060,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>synergydimas</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -2112,7 +2102,7 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>achieversabram</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -2154,7 +2144,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>achieversalbert</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -2196,7 +2186,7 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>achieversendi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -2238,7 +2228,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>achieversfrans</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -2280,7 +2270,7 @@
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>achieversika</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H11" s="11" t="inlineStr">
@@ -2322,7 +2312,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>achieversjoni</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -2364,7 +2354,7 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>achieverskalis</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -2406,7 +2396,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>achieverslidia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -2448,7 +2438,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>achieversmaisari</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -2490,7 +2480,7 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>achieversmarissa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -2532,7 +2522,7 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>achieversmuliady</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -2574,7 +2564,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>achieverspata</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
@@ -2616,7 +2606,7 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>achieversriawan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -2658,7 +2648,7 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>achieversshafira</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
@@ -2700,7 +2690,7 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>achieversshella</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -2738,7 +2728,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>achieverstheresia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
@@ -2776,7 +2766,7 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>achieversyetty</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -2818,7 +2808,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>achieversyosep</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
@@ -2860,7 +2850,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>achieversaldo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -2902,7 +2892,7 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>altitudedarwin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
@@ -2944,7 +2934,7 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>altitudedian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -2986,7 +2976,7 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>altitudedipa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
@@ -3028,7 +3018,7 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>altitudeelizabeth</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
@@ -3070,7 +3060,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>altitudefanny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -3112,7 +3102,7 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>altitudegevin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -3154,7 +3144,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>altitudejeane</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
@@ -3192,7 +3182,7 @@
       </c>
       <c r="G33" s="10" t="inlineStr">
         <is>
-          <t>altitudejovi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -3234,7 +3224,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>altitudejovita</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -3276,7 +3266,7 @@
       </c>
       <c r="G35" s="10" t="inlineStr">
         <is>
-          <t>altitudeliana</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -3318,7 +3308,7 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>altitudemeilina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -3360,7 +3350,7 @@
       </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>altitudemelissa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -3402,7 +3392,7 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>altitudenerissa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
@@ -3444,7 +3434,7 @@
       </c>
       <c r="G39" s="10" t="inlineStr">
         <is>
-          <t>altitudenicander</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
@@ -3486,7 +3476,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>altituderey</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
@@ -3528,7 +3518,7 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>altitudereynaldo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -3570,7 +3560,7 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>altitudesunardi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
@@ -3612,7 +3602,7 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>altitudetry</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
@@ -3654,7 +3644,7 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>altitudevonny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
@@ -3696,7 +3686,7 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>altitudewilly</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
@@ -3738,7 +3728,7 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>ampangangie</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
@@ -3780,7 +3770,7 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>ampangdennis</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
@@ -3822,7 +3812,7 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>ampangdr.</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -3864,7 +3854,7 @@
       </c>
       <c r="G49" s="10" t="inlineStr">
         <is>
-          <t>ampangnicholas</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
@@ -3906,7 +3896,7 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>amplifyalfawzia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -3948,7 +3938,7 @@
       </c>
       <c r="G51" s="10" t="inlineStr">
         <is>
-          <t>amplifyalvin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
@@ -3990,7 +3980,7 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>amplifyandrina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
@@ -4032,7 +4022,7 @@
       </c>
       <c r="G53" s="10" t="inlineStr">
         <is>
-          <t>amplifyarya</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H53" s="11" t="inlineStr">
@@ -4074,7 +4064,7 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>amplifydarren</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
@@ -4116,7 +4106,7 @@
       </c>
       <c r="G55" s="10" t="inlineStr">
         <is>
-          <t>amplifydarwanto</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
@@ -4143,12 +4133,12 @@
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>171AF-256721E18</t>
+          <t>16797-225230C24</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09728</t>
+          <t>NATCON-2026-09415</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
@@ -4158,7 +4148,7 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>amplifydavid</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
@@ -4185,12 +4175,12 @@
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>171AF-256722064</t>
+          <t>171AF-256721F10</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09547</t>
+          <t>NATCON-2026-09244</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
@@ -4200,7 +4190,7 @@
       </c>
       <c r="G57" s="10" t="inlineStr">
         <is>
-          <t>amplifydavid</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
@@ -4227,12 +4217,12 @@
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>16797-225230C24</t>
+          <t>171AF-256721E18</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09415</t>
+          <t>NATCON-2026-09728</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
@@ -4242,7 +4232,7 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>amplifydavid</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -4269,12 +4259,12 @@
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>171AF-256721F10</t>
+          <t>171AF-256722064</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09244</t>
+          <t>NATCON-2026-09547</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
@@ -4284,7 +4274,7 @@
       </c>
       <c r="G59" s="10" t="inlineStr">
         <is>
-          <t>amplifydavid</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -4322,7 +4312,7 @@
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>amplifydenis</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H60" s="11" t="inlineStr">
@@ -4364,7 +4354,7 @@
       </c>
       <c r="G61" s="10" t="inlineStr">
         <is>
-          <t>amplifydenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
@@ -4406,7 +4396,7 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>amplifydody</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
@@ -4444,7 +4434,7 @@
       </c>
       <c r="G63" s="10" t="inlineStr">
         <is>
-          <t>amplifydyah</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H63" s="11" t="inlineStr">
@@ -4467,12 +4457,12 @@
       <c r="C64" s="9" t="inlineStr"/>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>171AF-256730D43</t>
+          <t>171AF-256730E17</t>
         </is>
       </c>
       <c r="E64" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09281</t>
+          <t>NATCON-2026-09141</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
@@ -4482,7 +4472,7 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>amplifydyah</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
@@ -4505,12 +4495,12 @@
       <c r="C65" s="9" t="inlineStr"/>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>171AF-256730E17</t>
+          <t>171AF-256730D43</t>
         </is>
       </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09141</t>
+          <t>NATCON-2026-09281</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -4520,7 +4510,7 @@
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>amplifydyah</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -4562,7 +4552,7 @@
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>amplifyedwin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
@@ -4604,7 +4594,7 @@
       </c>
       <c r="G67" s="10" t="inlineStr">
         <is>
-          <t>amplifyeka</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H67" s="11" t="inlineStr">
@@ -4646,7 +4636,7 @@
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>amplifyfoni</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
@@ -4688,7 +4678,7 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>amplifyfrenky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
@@ -4730,7 +4720,7 @@
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>amplifyhendrik</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
@@ -4772,7 +4762,7 @@
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>amplifyhendro</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -4814,7 +4804,7 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>amplifyhenri</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H72" s="11" t="inlineStr">
@@ -4856,7 +4846,7 @@
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>amplifyidrus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
@@ -4898,7 +4888,7 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>amplifyinka</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
@@ -4936,7 +4926,7 @@
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>amplifyjacob</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
@@ -4978,7 +4968,7 @@
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>amplifyjantra</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
@@ -5020,7 +5010,7 @@
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>amplifyjason</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
@@ -5062,7 +5052,7 @@
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>amplifyjosshhua</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
@@ -5104,7 +5094,7 @@
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>amplifyjulius</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
@@ -5146,7 +5136,7 @@
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>amplifykarni</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H80" s="11" t="inlineStr">
@@ -5188,7 +5178,7 @@
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>amplifyleny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
@@ -5230,7 +5220,7 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>amplifylina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H82" s="11" t="inlineStr">
@@ -5272,7 +5262,7 @@
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>amplifylukito</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
@@ -5314,7 +5304,7 @@
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>amplifymeiliana</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
@@ -5356,7 +5346,7 @@
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>amplifymicky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
@@ -5398,7 +5388,7 @@
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>amplifymochammad</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
@@ -5440,7 +5430,7 @@
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>amplifyratna</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
@@ -5482,7 +5472,7 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>amplifyria</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H88" s="11" t="inlineStr">
@@ -5524,7 +5514,7 @@
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>amplifyrobby</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
@@ -5566,7 +5556,7 @@
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>amplifyrobertus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
@@ -5608,7 +5598,7 @@
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>amplifyroy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
@@ -5650,7 +5640,7 @@
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>amplifyryan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H92" s="11" t="inlineStr">
@@ -5692,7 +5682,7 @@
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>amplifysoefery</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
@@ -5734,7 +5724,7 @@
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>amplifystefanus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
@@ -5772,7 +5762,7 @@
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>amplifystephanie</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
@@ -5814,7 +5804,7 @@
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>amplifysusanto</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
@@ -5856,7 +5846,7 @@
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>amplifyveronica</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
@@ -5898,7 +5888,7 @@
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>amplifywijaya</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H98" s="11" t="inlineStr">
@@ -5940,7 +5930,7 @@
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>amplifywiyogo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
@@ -5982,7 +5972,7 @@
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>amplifyannatasia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
@@ -6024,7 +6014,7 @@
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>arcadiachai</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
@@ -6066,7 +6056,7 @@
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>arcadiajoanne</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H102" s="11" t="inlineStr">
@@ -6104,7 +6094,7 @@
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>arcadiakc</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H103" s="11" t="inlineStr">
@@ -6146,7 +6136,7 @@
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>arcadiakee</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H104" s="11" t="inlineStr">
@@ -6188,7 +6178,7 @@
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>arcadiatan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H105" s="11" t="inlineStr">
@@ -6230,7 +6220,7 @@
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>arcadiawong</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H106" s="11" t="inlineStr">
@@ -6272,7 +6262,7 @@
       </c>
       <c r="G107" s="10" t="inlineStr">
         <is>
-          <t>bniachieverschery</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr">
@@ -6314,7 +6304,7 @@
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>bniampang,klccregion,malaysiashanmuganathan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
@@ -6356,7 +6346,7 @@
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>bnibalionairejocelyn</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
@@ -6383,12 +6373,12 @@
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>171B0-22D8EA999</t>
+          <t>171B0-22D8EA843</t>
         </is>
       </c>
       <c r="E110" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09813</t>
+          <t>NATCON-2026-09235</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
@@ -6398,7 +6388,7 @@
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>bnichampions(singapore)lancaster</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
@@ -6425,12 +6415,12 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>171B0-22D8EA843</t>
+          <t>171B0-22D8EA999</t>
         </is>
       </c>
       <c r="E111" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09235</t>
+          <t>NATCON-2026-09813</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
@@ -6440,7 +6430,7 @@
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>bnichampions(singapore)lancaster</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
@@ -6482,7 +6472,7 @@
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>bnicherasexploreronlinejason</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
@@ -6524,7 +6514,7 @@
       </c>
       <c r="G113" s="10" t="inlineStr">
         <is>
-          <t>bnimalaysiacherasexploreronlineyong</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
@@ -6566,7 +6556,7 @@
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>bninakshatra,chennainorthregion,indiasubhashini</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr">
@@ -6608,7 +6598,7 @@
       </c>
       <c r="G115" s="10" t="inlineStr">
         <is>
-          <t>bniopulencechermaine</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H115" s="11" t="inlineStr">
@@ -6646,7 +6636,7 @@
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>bniperkasanik</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H116" s="11" t="inlineStr">
@@ -6688,7 +6678,7 @@
       </c>
       <c r="G117" s="10" t="inlineStr">
         <is>
-          <t>bnisouqarabiaastha</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
@@ -6730,7 +6720,7 @@
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>bnisouqarabia(manama,bahrain)nitish</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr">
@@ -6772,7 +6762,7 @@
       </c>
       <c r="G119" s="10" t="inlineStr">
         <is>
-          <t>bniopulencesingaporefrancis</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H119" s="11" t="inlineStr">
@@ -6814,7 +6804,7 @@
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>bagaskaraega</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
@@ -6856,7 +6846,7 @@
       </c>
       <c r="G121" s="10" t="inlineStr">
         <is>
-          <t>balionairearief</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
@@ -6898,7 +6888,7 @@
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>balionairebagus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
@@ -6940,7 +6930,7 @@
       </c>
       <c r="G123" s="10" t="inlineStr">
         <is>
-          <t>balionairebenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
@@ -6978,7 +6968,7 @@
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>balionaireendi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H124" s="11" t="inlineStr">
@@ -7020,7 +7010,7 @@
       </c>
       <c r="G125" s="10" t="inlineStr">
         <is>
-          <t>balionairefelisia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
@@ -7058,7 +7048,7 @@
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>balionairefrida</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H126" s="11" t="inlineStr">
@@ -7100,7 +7090,7 @@
       </c>
       <c r="G127" s="10" t="inlineStr">
         <is>
-          <t>balionairehandian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
@@ -7142,7 +7132,7 @@
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
-          <t>balionairei</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H128" s="11" t="inlineStr">
@@ -7184,7 +7174,7 @@
       </c>
       <c r="G129" s="10" t="inlineStr">
         <is>
-          <t>balionairei</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
@@ -7226,7 +7216,7 @@
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>balionairei</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H130" s="11" t="inlineStr">
@@ -7268,7 +7258,7 @@
       </c>
       <c r="G131" s="10" t="inlineStr">
         <is>
-          <t>balionairejenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
@@ -7310,7 +7300,7 @@
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>balionairejoram</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H132" s="11" t="inlineStr">
@@ -7352,7 +7342,7 @@
       </c>
       <c r="G133" s="10" t="inlineStr">
         <is>
-          <t>balionairekadek</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
@@ -7394,7 +7384,7 @@
       </c>
       <c r="G134" s="10" t="inlineStr">
         <is>
-          <t>balionairemoses</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H134" s="11" t="inlineStr">
@@ -7436,7 +7426,7 @@
       </c>
       <c r="G135" s="10" t="inlineStr">
         <is>
-          <t>balionairemulyadi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
@@ -7478,7 +7468,7 @@
       </c>
       <c r="G136" s="10" t="inlineStr">
         <is>
-          <t>balionairemurdiani</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H136" s="11" t="inlineStr">
@@ -7520,7 +7510,7 @@
       </c>
       <c r="G137" s="10" t="inlineStr">
         <is>
-          <t>balionairepaolo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H137" s="11" t="inlineStr">
@@ -7562,7 +7552,7 @@
       </c>
       <c r="G138" s="10" t="inlineStr">
         <is>
-          <t>balionaireputu</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H138" s="11" t="inlineStr">
@@ -7604,7 +7594,7 @@
       </c>
       <c r="G139" s="10" t="inlineStr">
         <is>
-          <t>balionairerudi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
@@ -7646,7 +7636,7 @@
       </c>
       <c r="G140" s="10" t="inlineStr">
         <is>
-          <t>balionaireyohan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H140" s="11" t="inlineStr">
@@ -7688,7 +7678,7 @@
       </c>
       <c r="G141" s="10" t="inlineStr">
         <is>
-          <t>balionairei</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
@@ -7730,7 +7720,7 @@
       </c>
       <c r="G142" s="10" t="inlineStr">
         <is>
-          <t>balionairemulyadi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H142" s="11" t="inlineStr">
@@ -7772,7 +7762,7 @@
       </c>
       <c r="G143" s="10" t="inlineStr">
         <is>
-          <t>balionaireyoan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
@@ -7814,7 +7804,7 @@
       </c>
       <c r="G144" s="10" t="inlineStr">
         <is>
-          <t>brilliantjialin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H144" s="11" t="inlineStr">
@@ -7856,7 +7846,7 @@
       </c>
       <c r="G145" s="10" t="inlineStr">
         <is>
-          <t>championagnes</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
@@ -7898,7 +7888,7 @@
       </c>
       <c r="G146" s="10" t="inlineStr">
         <is>
-          <t>championalexander</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H146" s="11" t="inlineStr">
@@ -7940,7 +7930,7 @@
       </c>
       <c r="G147" s="10" t="inlineStr">
         <is>
-          <t>championanastasia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
@@ -7982,7 +7972,7 @@
       </c>
       <c r="G148" s="10" t="inlineStr">
         <is>
-          <t>championandryaas</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H148" s="11" t="inlineStr">
@@ -8024,7 +8014,7 @@
       </c>
       <c r="G149" s="10" t="inlineStr">
         <is>
-          <t>championari</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
@@ -8066,7 +8056,7 @@
       </c>
       <c r="G150" s="10" t="inlineStr">
         <is>
-          <t>championbambang</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H150" s="11" t="inlineStr">
@@ -8108,7 +8098,7 @@
       </c>
       <c r="G151" s="10" t="inlineStr">
         <is>
-          <t>championcatherine</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
@@ -8150,7 +8140,7 @@
       </c>
       <c r="G152" s="10" t="inlineStr">
         <is>
-          <t>championedwin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H152" s="11" t="inlineStr">
@@ -8188,7 +8178,7 @@
       </c>
       <c r="G153" s="10" t="inlineStr">
         <is>
-          <t>championedy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H153" s="11" t="inlineStr">
@@ -8226,7 +8216,7 @@
       </c>
       <c r="G154" s="10" t="inlineStr">
         <is>
-          <t>championelisabeth</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">
@@ -8264,7 +8254,7 @@
       </c>
       <c r="G155" s="10" t="inlineStr">
         <is>
-          <t>championgitha</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H155" s="11" t="inlineStr">
@@ -8306,7 +8296,7 @@
       </c>
       <c r="G156" s="10" t="inlineStr">
         <is>
-          <t>championirwan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H156" s="11" t="inlineStr">
@@ -8348,7 +8338,7 @@
       </c>
       <c r="G157" s="10" t="inlineStr">
         <is>
-          <t>championjoshua</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
@@ -8390,7 +8380,7 @@
       </c>
       <c r="G158" s="10" t="inlineStr">
         <is>
-          <t>championkai</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H158" s="11" t="inlineStr">
@@ -8432,7 +8422,7 @@
       </c>
       <c r="G159" s="10" t="inlineStr">
         <is>
-          <t>championm</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
@@ -8474,7 +8464,7 @@
       </c>
       <c r="G160" s="10" t="inlineStr">
         <is>
-          <t>championmohamad</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H160" s="11" t="inlineStr">
@@ -8516,7 +8506,7 @@
       </c>
       <c r="G161" s="10" t="inlineStr">
         <is>
-          <t>championmona</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
@@ -8554,7 +8544,7 @@
       </c>
       <c r="G162" s="10" t="inlineStr">
         <is>
-          <t>championnicholas</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H162" s="11" t="inlineStr">
@@ -8596,7 +8586,7 @@
       </c>
       <c r="G163" s="10" t="inlineStr">
         <is>
-          <t>championristi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
@@ -8634,7 +8624,7 @@
       </c>
       <c r="G164" s="10" t="inlineStr">
         <is>
-          <t>championroby</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H164" s="11" t="inlineStr">
@@ -8676,7 +8666,7 @@
       </c>
       <c r="G165" s="10" t="inlineStr">
         <is>
-          <t>championsylvia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
@@ -8718,7 +8708,7 @@
       </c>
       <c r="G166" s="10" t="inlineStr">
         <is>
-          <t>championtandhy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H166" s="11" t="inlineStr">
@@ -8760,7 +8750,7 @@
       </c>
       <c r="G167" s="10" t="inlineStr">
         <is>
-          <t>championthomas</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
@@ -8802,7 +8792,7 @@
       </c>
       <c r="G168" s="10" t="inlineStr">
         <is>
-          <t>championveronica</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H168" s="11" t="inlineStr">
@@ -8844,7 +8834,7 @@
       </c>
       <c r="G169" s="10" t="inlineStr">
         <is>
-          <t>championveronica</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H169" s="11" t="inlineStr">
@@ -8886,7 +8876,7 @@
       </c>
       <c r="G170" s="10" t="inlineStr">
         <is>
-          <t>championweti</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H170" s="11" t="inlineStr">
@@ -8928,7 +8918,7 @@
       </c>
       <c r="G171" s="10" t="inlineStr">
         <is>
-          <t>championwing</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H171" s="11" t="inlineStr">
@@ -8970,7 +8960,7 @@
       </c>
       <c r="G172" s="10" t="inlineStr">
         <is>
-          <t>championyulianto</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H172" s="11" t="inlineStr">
@@ -9008,7 +8998,7 @@
       </c>
       <c r="G173" s="10" t="inlineStr">
         <is>
-          <t>championyves</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr">
@@ -9035,12 +9025,12 @@
       </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
-          <t>171B0-226C21B27</t>
+          <t>171B0-226C21A67</t>
         </is>
       </c>
       <c r="E174" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09025</t>
+          <t>NATCON-2026-09050</t>
         </is>
       </c>
       <c r="F174" s="10" t="inlineStr">
@@ -9050,7 +9040,7 @@
       </c>
       <c r="G174" s="10" t="inlineStr">
         <is>
-          <t>championseilton</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H174" s="11" t="inlineStr">
@@ -9077,12 +9067,12 @@
       </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
-          <t>171B0-226C21A67</t>
+          <t>171B0-226C21B27</t>
         </is>
       </c>
       <c r="E175" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09050</t>
+          <t>NATCON-2026-09025</t>
         </is>
       </c>
       <c r="F175" s="10" t="inlineStr">
@@ -9092,7 +9082,7 @@
       </c>
       <c r="G175" s="10" t="inlineStr">
         <is>
-          <t>championseilton</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H175" s="11" t="inlineStr">
@@ -9134,7 +9124,7 @@
       </c>
       <c r="G176" s="10" t="inlineStr">
         <is>
-          <t>championshuzaimi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H176" s="11" t="inlineStr">
@@ -9176,7 +9166,7 @@
       </c>
       <c r="G177" s="10" t="inlineStr">
         <is>
-          <t>championsjack</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr">
@@ -9218,7 +9208,7 @@
       </c>
       <c r="G178" s="10" t="inlineStr">
         <is>
-          <t>championsjonathan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H178" s="11" t="inlineStr">
@@ -9260,7 +9250,7 @@
       </c>
       <c r="G179" s="10" t="inlineStr">
         <is>
-          <t>championsroy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H179" s="11" t="inlineStr">
@@ -9302,7 +9292,7 @@
       </c>
       <c r="G180" s="10" t="inlineStr">
         <is>
-          <t>chanpionslorene</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H180" s="11" t="inlineStr">
@@ -9344,7 +9334,7 @@
       </c>
       <c r="G181" s="10" t="inlineStr">
         <is>
-          <t>chaptermagnifychristopher</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H181" s="11" t="inlineStr">
@@ -9386,7 +9376,7 @@
       </c>
       <c r="G182" s="10" t="inlineStr">
         <is>
-          <t>cherasexploreronlineviolet</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H182" s="11" t="inlineStr">
@@ -9428,7 +9418,7 @@
       </c>
       <c r="G183" s="10" t="inlineStr">
         <is>
-          <t>cherasmissiononlinemarina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H183" s="11" t="inlineStr">
@@ -9470,7 +9460,7 @@
       </c>
       <c r="G184" s="10" t="inlineStr">
         <is>
-          <t>cleaningagencydajuan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H184" s="11" t="inlineStr">
@@ -9512,7 +9502,7 @@
       </c>
       <c r="G185" s="10" t="inlineStr">
         <is>
-          <t>dignifycaroline</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H185" s="11" t="inlineStr">
@@ -9554,7 +9544,7 @@
       </c>
       <c r="G186" s="10" t="inlineStr">
         <is>
-          <t>dignifyevan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H186" s="11" t="inlineStr">
@@ -9596,7 +9586,7 @@
       </c>
       <c r="G187" s="10" t="inlineStr">
         <is>
-          <t>dignifyheni</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H187" s="11" t="inlineStr">
@@ -9638,7 +9628,7 @@
       </c>
       <c r="G188" s="10" t="inlineStr">
         <is>
-          <t>dignifyheinrich</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H188" s="11" t="inlineStr">
@@ -9680,7 +9670,7 @@
       </c>
       <c r="G189" s="10" t="inlineStr">
         <is>
-          <t>dignifykayleen</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H189" s="11" t="inlineStr">
@@ -9722,7 +9712,7 @@
       </c>
       <c r="G190" s="10" t="inlineStr">
         <is>
-          <t>dignifykezia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H190" s="11" t="inlineStr">
@@ -9764,7 +9754,7 @@
       </c>
       <c r="G191" s="10" t="inlineStr">
         <is>
-          <t>dignifylidwina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H191" s="11" t="inlineStr">
@@ -9806,7 +9796,7 @@
       </c>
       <c r="G192" s="10" t="inlineStr">
         <is>
-          <t>dignifymarcello</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H192" s="11" t="inlineStr">
@@ -9848,7 +9838,7 @@
       </c>
       <c r="G193" s="10" t="inlineStr">
         <is>
-          <t>dignifymaulida</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H193" s="11" t="inlineStr">
@@ -9890,7 +9880,7 @@
       </c>
       <c r="G194" s="10" t="inlineStr">
         <is>
-          <t>dignifynadya</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H194" s="11" t="inlineStr">
@@ -9932,7 +9922,7 @@
       </c>
       <c r="G195" s="10" t="inlineStr">
         <is>
-          <t>dignifyryan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H195" s="11" t="inlineStr">
@@ -9974,7 +9964,7 @@
       </c>
       <c r="G196" s="10" t="inlineStr">
         <is>
-          <t>dignifyvalerie</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H196" s="11" t="inlineStr">
@@ -10012,7 +10002,7 @@
       </c>
       <c r="G197" s="10" t="inlineStr">
         <is>
-          <t>dongguannavigationjingjing</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H197" s="11" t="inlineStr">
@@ -10050,7 +10040,7 @@
       </c>
       <c r="G198" s="10" t="inlineStr">
         <is>
-          <t>dongguansincere(2024)fangbi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H198" s="11" t="inlineStr">
@@ -10092,7 +10082,7 @@
       </c>
       <c r="G199" s="10" t="inlineStr">
         <is>
-          <t>dynastyaudebert</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H199" s="11" t="inlineStr">
@@ -10134,7 +10124,7 @@
       </c>
       <c r="G200" s="10" t="inlineStr">
         <is>
-          <t>dynastybaskoro</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H200" s="11" t="inlineStr">
@@ -10176,7 +10166,7 @@
       </c>
       <c r="G201" s="10" t="inlineStr">
         <is>
-          <t>dynastybenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H201" s="11" t="inlineStr">
@@ -10218,7 +10208,7 @@
       </c>
       <c r="G202" s="10" t="inlineStr">
         <is>
-          <t>dynastychristopher</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H202" s="11" t="inlineStr">
@@ -10256,7 +10246,7 @@
       </c>
       <c r="G203" s="10" t="inlineStr">
         <is>
-          <t>dynastydewi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H203" s="11" t="inlineStr">
@@ -10298,7 +10288,7 @@
       </c>
       <c r="G204" s="10" t="inlineStr">
         <is>
-          <t>dynastydiana</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H204" s="11" t="inlineStr">
@@ -10340,7 +10330,7 @@
       </c>
       <c r="G205" s="10" t="inlineStr">
         <is>
-          <t>dynastyevi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H205" s="11" t="inlineStr">
@@ -10382,7 +10372,7 @@
       </c>
       <c r="G206" s="10" t="inlineStr">
         <is>
-          <t>dynastygirindra</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H206" s="11" t="inlineStr">
@@ -10420,7 +10410,7 @@
       </c>
       <c r="G207" s="10" t="inlineStr">
         <is>
-          <t>dynastygracy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H207" s="11" t="inlineStr">
@@ -10462,7 +10452,7 @@
       </c>
       <c r="G208" s="10" t="inlineStr">
         <is>
-          <t>dynastyhanson</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H208" s="11" t="inlineStr">
@@ -10504,7 +10494,7 @@
       </c>
       <c r="G209" s="10" t="inlineStr">
         <is>
-          <t>dynastyihsan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H209" s="11" t="inlineStr">
@@ -10546,7 +10536,7 @@
       </c>
       <c r="G210" s="10" t="inlineStr">
         <is>
-          <t>dynastyimeria</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H210" s="11" t="inlineStr">
@@ -10584,7 +10574,7 @@
       </c>
       <c r="G211" s="10" t="inlineStr">
         <is>
-          <t>dynastyivan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H211" s="11" t="inlineStr">
@@ -10626,7 +10616,7 @@
       </c>
       <c r="G212" s="10" t="inlineStr">
         <is>
-          <t>dynastyjeanne</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H212" s="11" t="inlineStr">
@@ -10668,7 +10658,7 @@
       </c>
       <c r="G213" s="10" t="inlineStr">
         <is>
-          <t>dynastyjeanny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H213" s="11" t="inlineStr">
@@ -10710,7 +10700,7 @@
       </c>
       <c r="G214" s="10" t="inlineStr">
         <is>
-          <t>dynastyjeroen</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H214" s="11" t="inlineStr">
@@ -10752,7 +10742,7 @@
       </c>
       <c r="G215" s="10" t="inlineStr">
         <is>
-          <t>dynastyjoerg</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H215" s="11" t="inlineStr">
@@ -10794,7 +10784,7 @@
       </c>
       <c r="G216" s="10" t="inlineStr">
         <is>
-          <t>dynastykamlesh</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H216" s="11" t="inlineStr">
@@ -10836,7 +10826,7 @@
       </c>
       <c r="G217" s="10" t="inlineStr">
         <is>
-          <t>dynastykamna</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H217" s="11" t="inlineStr">
@@ -10878,7 +10868,7 @@
       </c>
       <c r="G218" s="10" t="inlineStr">
         <is>
-          <t>dynastylionel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H218" s="11" t="inlineStr">
@@ -10916,7 +10906,7 @@
       </c>
       <c r="G219" s="10" t="inlineStr">
         <is>
-          <t>dynastymarco</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H219" s="11" t="inlineStr">
@@ -10958,7 +10948,7 @@
       </c>
       <c r="G220" s="10" t="inlineStr">
         <is>
-          <t>dynastyms</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H220" s="11" t="inlineStr">
@@ -10996,7 +10986,7 @@
       </c>
       <c r="G221" s="10" t="inlineStr">
         <is>
-          <t>dynastynirmala</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H221" s="11" t="inlineStr">
@@ -11038,7 +11028,7 @@
       </c>
       <c r="G222" s="10" t="inlineStr">
         <is>
-          <t>dynastyprita</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H222" s="11" t="inlineStr">
@@ -11080,7 +11070,7 @@
       </c>
       <c r="G223" s="10" t="inlineStr">
         <is>
-          <t>dynastyronald</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H223" s="11" t="inlineStr">
@@ -11122,7 +11112,7 @@
       </c>
       <c r="G224" s="10" t="inlineStr">
         <is>
-          <t>dynastysharifah</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H224" s="11" t="inlineStr">
@@ -11164,7 +11154,7 @@
       </c>
       <c r="G225" s="10" t="inlineStr">
         <is>
-          <t>dynastysusy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H225" s="11" t="inlineStr">
@@ -11206,7 +11196,7 @@
       </c>
       <c r="G226" s="10" t="inlineStr">
         <is>
-          <t>dynastytsung-han</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H226" s="11" t="inlineStr">
@@ -11248,7 +11238,7 @@
       </c>
       <c r="G227" s="10" t="inlineStr">
         <is>
-          <t>dynastyutari</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H227" s="11" t="inlineStr">
@@ -11290,7 +11280,7 @@
       </c>
       <c r="G228" s="10" t="inlineStr">
         <is>
-          <t>dynastyvini</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H228" s="11" t="inlineStr">
@@ -11328,7 +11318,7 @@
       </c>
       <c r="G229" s="10" t="inlineStr">
         <is>
-          <t>excellenceso</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H229" s="11" t="inlineStr">
@@ -11370,7 +11360,7 @@
       </c>
       <c r="G230" s="10" t="inlineStr">
         <is>
-          <t>elevatepriscilla</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H230" s="11" t="inlineStr">
@@ -11412,7 +11402,7 @@
       </c>
       <c r="G231" s="10" t="inlineStr">
         <is>
-          <t>elevatewilliam</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H231" s="11" t="inlineStr">
@@ -11454,7 +11444,7 @@
       </c>
       <c r="G232" s="10" t="inlineStr">
         <is>
-          <t>empowerzefirelli</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H232" s="11" t="inlineStr">
@@ -11492,7 +11482,7 @@
       </c>
       <c r="G233" s="10" t="inlineStr">
         <is>
-          <t>evolvejane</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H233" s="11" t="inlineStr">
@@ -11530,7 +11520,7 @@
       </c>
       <c r="G234" s="10" t="inlineStr">
         <is>
-          <t>excellencekevin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H234" s="11" t="inlineStr">
@@ -11568,7 +11558,7 @@
       </c>
       <c r="G235" s="10" t="inlineStr">
         <is>
-          <t>excellencelaw</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H235" s="11" t="inlineStr">
@@ -11610,7 +11600,7 @@
       </c>
       <c r="G236" s="10" t="inlineStr">
         <is>
-          <t>exploreronlinemille</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H236" s="11" t="inlineStr">
@@ -11652,7 +11642,7 @@
       </c>
       <c r="G237" s="10" t="inlineStr">
         <is>
-          <t>extremesamantha</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H237" s="11" t="inlineStr">
@@ -11694,7 +11684,7 @@
       </c>
       <c r="G238" s="10" t="inlineStr">
         <is>
-          <t>fireflyaditya</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H238" s="11" t="inlineStr">
@@ -11736,7 +11726,7 @@
       </c>
       <c r="G239" s="10" t="inlineStr">
         <is>
-          <t>fireflycharles</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H239" s="11" t="inlineStr">
@@ -11778,7 +11768,7 @@
       </c>
       <c r="G240" s="10" t="inlineStr">
         <is>
-          <t>fireflygustina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H240" s="11" t="inlineStr">
@@ -11820,7 +11810,7 @@
       </c>
       <c r="G241" s="10" t="inlineStr">
         <is>
-          <t>fireflyhendra</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H241" s="11" t="inlineStr">
@@ -11862,7 +11852,7 @@
       </c>
       <c r="G242" s="10" t="inlineStr">
         <is>
-          <t>fireflyjanto</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H242" s="11" t="inlineStr">
@@ -11904,7 +11894,7 @@
       </c>
       <c r="G243" s="10" t="inlineStr">
         <is>
-          <t>fireflyjeanette</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H243" s="11" t="inlineStr">
@@ -11946,7 +11936,7 @@
       </c>
       <c r="G244" s="10" t="inlineStr">
         <is>
-          <t>fireflyjohnny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H244" s="11" t="inlineStr">
@@ -11988,7 +11978,7 @@
       </c>
       <c r="G245" s="10" t="inlineStr">
         <is>
-          <t>fireflyrusli</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H245" s="11" t="inlineStr">
@@ -12030,7 +12020,7 @@
       </c>
       <c r="G246" s="10" t="inlineStr">
         <is>
-          <t>fireflysuhandy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H246" s="11" t="inlineStr">
@@ -12072,7 +12062,7 @@
       </c>
       <c r="G247" s="10" t="inlineStr">
         <is>
-          <t>fireflywiryawan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H247" s="11" t="inlineStr">
@@ -12114,7 +12104,7 @@
       </c>
       <c r="G248" s="10" t="inlineStr">
         <is>
-          <t>fireflyyandi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H248" s="11" t="inlineStr">
@@ -12152,7 +12142,7 @@
       </c>
       <c r="G249" s="10" t="inlineStr">
         <is>
-          <t>foshannanhaiwestwealthymei</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H249" s="11" t="inlineStr">
@@ -12190,7 +12180,7 @@
       </c>
       <c r="G250" s="10" t="inlineStr">
         <is>
-          <t>foshannanhaiwestwealthywingkin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H250" s="11" t="inlineStr">
@@ -12228,7 +12218,7 @@
       </c>
       <c r="G251" s="10" t="inlineStr">
         <is>
-          <t>foshannanhaiwestwealthyyanbin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H251" s="11" t="inlineStr">
@@ -12266,7 +12256,7 @@
       </c>
       <c r="G252" s="10" t="inlineStr">
         <is>
-          <t>foshannanhaiwestwealthyying</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H252" s="11" t="inlineStr">
@@ -12304,7 +12294,7 @@
       </c>
       <c r="G253" s="10" t="inlineStr">
         <is>
-          <t>foshannanhaiwestwealthyyonghong</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H253" s="11" t="inlineStr">
@@ -12342,7 +12332,7 @@
       </c>
       <c r="G254" s="10" t="inlineStr">
         <is>
-          <t>gzdezhongjinghong</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H254" s="11" t="inlineStr">
@@ -12380,7 +12370,7 @@
       </c>
       <c r="G255" s="10" t="inlineStr">
         <is>
-          <t>gzxingdebo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H255" s="11" t="inlineStr">
@@ -12418,7 +12408,7 @@
       </c>
       <c r="G256" s="10" t="inlineStr">
         <is>
-          <t>gzxingdexianhua</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H256" s="11" t="inlineStr">
@@ -12456,7 +12446,7 @@
       </c>
       <c r="G257" s="10" t="inlineStr">
         <is>
-          <t>gzzhongchenghuali</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H257" s="11" t="inlineStr">
@@ -12494,7 +12484,7 @@
       </c>
       <c r="G258" s="10" t="inlineStr">
         <is>
-          <t>gamadasuhanae</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H258" s="11" t="inlineStr">
@@ -12536,7 +12526,7 @@
       </c>
       <c r="G259" s="10" t="inlineStr">
         <is>
-          <t>ganeshaarief</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H259" s="11" t="inlineStr">
@@ -12578,7 +12568,7 @@
       </c>
       <c r="G260" s="10" t="inlineStr">
         <is>
-          <t>ganeshadr</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H260" s="11" t="inlineStr">
@@ -12620,7 +12610,7 @@
       </c>
       <c r="G261" s="10" t="inlineStr">
         <is>
-          <t>ganeshadr</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H261" s="11" t="inlineStr">
@@ -12662,7 +12652,7 @@
       </c>
       <c r="G262" s="10" t="inlineStr">
         <is>
-          <t>ganeshafreddy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H262" s="11" t="inlineStr">
@@ -12704,7 +12694,7 @@
       </c>
       <c r="G263" s="10" t="inlineStr">
         <is>
-          <t>ganeshaindari</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H263" s="11" t="inlineStr">
@@ -12746,7 +12736,7 @@
       </c>
       <c r="G264" s="10" t="inlineStr">
         <is>
-          <t>ganeshaindradjaja</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H264" s="11" t="inlineStr">
@@ -12788,7 +12778,7 @@
       </c>
       <c r="G265" s="10" t="inlineStr">
         <is>
-          <t>ganeshairma</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H265" s="11" t="inlineStr">
@@ -12830,7 +12820,7 @@
       </c>
       <c r="G266" s="10" t="inlineStr">
         <is>
-          <t>ganeshanugroho</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H266" s="11" t="inlineStr">
@@ -12872,7 +12862,7 @@
       </c>
       <c r="G267" s="10" t="inlineStr">
         <is>
-          <t>ganeshapujo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H267" s="11" t="inlineStr">
@@ -12914,7 +12904,7 @@
       </c>
       <c r="G268" s="10" t="inlineStr">
         <is>
-          <t>ganeshaputra</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H268" s="11" t="inlineStr">
@@ -12956,7 +12946,7 @@
       </c>
       <c r="G269" s="10" t="inlineStr">
         <is>
-          <t>ganesharudi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H269" s="11" t="inlineStr">
@@ -12983,22 +12973,22 @@
       </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
-          <t>1679F-2526B0D53</t>
+          <t>1679F-240DB2231</t>
         </is>
       </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09078</t>
+          <t>NATCON-2026-09305</t>
         </is>
       </c>
       <c r="F270" s="10" t="inlineStr">
         <is>
-          <t>interiir.xie@gmail.com</t>
+          <t>interior.xie@gmail.com</t>
         </is>
       </c>
       <c r="G270" s="10" t="inlineStr">
         <is>
-          <t>ganeshastevanus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H270" s="11" t="inlineStr">
@@ -13025,22 +13015,22 @@
       </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
-          <t>1679F-240DB2231</t>
+          <t>1679F-2526B0D53</t>
         </is>
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09305</t>
+          <t>NATCON-2026-09078</t>
         </is>
       </c>
       <c r="F271" s="10" t="inlineStr">
         <is>
-          <t>interior.xie@gmail.com</t>
+          <t>interiir.xie@gmail.com</t>
         </is>
       </c>
       <c r="G271" s="10" t="inlineStr">
         <is>
-          <t>ganeshastevanus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H271" s="11" t="inlineStr">
@@ -13082,7 +13072,7 @@
       </c>
       <c r="G272" s="10" t="inlineStr">
         <is>
-          <t>ganeshayeri</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H272" s="11" t="inlineStr">
@@ -13124,7 +13114,7 @@
       </c>
       <c r="G273" s="10" t="inlineStr">
         <is>
-          <t>garudadanang</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H273" s="11" t="inlineStr">
@@ -13166,7 +13156,7 @@
       </c>
       <c r="G274" s="10" t="inlineStr">
         <is>
-          <t>garudaedo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H274" s="11" t="inlineStr">
@@ -13208,7 +13198,7 @@
       </c>
       <c r="G275" s="10" t="inlineStr">
         <is>
-          <t>garudaerni</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H275" s="11" t="inlineStr">
@@ -13250,7 +13240,7 @@
       </c>
       <c r="G276" s="10" t="inlineStr">
         <is>
-          <t>garudaleamartin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H276" s="11" t="inlineStr">
@@ -13292,7 +13282,7 @@
       </c>
       <c r="G277" s="10" t="inlineStr">
         <is>
-          <t>garudalukman</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H277" s="11" t="inlineStr">
@@ -13334,7 +13324,7 @@
       </c>
       <c r="G278" s="10" t="inlineStr">
         <is>
-          <t>garudasriwedari</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H278" s="11" t="inlineStr">
@@ -13372,7 +13362,7 @@
       </c>
       <c r="G279" s="10" t="inlineStr">
         <is>
-          <t>glorifyallif</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H279" s="11" t="inlineStr">
@@ -13414,7 +13404,7 @@
       </c>
       <c r="G280" s="10" t="inlineStr">
         <is>
-          <t>glorifyamri</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H280" s="11" t="inlineStr">
@@ -13456,7 +13446,7 @@
       </c>
       <c r="G281" s="10" t="inlineStr">
         <is>
-          <t>glorifyandre</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H281" s="11" t="inlineStr">
@@ -13498,7 +13488,7 @@
       </c>
       <c r="G282" s="10" t="inlineStr">
         <is>
-          <t>glorifyandrew</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H282" s="11" t="inlineStr">
@@ -13540,7 +13530,7 @@
       </c>
       <c r="G283" s="10" t="inlineStr">
         <is>
-          <t>glorifyanita</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H283" s="11" t="inlineStr">
@@ -13582,7 +13572,7 @@
       </c>
       <c r="G284" s="10" t="inlineStr">
         <is>
-          <t>glorifyanthonius</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H284" s="11" t="inlineStr">
@@ -13624,7 +13614,7 @@
       </c>
       <c r="G285" s="10" t="inlineStr">
         <is>
-          <t>glorifyaprilia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H285" s="11" t="inlineStr">
@@ -13666,7 +13656,7 @@
       </c>
       <c r="G286" s="10" t="inlineStr">
         <is>
-          <t>glorifyaudia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H286" s="11" t="inlineStr">
@@ -13708,7 +13698,7 @@
       </c>
       <c r="G287" s="10" t="inlineStr">
         <is>
-          <t>glorifybenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H287" s="11" t="inlineStr">
@@ -13750,7 +13740,7 @@
       </c>
       <c r="G288" s="10" t="inlineStr">
         <is>
-          <t>glorifydedy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H288" s="11" t="inlineStr">
@@ -13792,7 +13782,7 @@
       </c>
       <c r="G289" s="10" t="inlineStr">
         <is>
-          <t>glorifydominggus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H289" s="11" t="inlineStr">
@@ -13834,7 +13824,7 @@
       </c>
       <c r="G290" s="10" t="inlineStr">
         <is>
-          <t>glorifyfebrianto</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H290" s="11" t="inlineStr">
@@ -13876,7 +13866,7 @@
       </c>
       <c r="G291" s="10" t="inlineStr">
         <is>
-          <t>glorifyfrans</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H291" s="11" t="inlineStr">
@@ -13918,7 +13908,7 @@
       </c>
       <c r="G292" s="10" t="inlineStr">
         <is>
-          <t>glorifyharimbob</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H292" s="11" t="inlineStr">
@@ -13960,7 +13950,7 @@
       </c>
       <c r="G293" s="10" t="inlineStr">
         <is>
-          <t>glorifyi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H293" s="11" t="inlineStr">
@@ -14002,7 +13992,7 @@
       </c>
       <c r="G294" s="10" t="inlineStr">
         <is>
-          <t>glorifyika</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H294" s="11" t="inlineStr">
@@ -14044,7 +14034,7 @@
       </c>
       <c r="G295" s="10" t="inlineStr">
         <is>
-          <t>glorifyjimmy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H295" s="11" t="inlineStr">
@@ -14082,7 +14072,7 @@
       </c>
       <c r="G296" s="10" t="inlineStr">
         <is>
-          <t>glorifykathryn</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H296" s="11" t="inlineStr">
@@ -14124,7 +14114,7 @@
       </c>
       <c r="G297" s="10" t="inlineStr">
         <is>
-          <t>glorifykian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H297" s="11" t="inlineStr">
@@ -14166,7 +14156,7 @@
       </c>
       <c r="G298" s="10" t="inlineStr">
         <is>
-          <t>glorifylia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H298" s="11" t="inlineStr">
@@ -14208,7 +14198,7 @@
       </c>
       <c r="G299" s="10" t="inlineStr">
         <is>
-          <t>glorifylisa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H299" s="11" t="inlineStr">
@@ -14250,7 +14240,7 @@
       </c>
       <c r="G300" s="10" t="inlineStr">
         <is>
-          <t>glorifyliza</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H300" s="11" t="inlineStr">
@@ -14292,7 +14282,7 @@
       </c>
       <c r="G301" s="10" t="inlineStr">
         <is>
-          <t>glorifymaria</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H301" s="11" t="inlineStr">
@@ -14334,7 +14324,7 @@
       </c>
       <c r="G302" s="10" t="inlineStr">
         <is>
-          <t>glorifymuhammad</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H302" s="11" t="inlineStr">
@@ -14376,7 +14366,7 @@
       </c>
       <c r="G303" s="10" t="inlineStr">
         <is>
-          <t>glorifypuguh</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H303" s="11" t="inlineStr">
@@ -14418,7 +14408,7 @@
       </c>
       <c r="G304" s="10" t="inlineStr">
         <is>
-          <t>glorifyrio</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H304" s="11" t="inlineStr">
@@ -14460,7 +14450,7 @@
       </c>
       <c r="G305" s="10" t="inlineStr">
         <is>
-          <t>glorifystanley</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H305" s="11" t="inlineStr">
@@ -14502,7 +14492,7 @@
       </c>
       <c r="G306" s="10" t="inlineStr">
         <is>
-          <t>glorifysugeng</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H306" s="11" t="inlineStr">
@@ -14544,7 +14534,7 @@
       </c>
       <c r="G307" s="10" t="inlineStr">
         <is>
-          <t>glorifyveronica</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H307" s="11" t="inlineStr">
@@ -14586,7 +14576,7 @@
       </c>
       <c r="G308" s="10" t="inlineStr">
         <is>
-          <t>glorifyyan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H308" s="11" t="inlineStr">
@@ -14628,7 +14618,7 @@
       </c>
       <c r="G309" s="10" t="inlineStr">
         <is>
-          <t>glorifyzeti</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H309" s="11" t="inlineStr">
@@ -14670,7 +14660,7 @@
       </c>
       <c r="G310" s="10" t="inlineStr">
         <is>
-          <t>growachmad</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H310" s="11" t="inlineStr">
@@ -14712,7 +14702,7 @@
       </c>
       <c r="G311" s="10" t="inlineStr">
         <is>
-          <t>growadil</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H311" s="11" t="inlineStr">
@@ -14754,7 +14744,7 @@
       </c>
       <c r="G312" s="10" t="inlineStr">
         <is>
-          <t>growagnes</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H312" s="11" t="inlineStr">
@@ -14796,7 +14786,7 @@
       </c>
       <c r="G313" s="10" t="inlineStr">
         <is>
-          <t>growalbert</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H313" s="11" t="inlineStr">
@@ -14838,7 +14828,7 @@
       </c>
       <c r="G314" s="10" t="inlineStr">
         <is>
-          <t>growandre</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H314" s="11" t="inlineStr">
@@ -14880,7 +14870,7 @@
       </c>
       <c r="G315" s="10" t="inlineStr">
         <is>
-          <t>growanna</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H315" s="11" t="inlineStr">
@@ -14922,7 +14912,7 @@
       </c>
       <c r="G316" s="10" t="inlineStr">
         <is>
-          <t>growarvind</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H316" s="11" t="inlineStr">
@@ -14964,7 +14954,7 @@
       </c>
       <c r="G317" s="10" t="inlineStr">
         <is>
-          <t>growazinul</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H317" s="11" t="inlineStr">
@@ -15006,7 +14996,7 @@
       </c>
       <c r="G318" s="10" t="inlineStr">
         <is>
-          <t>growben</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H318" s="11" t="inlineStr">
@@ -15048,7 +15038,7 @@
       </c>
       <c r="G319" s="10" t="inlineStr">
         <is>
-          <t>growbenediktus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H319" s="11" t="inlineStr">
@@ -15090,7 +15080,7 @@
       </c>
       <c r="G320" s="10" t="inlineStr">
         <is>
-          <t>growbonaventura</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H320" s="11" t="inlineStr">
@@ -15132,7 +15122,7 @@
       </c>
       <c r="G321" s="10" t="inlineStr">
         <is>
-          <t>growcharles</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H321" s="11" t="inlineStr">
@@ -15174,7 +15164,7 @@
       </c>
       <c r="G322" s="10" t="inlineStr">
         <is>
-          <t>growdedy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H322" s="11" t="inlineStr">
@@ -15216,7 +15206,7 @@
       </c>
       <c r="G323" s="10" t="inlineStr">
         <is>
-          <t>growdiany</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H323" s="11" t="inlineStr">
@@ -15258,7 +15248,7 @@
       </c>
       <c r="G324" s="10" t="inlineStr">
         <is>
-          <t>growerdy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H324" s="11" t="inlineStr">
@@ -15300,7 +15290,7 @@
       </c>
       <c r="G325" s="10" t="inlineStr">
         <is>
-          <t>growerly</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H325" s="11" t="inlineStr">
@@ -15342,7 +15332,7 @@
       </c>
       <c r="G326" s="10" t="inlineStr">
         <is>
-          <t>groweva</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H326" s="11" t="inlineStr">
@@ -15380,7 +15370,7 @@
       </c>
       <c r="G327" s="10" t="inlineStr">
         <is>
-          <t>growfelix</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H327" s="11" t="inlineStr">
@@ -15418,7 +15408,7 @@
       </c>
       <c r="G328" s="10" t="inlineStr">
         <is>
-          <t>growgrace</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H328" s="11" t="inlineStr">
@@ -15456,7 +15446,7 @@
       </c>
       <c r="G329" s="10" t="inlineStr">
         <is>
-          <t>growgrace</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H329" s="11" t="inlineStr">
@@ -15498,7 +15488,7 @@
       </c>
       <c r="G330" s="10" t="inlineStr">
         <is>
-          <t>growhandy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H330" s="11" t="inlineStr">
@@ -15540,7 +15530,7 @@
       </c>
       <c r="G331" s="10" t="inlineStr">
         <is>
-          <t>growhari</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H331" s="11" t="inlineStr">
@@ -15582,7 +15572,7 @@
       </c>
       <c r="G332" s="10" t="inlineStr">
         <is>
-          <t>growherlambang</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H332" s="11" t="inlineStr">
@@ -15624,7 +15614,7 @@
       </c>
       <c r="G333" s="10" t="inlineStr">
         <is>
-          <t>growherwin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H333" s="11" t="inlineStr">
@@ -15666,7 +15656,7 @@
       </c>
       <c r="G334" s="10" t="inlineStr">
         <is>
-          <t>growhsuehhui</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H334" s="11" t="inlineStr">
@@ -15708,7 +15698,7 @@
       </c>
       <c r="G335" s="10" t="inlineStr">
         <is>
-          <t>growiman</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H335" s="11" t="inlineStr">
@@ -15750,7 +15740,7 @@
       </c>
       <c r="G336" s="10" t="inlineStr">
         <is>
-          <t>growjaksen</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H336" s="11" t="inlineStr">
@@ -15792,7 +15782,7 @@
       </c>
       <c r="G337" s="10" t="inlineStr">
         <is>
-          <t>growjohn</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H337" s="11" t="inlineStr">
@@ -15830,7 +15820,7 @@
       </c>
       <c r="G338" s="10" t="inlineStr">
         <is>
-          <t>growjonathan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H338" s="11" t="inlineStr">
@@ -15872,7 +15862,7 @@
       </c>
       <c r="G339" s="10" t="inlineStr">
         <is>
-          <t>growkezia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H339" s="11" t="inlineStr">
@@ -15914,7 +15904,7 @@
       </c>
       <c r="G340" s="10" t="inlineStr">
         <is>
-          <t>growlurus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H340" s="11" t="inlineStr">
@@ -15956,7 +15946,7 @@
       </c>
       <c r="G341" s="10" t="inlineStr">
         <is>
-          <t>growmaria</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H341" s="11" t="inlineStr">
@@ -15998,7 +15988,7 @@
       </c>
       <c r="G342" s="10" t="inlineStr">
         <is>
-          <t>growmark</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H342" s="11" t="inlineStr">
@@ -16040,7 +16030,7 @@
       </c>
       <c r="G343" s="10" t="inlineStr">
         <is>
-          <t>growmas</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H343" s="11" t="inlineStr">
@@ -16082,7 +16072,7 @@
       </c>
       <c r="G344" s="10" t="inlineStr">
         <is>
-          <t>growmayawati</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H344" s="11" t="inlineStr">
@@ -16124,7 +16114,7 @@
       </c>
       <c r="G345" s="10" t="inlineStr">
         <is>
-          <t>growmichael</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H345" s="11" t="inlineStr">
@@ -16166,7 +16156,7 @@
       </c>
       <c r="G346" s="10" t="inlineStr">
         <is>
-          <t>grownicholas</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H346" s="11" t="inlineStr">
@@ -16208,7 +16198,7 @@
       </c>
       <c r="G347" s="10" t="inlineStr">
         <is>
-          <t>grownida</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H347" s="11" t="inlineStr">
@@ -16250,7 +16240,7 @@
       </c>
       <c r="G348" s="10" t="inlineStr">
         <is>
-          <t>grownovi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H348" s="11" t="inlineStr">
@@ -16292,7 +16282,7 @@
       </c>
       <c r="G349" s="10" t="inlineStr">
         <is>
-          <t>growpaul</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H349" s="11" t="inlineStr">
@@ -16334,7 +16324,7 @@
       </c>
       <c r="G350" s="10" t="inlineStr">
         <is>
-          <t>growprijono</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H350" s="11" t="inlineStr">
@@ -16376,7 +16366,7 @@
       </c>
       <c r="G351" s="10" t="inlineStr">
         <is>
-          <t>growriene</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H351" s="11" t="inlineStr">
@@ -16418,7 +16408,7 @@
       </c>
       <c r="G352" s="10" t="inlineStr">
         <is>
-          <t>growryan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H352" s="11" t="inlineStr">
@@ -16460,7 +16450,7 @@
       </c>
       <c r="G353" s="10" t="inlineStr">
         <is>
-          <t>growsamuel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H353" s="11" t="inlineStr">
@@ -16502,7 +16492,7 @@
       </c>
       <c r="G354" s="10" t="inlineStr">
         <is>
-          <t>growsetia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H354" s="11" t="inlineStr">
@@ -16544,7 +16534,7 @@
       </c>
       <c r="G355" s="10" t="inlineStr">
         <is>
-          <t>growsissy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H355" s="11" t="inlineStr">
@@ -16582,7 +16572,7 @@
       </c>
       <c r="G356" s="10" t="inlineStr">
         <is>
-          <t>growsofyana</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H356" s="11" t="inlineStr">
@@ -16620,7 +16610,7 @@
       </c>
       <c r="G357" s="10" t="inlineStr">
         <is>
-          <t>growsuntoro</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H357" s="11" t="inlineStr">
@@ -16662,7 +16652,7 @@
       </c>
       <c r="G358" s="10" t="inlineStr">
         <is>
-          <t>growyuli</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H358" s="11" t="inlineStr">
@@ -16704,7 +16694,7 @@
       </c>
       <c r="G359" s="10" t="inlineStr">
         <is>
-          <t>growarry</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H359" s="11" t="inlineStr">
@@ -16746,7 +16736,7 @@
       </c>
       <c r="G360" s="10" t="inlineStr">
         <is>
-          <t>growlucky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H360" s="11" t="inlineStr">
@@ -16788,7 +16778,7 @@
       </c>
       <c r="G361" s="10" t="inlineStr">
         <is>
-          <t>guestpraderm</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H361" s="11" t="inlineStr">
@@ -16826,7 +16816,7 @@
       </c>
       <c r="G362" s="10" t="inlineStr">
         <is>
-          <t>herowong</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H362" s="11" t="inlineStr">
@@ -16864,7 +16854,7 @@
       </c>
       <c r="G363" s="10" t="inlineStr">
         <is>
-          <t>horizonmeirong</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H363" s="11" t="inlineStr">
@@ -16906,7 +16896,7 @@
       </c>
       <c r="G364" s="10" t="inlineStr">
         <is>
-          <t>heritageabraham</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H364" s="11" t="inlineStr">
@@ -16948,7 +16938,7 @@
       </c>
       <c r="G365" s="10" t="inlineStr">
         <is>
-          <t>heritageagustienna</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H365" s="11" t="inlineStr">
@@ -16986,7 +16976,7 @@
       </c>
       <c r="G366" s="10" t="inlineStr">
         <is>
-          <t>heritagealoysius</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H366" s="11" t="inlineStr">
@@ -17028,7 +17018,7 @@
       </c>
       <c r="G367" s="10" t="inlineStr">
         <is>
-          <t>heritagealvin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H367" s="11" t="inlineStr">
@@ -17070,7 +17060,7 @@
       </c>
       <c r="G368" s="10" t="inlineStr">
         <is>
-          <t>heritageandre</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H368" s="11" t="inlineStr">
@@ -17112,7 +17102,7 @@
       </c>
       <c r="G369" s="10" t="inlineStr">
         <is>
-          <t>heritagearis</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H369" s="11" t="inlineStr">
@@ -17154,7 +17144,7 @@
       </c>
       <c r="G370" s="10" t="inlineStr">
         <is>
-          <t>heritagefarizal</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H370" s="11" t="inlineStr">
@@ -17196,7 +17186,7 @@
       </c>
       <c r="G371" s="10" t="inlineStr">
         <is>
-          <t>heritagefelicia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H371" s="11" t="inlineStr">
@@ -17238,7 +17228,7 @@
       </c>
       <c r="G372" s="10" t="inlineStr">
         <is>
-          <t>heritagefenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H372" s="11" t="inlineStr">
@@ -17280,7 +17270,7 @@
       </c>
       <c r="G373" s="10" t="inlineStr">
         <is>
-          <t>heritagefransisca</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H373" s="11" t="inlineStr">
@@ -17322,7 +17312,7 @@
       </c>
       <c r="G374" s="10" t="inlineStr">
         <is>
-          <t>heritagegideon</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H374" s="11" t="inlineStr">
@@ -17364,7 +17354,7 @@
       </c>
       <c r="G375" s="10" t="inlineStr">
         <is>
-          <t>heritageharry</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H375" s="11" t="inlineStr">
@@ -17406,7 +17396,7 @@
       </c>
       <c r="G376" s="10" t="inlineStr">
         <is>
-          <t>heritagehendy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H376" s="11" t="inlineStr">
@@ -17448,7 +17438,7 @@
       </c>
       <c r="G377" s="10" t="inlineStr">
         <is>
-          <t>heritagehenky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H377" s="11" t="inlineStr">
@@ -17490,7 +17480,7 @@
       </c>
       <c r="G378" s="10" t="inlineStr">
         <is>
-          <t>heritagehugo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H378" s="11" t="inlineStr">
@@ -17532,7 +17522,7 @@
       </c>
       <c r="G379" s="10" t="inlineStr">
         <is>
-          <t>heritageimam</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H379" s="11" t="inlineStr">
@@ -17574,7 +17564,7 @@
       </c>
       <c r="G380" s="10" t="inlineStr">
         <is>
-          <t>heritageivan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H380" s="11" t="inlineStr">
@@ -17616,7 +17606,7 @@
       </c>
       <c r="G381" s="10" t="inlineStr">
         <is>
-          <t>heritagejane</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H381" s="11" t="inlineStr">
@@ -17658,7 +17648,7 @@
       </c>
       <c r="G382" s="10" t="inlineStr">
         <is>
-          <t>heritagelidia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H382" s="11" t="inlineStr">
@@ -17700,7 +17690,7 @@
       </c>
       <c r="G383" s="10" t="inlineStr">
         <is>
-          <t>heritagenatalia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H383" s="11" t="inlineStr">
@@ -17742,7 +17732,7 @@
       </c>
       <c r="G384" s="10" t="inlineStr">
         <is>
-          <t>heritagentjahajono</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H384" s="11" t="inlineStr">
@@ -17784,7 +17774,7 @@
       </c>
       <c r="G385" s="10" t="inlineStr">
         <is>
-          <t>heritagerandy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H385" s="11" t="inlineStr">
@@ -17826,7 +17816,7 @@
       </c>
       <c r="G386" s="10" t="inlineStr">
         <is>
-          <t>heritagerenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H386" s="11" t="inlineStr">
@@ -17868,7 +17858,7 @@
       </c>
       <c r="G387" s="10" t="inlineStr">
         <is>
-          <t>heritageruddy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H387" s="11" t="inlineStr">
@@ -17910,7 +17900,7 @@
       </c>
       <c r="G388" s="10" t="inlineStr">
         <is>
-          <t>heritagesusanti</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H388" s="11" t="inlineStr">
@@ -17952,7 +17942,7 @@
       </c>
       <c r="G389" s="10" t="inlineStr">
         <is>
-          <t>heritagetommy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H389" s="11" t="inlineStr">
@@ -17994,7 +17984,7 @@
       </c>
       <c r="G390" s="10" t="inlineStr">
         <is>
-          <t>heritagevania</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H390" s="11" t="inlineStr">
@@ -18036,7 +18026,7 @@
       </c>
       <c r="G391" s="10" t="inlineStr">
         <is>
-          <t>heritagewilliam</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H391" s="11" t="inlineStr">
@@ -18078,7 +18068,7 @@
       </c>
       <c r="G392" s="10" t="inlineStr">
         <is>
-          <t>heritageyohana</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H392" s="11" t="inlineStr">
@@ -18116,7 +18106,7 @@
       </c>
       <c r="G393" s="10" t="inlineStr">
         <is>
-          <t>herokenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H393" s="11" t="inlineStr">
@@ -18154,7 +18144,7 @@
       </c>
       <c r="G394" s="10" t="inlineStr">
         <is>
-          <t>herokenway</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H394" s="11" t="inlineStr">
@@ -18192,7 +18182,7 @@
       </c>
       <c r="G395" s="10" t="inlineStr">
         <is>
-          <t>huajapannexustony</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H395" s="11" t="inlineStr">
@@ -18234,7 +18224,7 @@
       </c>
       <c r="G396" s="10" t="inlineStr">
         <is>
-          <t>huayibillionjenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H396" s="11" t="inlineStr">
@@ -18276,7 +18266,7 @@
       </c>
       <c r="G397" s="10" t="inlineStr">
         <is>
-          <t>huayibillionshiau</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H397" s="11" t="inlineStr">
@@ -18314,7 +18304,7 @@
       </c>
       <c r="G398" s="10" t="inlineStr">
         <is>
-          <t>igniteafif</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H398" s="11" t="inlineStr">
@@ -18356,7 +18346,7 @@
       </c>
       <c r="G399" s="10" t="inlineStr">
         <is>
-          <t>ignitealbert</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H399" s="11" t="inlineStr">
@@ -18398,7 +18388,7 @@
       </c>
       <c r="G400" s="10" t="inlineStr">
         <is>
-          <t>ignitealbert</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H400" s="11" t="inlineStr">
@@ -18440,7 +18430,7 @@
       </c>
       <c r="G401" s="10" t="inlineStr">
         <is>
-          <t>igniteayu</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H401" s="11" t="inlineStr">
@@ -18482,7 +18472,7 @@
       </c>
       <c r="G402" s="10" t="inlineStr">
         <is>
-          <t>ignitebudiman</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H402" s="11" t="inlineStr">
@@ -18524,7 +18514,7 @@
       </c>
       <c r="G403" s="10" t="inlineStr">
         <is>
-          <t>ignitecahyadi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H403" s="11" t="inlineStr">
@@ -18566,7 +18556,7 @@
       </c>
       <c r="G404" s="10" t="inlineStr">
         <is>
-          <t>igniteelise</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H404" s="11" t="inlineStr">
@@ -18608,7 +18598,7 @@
       </c>
       <c r="G405" s="10" t="inlineStr">
         <is>
-          <t>ignitefery</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H405" s="11" t="inlineStr">
@@ -18650,7 +18640,7 @@
       </c>
       <c r="G406" s="10" t="inlineStr">
         <is>
-          <t>ignitelim</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H406" s="11" t="inlineStr">
@@ -18692,7 +18682,7 @@
       </c>
       <c r="G407" s="10" t="inlineStr">
         <is>
-          <t>ignitelucia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H407" s="11" t="inlineStr">
@@ -18734,7 +18724,7 @@
       </c>
       <c r="G408" s="10" t="inlineStr">
         <is>
-          <t>ignitemaximillian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H408" s="11" t="inlineStr">
@@ -18776,7 +18766,7 @@
       </c>
       <c r="G409" s="10" t="inlineStr">
         <is>
-          <t>ignitenorma</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H409" s="11" t="inlineStr">
@@ -18818,7 +18808,7 @@
       </c>
       <c r="G410" s="10" t="inlineStr">
         <is>
-          <t>igniterichard</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H410" s="11" t="inlineStr">
@@ -18860,7 +18850,7 @@
       </c>
       <c r="G411" s="10" t="inlineStr">
         <is>
-          <t>igniterika</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H411" s="11" t="inlineStr">
@@ -18902,7 +18892,7 @@
       </c>
       <c r="G412" s="10" t="inlineStr">
         <is>
-          <t>ignitesebastian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H412" s="11" t="inlineStr">
@@ -18944,7 +18934,7 @@
       </c>
       <c r="G413" s="10" t="inlineStr">
         <is>
-          <t>ignitesherly</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H413" s="11" t="inlineStr">
@@ -18986,7 +18976,7 @@
       </c>
       <c r="G414" s="10" t="inlineStr">
         <is>
-          <t>ignitesurandi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H414" s="11" t="inlineStr">
@@ -19028,7 +19018,7 @@
       </c>
       <c r="G415" s="10" t="inlineStr">
         <is>
-          <t>ignitewilly</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H415" s="11" t="inlineStr">
@@ -19070,7 +19060,7 @@
       </c>
       <c r="G416" s="10" t="inlineStr">
         <is>
-          <t>igniteyunita</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H416" s="11" t="inlineStr">
@@ -19112,7 +19102,7 @@
       </c>
       <c r="G417" s="10" t="inlineStr">
         <is>
-          <t>igniteyusfa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H417" s="11" t="inlineStr">
@@ -19150,7 +19140,7 @@
       </c>
       <c r="G418" s="10" t="inlineStr">
         <is>
-          <t>lighthouseadina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H418" s="11" t="inlineStr">
@@ -19192,7 +19182,7 @@
       </c>
       <c r="G419" s="10" t="inlineStr">
         <is>
-          <t>lighthousealif</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H419" s="11" t="inlineStr">
@@ -19234,7 +19224,7 @@
       </c>
       <c r="G420" s="10" t="inlineStr">
         <is>
-          <t>lighthouseandre</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H420" s="11" t="inlineStr">
@@ -19276,7 +19266,7 @@
       </c>
       <c r="G421" s="10" t="inlineStr">
         <is>
-          <t>lighthouseandy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H421" s="11" t="inlineStr">
@@ -19318,7 +19308,7 @@
       </c>
       <c r="G422" s="10" t="inlineStr">
         <is>
-          <t>lighthouseardley</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H422" s="11" t="inlineStr">
@@ -19360,7 +19350,7 @@
       </c>
       <c r="G423" s="10" t="inlineStr">
         <is>
-          <t>lighthouseardylles</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H423" s="11" t="inlineStr">
@@ -19402,7 +19392,7 @@
       </c>
       <c r="G424" s="10" t="inlineStr">
         <is>
-          <t>lighthousearline</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H424" s="11" t="inlineStr">
@@ -19444,7 +19434,7 @@
       </c>
       <c r="G425" s="10" t="inlineStr">
         <is>
-          <t>lighthousecaprice</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H425" s="11" t="inlineStr">
@@ -19486,7 +19476,7 @@
       </c>
       <c r="G426" s="10" t="inlineStr">
         <is>
-          <t>lighthouseevy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H426" s="11" t="inlineStr">
@@ -19528,7 +19518,7 @@
       </c>
       <c r="G427" s="10" t="inlineStr">
         <is>
-          <t>lighthousefaridho</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H427" s="11" t="inlineStr">
@@ -19570,7 +19560,7 @@
       </c>
       <c r="G428" s="10" t="inlineStr">
         <is>
-          <t>lighthouseferina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H428" s="11" t="inlineStr">
@@ -19612,7 +19602,7 @@
       </c>
       <c r="G429" s="10" t="inlineStr">
         <is>
-          <t>lighthousehengky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H429" s="11" t="inlineStr">
@@ -19654,7 +19644,7 @@
       </c>
       <c r="G430" s="10" t="inlineStr">
         <is>
-          <t>lighthouseikhsan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H430" s="11" t="inlineStr">
@@ -19696,7 +19686,7 @@
       </c>
       <c r="G431" s="10" t="inlineStr">
         <is>
-          <t>lighthousejan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H431" s="11" t="inlineStr">
@@ -19738,7 +19728,7 @@
       </c>
       <c r="G432" s="10" t="inlineStr">
         <is>
-          <t>lighthousejustina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H432" s="11" t="inlineStr">
@@ -19780,7 +19770,7 @@
       </c>
       <c r="G433" s="10" t="inlineStr">
         <is>
-          <t>lighthouselinda</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H433" s="11" t="inlineStr">
@@ -19818,7 +19808,7 @@
       </c>
       <c r="G434" s="10" t="inlineStr">
         <is>
-          <t>lighthousemellisa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H434" s="11" t="inlineStr">
@@ -19860,7 +19850,7 @@
       </c>
       <c r="G435" s="10" t="inlineStr">
         <is>
-          <t>lighthousemichelle</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H435" s="11" t="inlineStr">
@@ -19902,7 +19892,7 @@
       </c>
       <c r="G436" s="10" t="inlineStr">
         <is>
-          <t>lighthousepurwoko</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H436" s="11" t="inlineStr">
@@ -19944,7 +19934,7 @@
       </c>
       <c r="G437" s="10" t="inlineStr">
         <is>
-          <t>lighthouseradhyta</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H437" s="11" t="inlineStr">
@@ -19986,7 +19976,7 @@
       </c>
       <c r="G438" s="10" t="inlineStr">
         <is>
-          <t>lighthouseraditya</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H438" s="11" t="inlineStr">
@@ -20028,7 +20018,7 @@
       </c>
       <c r="G439" s="10" t="inlineStr">
         <is>
-          <t>lighthouserio</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H439" s="11" t="inlineStr">
@@ -20070,7 +20060,7 @@
       </c>
       <c r="G440" s="10" t="inlineStr">
         <is>
-          <t>lighthouserosita</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H440" s="11" t="inlineStr">
@@ -20112,7 +20102,7 @@
       </c>
       <c r="G441" s="10" t="inlineStr">
         <is>
-          <t>lighthousesamuel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H441" s="11" t="inlineStr">
@@ -20154,7 +20144,7 @@
       </c>
       <c r="G442" s="10" t="inlineStr">
         <is>
-          <t>lighthousesilvie</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H442" s="11" t="inlineStr">
@@ -20196,7 +20186,7 @@
       </c>
       <c r="G443" s="10" t="inlineStr">
         <is>
-          <t>lighthousesoebandriyo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H443" s="11" t="inlineStr">
@@ -20238,7 +20228,7 @@
       </c>
       <c r="G444" s="10" t="inlineStr">
         <is>
-          <t>lighthousesteve</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H444" s="11" t="inlineStr">
@@ -20280,7 +20270,7 @@
       </c>
       <c r="G445" s="10" t="inlineStr">
         <is>
-          <t>lighthouseteddy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H445" s="11" t="inlineStr">
@@ -20322,7 +20312,7 @@
       </c>
       <c r="G446" s="10" t="inlineStr">
         <is>
-          <t>lighthousevaderin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H446" s="11" t="inlineStr">
@@ -20364,7 +20354,7 @@
       </c>
       <c r="G447" s="10" t="inlineStr">
         <is>
-          <t>lighthousewidi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H447" s="11" t="inlineStr">
@@ -20406,7 +20396,7 @@
       </c>
       <c r="G448" s="10" t="inlineStr">
         <is>
-          <t>lighthouseyeanne</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H448" s="11" t="inlineStr">
@@ -20448,7 +20438,7 @@
       </c>
       <c r="G449" s="10" t="inlineStr">
         <is>
-          <t>lighthouseyoanita</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H449" s="11" t="inlineStr">
@@ -20490,7 +20480,7 @@
       </c>
       <c r="G450" s="10" t="inlineStr">
         <is>
-          <t>lighthouseyohanes</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H450" s="11" t="inlineStr">
@@ -20532,7 +20522,7 @@
       </c>
       <c r="G451" s="10" t="inlineStr">
         <is>
-          <t>lighthouseaning</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H451" s="11" t="inlineStr">
@@ -20574,7 +20564,7 @@
       </c>
       <c r="G452" s="10" t="inlineStr">
         <is>
-          <t>lighthouseanna</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H452" s="11" t="inlineStr">
@@ -20616,7 +20606,7 @@
       </c>
       <c r="G453" s="10" t="inlineStr">
         <is>
-          <t>lighthousejahja</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H453" s="11" t="inlineStr">
@@ -20658,7 +20648,7 @@
       </c>
       <c r="G454" s="10" t="inlineStr">
         <is>
-          <t>lighthousejourdan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H454" s="11" t="inlineStr">
@@ -20700,7 +20690,7 @@
       </c>
       <c r="G455" s="10" t="inlineStr">
         <is>
-          <t>lighthousemardiyah</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H455" s="11" t="inlineStr">
@@ -20742,7 +20732,7 @@
       </c>
       <c r="G456" s="10" t="inlineStr">
         <is>
-          <t>lighthouseridho</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H456" s="11" t="inlineStr">
@@ -20784,7 +20774,7 @@
       </c>
       <c r="G457" s="10" t="inlineStr">
         <is>
-          <t>lighthousevebrian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H457" s="11" t="inlineStr">
@@ -20826,7 +20816,7 @@
       </c>
       <c r="G458" s="10" t="inlineStr">
         <is>
-          <t>lighthousewisanggeni</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H458" s="11" t="inlineStr">
@@ -20864,7 +20854,7 @@
       </c>
       <c r="G459" s="10" t="inlineStr">
         <is>
-          <t>mambadavid</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H459" s="11" t="inlineStr">
@@ -20906,7 +20896,7 @@
       </c>
       <c r="G460" s="10" t="inlineStr">
         <is>
-          <t>magnifyagnes</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H460" s="11" t="inlineStr">
@@ -20944,7 +20934,7 @@
       </c>
       <c r="G461" s="10" t="inlineStr">
         <is>
-          <t>magnifyaldo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H461" s="11" t="inlineStr">
@@ -20986,7 +20976,7 @@
       </c>
       <c r="G462" s="10" t="inlineStr">
         <is>
-          <t>magnifyandrianto</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H462" s="11" t="inlineStr">
@@ -21028,7 +21018,7 @@
       </c>
       <c r="G463" s="10" t="inlineStr">
         <is>
-          <t>magnifyelsa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H463" s="11" t="inlineStr">
@@ -21051,12 +21041,12 @@
       <c r="C464" s="9" t="inlineStr"/>
       <c r="D464" s="9" t="inlineStr">
         <is>
-          <t>171AF-25675B540</t>
+          <t>171AF-25675B471</t>
         </is>
       </c>
       <c r="E464" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09637</t>
+          <t>NATCON-2026-09210</t>
         </is>
       </c>
       <c r="F464" s="10" t="inlineStr">
@@ -21066,7 +21056,7 @@
       </c>
       <c r="G464" s="10" t="inlineStr">
         <is>
-          <t>magnifyferly</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H464" s="11" t="inlineStr">
@@ -21089,12 +21079,12 @@
       <c r="C465" s="9" t="inlineStr"/>
       <c r="D465" s="9" t="inlineStr">
         <is>
-          <t>171AF-25675B471</t>
+          <t>171AF-25675B540</t>
         </is>
       </c>
       <c r="E465" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09210</t>
+          <t>NATCON-2026-09637</t>
         </is>
       </c>
       <c r="F465" s="10" t="inlineStr">
@@ -21104,7 +21094,7 @@
       </c>
       <c r="G465" s="10" t="inlineStr">
         <is>
-          <t>magnifyferly</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H465" s="11" t="inlineStr">
@@ -21146,7 +21136,7 @@
       </c>
       <c r="G466" s="10" t="inlineStr">
         <is>
-          <t>magnifyjessica</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H466" s="11" t="inlineStr">
@@ -21184,7 +21174,7 @@
       </c>
       <c r="G467" s="10" t="inlineStr">
         <is>
-          <t>magnifymarcel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H467" s="11" t="inlineStr">
@@ -21222,7 +21212,7 @@
       </c>
       <c r="G468" s="10" t="inlineStr">
         <is>
-          <t>magnifymaverick</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H468" s="11" t="inlineStr">
@@ -21260,7 +21250,7 @@
       </c>
       <c r="G469" s="10" t="inlineStr">
         <is>
-          <t>magnifymeidiyanto</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H469" s="11" t="inlineStr">
@@ -21302,7 +21292,7 @@
       </c>
       <c r="G470" s="10" t="inlineStr">
         <is>
-          <t>magnifyricardo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H470" s="11" t="inlineStr">
@@ -21344,7 +21334,7 @@
       </c>
       <c r="G471" s="10" t="inlineStr">
         <is>
-          <t>magnifyronald</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H471" s="11" t="inlineStr">
@@ -21382,7 +21372,7 @@
       </c>
       <c r="G472" s="10" t="inlineStr">
         <is>
-          <t>magnifyselina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H472" s="11" t="inlineStr">
@@ -21424,7 +21414,7 @@
       </c>
       <c r="G473" s="10" t="inlineStr">
         <is>
-          <t>magnifystephen</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H473" s="11" t="inlineStr">
@@ -21466,7 +21456,7 @@
       </c>
       <c r="G474" s="10" t="inlineStr">
         <is>
-          <t>magnifysteven</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H474" s="11" t="inlineStr">
@@ -21508,7 +21498,7 @@
       </c>
       <c r="G475" s="10" t="inlineStr">
         <is>
-          <t>magnifyveronica</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H475" s="11" t="inlineStr">
@@ -21550,7 +21540,7 @@
       </c>
       <c r="G476" s="10" t="inlineStr">
         <is>
-          <t>magnifyyoga</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H476" s="11" t="inlineStr">
@@ -21588,7 +21578,7 @@
       </c>
       <c r="G477" s="10" t="inlineStr">
         <is>
-          <t>magnifyyuanita</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H477" s="11" t="inlineStr">
@@ -21630,7 +21620,7 @@
       </c>
       <c r="G478" s="10" t="inlineStr">
         <is>
-          <t>magnifyrizki</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H478" s="11" t="inlineStr">
@@ -21672,7 +21662,7 @@
       </c>
       <c r="G479" s="10" t="inlineStr">
         <is>
-          <t>magnitudealbert</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H479" s="11" t="inlineStr">
@@ -21710,7 +21700,7 @@
       </c>
       <c r="G480" s="10" t="inlineStr">
         <is>
-          <t>magnitudearis</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H480" s="11" t="inlineStr">
@@ -21752,7 +21742,7 @@
       </c>
       <c r="G481" s="10" t="inlineStr">
         <is>
-          <t>magnitudebudy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H481" s="11" t="inlineStr">
@@ -21794,7 +21784,7 @@
       </c>
       <c r="G482" s="10" t="inlineStr">
         <is>
-          <t>magnitudedavid</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H482" s="11" t="inlineStr">
@@ -21836,7 +21826,7 @@
       </c>
       <c r="G483" s="10" t="inlineStr">
         <is>
-          <t>magnitudeeka</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H483" s="11" t="inlineStr">
@@ -21878,7 +21868,7 @@
       </c>
       <c r="G484" s="10" t="inlineStr">
         <is>
-          <t>magnitudeemanuel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H484" s="11" t="inlineStr">
@@ -21920,7 +21910,7 @@
       </c>
       <c r="G485" s="10" t="inlineStr">
         <is>
-          <t>magnitudeeric</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H485" s="11" t="inlineStr">
@@ -21958,7 +21948,7 @@
       </c>
       <c r="G486" s="10" t="inlineStr">
         <is>
-          <t>magnitudeevelyn</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H486" s="11" t="inlineStr">
@@ -22000,7 +21990,7 @@
       </c>
       <c r="G487" s="10" t="inlineStr">
         <is>
-          <t>magnitudefredi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H487" s="11" t="inlineStr">
@@ -22042,7 +22032,7 @@
       </c>
       <c r="G488" s="10" t="inlineStr">
         <is>
-          <t>magnitudeglenn</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H488" s="11" t="inlineStr">
@@ -22084,7 +22074,7 @@
       </c>
       <c r="G489" s="10" t="inlineStr">
         <is>
-          <t>magnitudehidayat</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H489" s="11" t="inlineStr">
@@ -22126,7 +22116,7 @@
       </c>
       <c r="G490" s="10" t="inlineStr">
         <is>
-          <t>magnitudeimelda</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H490" s="11" t="inlineStr">
@@ -22168,7 +22158,7 @@
       </c>
       <c r="G491" s="10" t="inlineStr">
         <is>
-          <t>magnitudejohanus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H491" s="11" t="inlineStr">
@@ -22210,7 +22200,7 @@
       </c>
       <c r="G492" s="10" t="inlineStr">
         <is>
-          <t>magnitudemeilya</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H492" s="11" t="inlineStr">
@@ -22252,7 +22242,7 @@
       </c>
       <c r="G493" s="10" t="inlineStr">
         <is>
-          <t>magnitudeni</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H493" s="11" t="inlineStr">
@@ -22290,7 +22280,7 @@
       </c>
       <c r="G494" s="10" t="inlineStr">
         <is>
-          <t>magnitudepaulus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H494" s="11" t="inlineStr">
@@ -22332,7 +22322,7 @@
       </c>
       <c r="G495" s="10" t="inlineStr">
         <is>
-          <t>magnituderabani</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H495" s="11" t="inlineStr">
@@ -22374,7 +22364,7 @@
       </c>
       <c r="G496" s="10" t="inlineStr">
         <is>
-          <t>magnituderia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H496" s="11" t="inlineStr">
@@ -22412,7 +22402,7 @@
       </c>
       <c r="G497" s="10" t="inlineStr">
         <is>
-          <t>magnituderudi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H497" s="11" t="inlineStr">
@@ -22450,7 +22440,7 @@
       </c>
       <c r="G498" s="10" t="inlineStr">
         <is>
-          <t>magnitudesendarius</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H498" s="11" t="inlineStr">
@@ -22488,7 +22478,7 @@
       </c>
       <c r="G499" s="10" t="inlineStr">
         <is>
-          <t>magnitudesendarius</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H499" s="11" t="inlineStr">
@@ -22530,7 +22520,7 @@
       </c>
       <c r="G500" s="10" t="inlineStr">
         <is>
-          <t>magnitudestefanny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H500" s="11" t="inlineStr">
@@ -22572,7 +22562,7 @@
       </c>
       <c r="G501" s="10" t="inlineStr">
         <is>
-          <t>magnitudesuhendra</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H501" s="11" t="inlineStr">
@@ -22614,7 +22604,7 @@
       </c>
       <c r="G502" s="10" t="inlineStr">
         <is>
-          <t>magnitudesungkono</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H502" s="11" t="inlineStr">
@@ -22656,7 +22646,7 @@
       </c>
       <c r="G503" s="10" t="inlineStr">
         <is>
-          <t>magnitudewiwiek</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H503" s="11" t="inlineStr">
@@ -22698,7 +22688,7 @@
       </c>
       <c r="G504" s="10" t="inlineStr">
         <is>
-          <t>magnitudeyosephine</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H504" s="11" t="inlineStr">
@@ -22740,7 +22730,7 @@
       </c>
       <c r="G505" s="10" t="inlineStr">
         <is>
-          <t>magnitudeyuliah</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H505" s="11" t="inlineStr">
@@ -22782,7 +22772,7 @@
       </c>
       <c r="G506" s="10" t="inlineStr">
         <is>
-          <t>magnitudeanisa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H506" s="11" t="inlineStr">
@@ -22824,7 +22814,7 @@
       </c>
       <c r="G507" s="10" t="inlineStr">
         <is>
-          <t>magnitudeeric</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H507" s="11" t="inlineStr">
@@ -22866,7 +22856,7 @@
       </c>
       <c r="G508" s="10" t="inlineStr">
         <is>
-          <t>mahardikaalbhert</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H508" s="11" t="inlineStr">
@@ -22908,7 +22898,7 @@
       </c>
       <c r="G509" s="10" t="inlineStr">
         <is>
-          <t>mahardikaandy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H509" s="11" t="inlineStr">
@@ -22950,7 +22940,7 @@
       </c>
       <c r="G510" s="10" t="inlineStr">
         <is>
-          <t>mahardikaawalia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H510" s="11" t="inlineStr">
@@ -22992,7 +22982,7 @@
       </c>
       <c r="G511" s="10" t="inlineStr">
         <is>
-          <t>mahardikaawan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H511" s="11" t="inlineStr">
@@ -23034,7 +23024,7 @@
       </c>
       <c r="G512" s="10" t="inlineStr">
         <is>
-          <t>mahardikabenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H512" s="11" t="inlineStr">
@@ -23076,7 +23066,7 @@
       </c>
       <c r="G513" s="10" t="inlineStr">
         <is>
-          <t>mahardikabobby</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H513" s="11" t="inlineStr">
@@ -23118,7 +23108,7 @@
       </c>
       <c r="G514" s="10" t="inlineStr">
         <is>
-          <t>mahardikaeunike</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H514" s="11" t="inlineStr">
@@ -23160,7 +23150,7 @@
       </c>
       <c r="G515" s="10" t="inlineStr">
         <is>
-          <t>mahardikaevan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H515" s="11" t="inlineStr">
@@ -23202,7 +23192,7 @@
       </c>
       <c r="G516" s="10" t="inlineStr">
         <is>
-          <t>mahardikafaradina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H516" s="11" t="inlineStr">
@@ -23244,7 +23234,7 @@
       </c>
       <c r="G517" s="10" t="inlineStr">
         <is>
-          <t>mahardikaglenn</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H517" s="11" t="inlineStr">
@@ -23286,7 +23276,7 @@
       </c>
       <c r="G518" s="10" t="inlineStr">
         <is>
-          <t>mahardikahari</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H518" s="11" t="inlineStr">
@@ -23328,7 +23318,7 @@
       </c>
       <c r="G519" s="10" t="inlineStr">
         <is>
-          <t>mahardikahenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H519" s="11" t="inlineStr">
@@ -23370,7 +23360,7 @@
       </c>
       <c r="G520" s="10" t="inlineStr">
         <is>
-          <t>mahardikaindah</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H520" s="11" t="inlineStr">
@@ -23412,7 +23402,7 @@
       </c>
       <c r="G521" s="10" t="inlineStr">
         <is>
-          <t>mahardikajosefa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H521" s="11" t="inlineStr">
@@ -23454,7 +23444,7 @@
       </c>
       <c r="G522" s="10" t="inlineStr">
         <is>
-          <t>mahardikalucky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H522" s="11" t="inlineStr">
@@ -23496,7 +23486,7 @@
       </c>
       <c r="G523" s="10" t="inlineStr">
         <is>
-          <t>mahardikamarcella</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H523" s="11" t="inlineStr">
@@ -23538,7 +23528,7 @@
       </c>
       <c r="G524" s="10" t="inlineStr">
         <is>
-          <t>mahardikamartina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H524" s="11" t="inlineStr">
@@ -23580,7 +23570,7 @@
       </c>
       <c r="G525" s="10" t="inlineStr">
         <is>
-          <t>mahardikaoscar</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H525" s="11" t="inlineStr">
@@ -23622,7 +23612,7 @@
       </c>
       <c r="G526" s="10" t="inlineStr">
         <is>
-          <t>mahardikaricardo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H526" s="11" t="inlineStr">
@@ -23664,7 +23654,7 @@
       </c>
       <c r="G527" s="10" t="inlineStr">
         <is>
-          <t>mahardikasatrio</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H527" s="11" t="inlineStr">
@@ -23706,7 +23696,7 @@
       </c>
       <c r="G528" s="10" t="inlineStr">
         <is>
-          <t>mahardikastella</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H528" s="11" t="inlineStr">
@@ -23748,7 +23738,7 @@
       </c>
       <c r="G529" s="10" t="inlineStr">
         <is>
-          <t>mahardikatheophillus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H529" s="11" t="inlineStr">
@@ -23790,7 +23780,7 @@
       </c>
       <c r="G530" s="10" t="inlineStr">
         <is>
-          <t>mahardikawilsary</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H530" s="11" t="inlineStr">
@@ -23832,7 +23822,7 @@
       </c>
       <c r="G531" s="10" t="inlineStr">
         <is>
-          <t>mahardikaerick</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H531" s="11" t="inlineStr">
@@ -23870,7 +23860,7 @@
       </c>
       <c r="G532" s="10" t="inlineStr">
         <is>
-          <t>mambakent</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H532" s="11" t="inlineStr">
@@ -23912,7 +23902,7 @@
       </c>
       <c r="G533" s="10" t="inlineStr">
         <is>
-          <t>matrixkarine</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H533" s="11" t="inlineStr">
@@ -23954,7 +23944,7 @@
       </c>
       <c r="G534" s="10" t="inlineStr">
         <is>
-          <t>matrixrosemary</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H534" s="11" t="inlineStr">
@@ -23996,7 +23986,7 @@
       </c>
       <c r="G535" s="10" t="inlineStr">
         <is>
-          <t>matrixmontkiararegionjennie</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H535" s="11" t="inlineStr">
@@ -24038,7 +24028,7 @@
       </c>
       <c r="G536" s="10" t="inlineStr">
         <is>
-          <t>multiplyandry</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H536" s="11" t="inlineStr">
@@ -24080,7 +24070,7 @@
       </c>
       <c r="G537" s="10" t="inlineStr">
         <is>
-          <t>multiplyandy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H537" s="11" t="inlineStr">
@@ -24122,7 +24112,7 @@
       </c>
       <c r="G538" s="10" t="inlineStr">
         <is>
-          <t>multiplybram</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H538" s="11" t="inlineStr">
@@ -24164,7 +24154,7 @@
       </c>
       <c r="G539" s="10" t="inlineStr">
         <is>
-          <t>multiplydudy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H539" s="11" t="inlineStr">
@@ -24206,7 +24196,7 @@
       </c>
       <c r="G540" s="10" t="inlineStr">
         <is>
-          <t>multiplyevan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H540" s="11" t="inlineStr">
@@ -24244,7 +24234,7 @@
       </c>
       <c r="G541" s="10" t="inlineStr">
         <is>
-          <t>multiplygladwin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H541" s="11" t="inlineStr">
@@ -24286,7 +24276,7 @@
       </c>
       <c r="G542" s="10" t="inlineStr">
         <is>
-          <t>multiplyhery</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H542" s="11" t="inlineStr">
@@ -24328,7 +24318,7 @@
       </c>
       <c r="G543" s="10" t="inlineStr">
         <is>
-          <t>multiplysu</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H543" s="11" t="inlineStr">
@@ -24370,7 +24360,7 @@
       </c>
       <c r="G544" s="10" t="inlineStr">
         <is>
-          <t>multiplytrisno</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H544" s="11" t="inlineStr">
@@ -24408,7 +24398,7 @@
       </c>
       <c r="G545" s="10" t="inlineStr">
         <is>
-          <t>multirichbadru</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H545" s="11" t="inlineStr">
@@ -24450,7 +24440,7 @@
       </c>
       <c r="G546" s="10" t="inlineStr">
         <is>
-          <t>multirichbayu</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H546" s="11" t="inlineStr">
@@ -24488,7 +24478,7 @@
       </c>
       <c r="G547" s="10" t="inlineStr">
         <is>
-          <t>multirichdani</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H547" s="11" t="inlineStr">
@@ -24530,7 +24520,7 @@
       </c>
       <c r="G548" s="10" t="inlineStr">
         <is>
-          <t>multiricheddy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H548" s="11" t="inlineStr">
@@ -24572,7 +24562,7 @@
       </c>
       <c r="G549" s="10" t="inlineStr">
         <is>
-          <t>multirichghilmansyah</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H549" s="11" t="inlineStr">
@@ -24599,22 +24589,22 @@
       </c>
       <c r="D550" s="9" t="inlineStr">
         <is>
-          <t>16C6C-24AEA0229</t>
+          <t>16C6C-23AD18319</t>
         </is>
       </c>
       <c r="E550" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09424</t>
+          <t>NATCON-2026-09479</t>
         </is>
       </c>
       <c r="F550" s="10" t="inlineStr">
         <is>
-          <t>zaldywirjawan@gmail.com</t>
+          <t>zaldywirjaean@gmail.com</t>
         </is>
       </c>
       <c r="G550" s="10" t="inlineStr">
         <is>
-          <t>multirichzaldy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H550" s="11" t="inlineStr">
@@ -24641,22 +24631,22 @@
       </c>
       <c r="D551" s="9" t="inlineStr">
         <is>
-          <t>16C6C-23AD18319</t>
+          <t>16C6C-24AEA0229</t>
         </is>
       </c>
       <c r="E551" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09479</t>
+          <t>NATCON-2026-09424</t>
         </is>
       </c>
       <c r="F551" s="10" t="inlineStr">
         <is>
-          <t>zaldywirjaean@gmail.com</t>
+          <t>zaldywirjawan@gmail.com</t>
         </is>
       </c>
       <c r="G551" s="10" t="inlineStr">
         <is>
-          <t>multirichzaldy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H551" s="11" t="inlineStr">
@@ -24698,7 +24688,7 @@
       </c>
       <c r="G552" s="10" t="inlineStr">
         <is>
-          <t>northstarlulu</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H552" s="11" t="inlineStr">
@@ -24740,7 +24730,7 @@
       </c>
       <c r="G553" s="10" t="inlineStr">
         <is>
-          <t>northstarokky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H553" s="11" t="inlineStr">
@@ -24782,7 +24772,7 @@
       </c>
       <c r="G554" s="10" t="inlineStr">
         <is>
-          <t>northstarvicky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H554" s="11" t="inlineStr">
@@ -24824,7 +24814,7 @@
       </c>
       <c r="G555" s="10" t="inlineStr">
         <is>
-          <t>nusantaraadrian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H555" s="11" t="inlineStr">
@@ -24866,7 +24856,7 @@
       </c>
       <c r="G556" s="10" t="inlineStr">
         <is>
-          <t>nusantaraasrini</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H556" s="11" t="inlineStr">
@@ -24908,7 +24898,7 @@
       </c>
       <c r="G557" s="10" t="inlineStr">
         <is>
-          <t>nusantarachilviane</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H557" s="11" t="inlineStr">
@@ -24950,7 +24940,7 @@
       </c>
       <c r="G558" s="10" t="inlineStr">
         <is>
-          <t>nusantarafelix</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H558" s="11" t="inlineStr">
@@ -24992,7 +24982,7 @@
       </c>
       <c r="G559" s="10" t="inlineStr">
         <is>
-          <t>nusantarahenry</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H559" s="11" t="inlineStr">
@@ -25034,7 +25024,7 @@
       </c>
       <c r="G560" s="10" t="inlineStr">
         <is>
-          <t>nusantarajoseph</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H560" s="11" t="inlineStr">
@@ -25076,7 +25066,7 @@
       </c>
       <c r="G561" s="10" t="inlineStr">
         <is>
-          <t>nusantarakarla</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H561" s="11" t="inlineStr">
@@ -25118,7 +25108,7 @@
       </c>
       <c r="G562" s="10" t="inlineStr">
         <is>
-          <t>nusantaramelvania</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H562" s="11" t="inlineStr">
@@ -25160,7 +25150,7 @@
       </c>
       <c r="G563" s="10" t="inlineStr">
         <is>
-          <t>nusantaranicodemus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H563" s="11" t="inlineStr">
@@ -25202,7 +25192,7 @@
       </c>
       <c r="G564" s="10" t="inlineStr">
         <is>
-          <t>nusantaraopa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H564" s="11" t="inlineStr">
@@ -25244,7 +25234,7 @@
       </c>
       <c r="G565" s="10" t="inlineStr">
         <is>
-          <t>nusantararhede</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H565" s="11" t="inlineStr">
@@ -25282,7 +25272,7 @@
       </c>
       <c r="G566" s="10" t="inlineStr">
         <is>
-          <t>positiveli</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H566" s="11" t="inlineStr">
@@ -25320,7 +25310,7 @@
       </c>
       <c r="G567" s="10" t="inlineStr">
         <is>
-          <t>passionadjie</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H567" s="11" t="inlineStr">
@@ -25358,7 +25348,7 @@
       </c>
       <c r="G568" s="10" t="inlineStr">
         <is>
-          <t>passionamanda</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H568" s="11" t="inlineStr">
@@ -25400,7 +25390,7 @@
       </c>
       <c r="G569" s="10" t="inlineStr">
         <is>
-          <t>passionandrew</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H569" s="11" t="inlineStr">
@@ -25442,7 +25432,7 @@
       </c>
       <c r="G570" s="10" t="inlineStr">
         <is>
-          <t>passionayudya</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H570" s="11" t="inlineStr">
@@ -25484,7 +25474,7 @@
       </c>
       <c r="G571" s="10" t="inlineStr">
         <is>
-          <t>passionbrilliant</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H571" s="11" t="inlineStr">
@@ -25526,7 +25516,7 @@
       </c>
       <c r="G572" s="10" t="inlineStr">
         <is>
-          <t>passiondenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H572" s="11" t="inlineStr">
@@ -25568,7 +25558,7 @@
       </c>
       <c r="G573" s="10" t="inlineStr">
         <is>
-          <t>passiondevina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H573" s="11" t="inlineStr">
@@ -25610,7 +25600,7 @@
       </c>
       <c r="G574" s="10" t="inlineStr">
         <is>
-          <t>passionemilia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H574" s="11" t="inlineStr">
@@ -25648,7 +25638,7 @@
       </c>
       <c r="G575" s="10" t="inlineStr">
         <is>
-          <t>passionfifi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H575" s="11" t="inlineStr">
@@ -25690,7 +25680,7 @@
       </c>
       <c r="G576" s="10" t="inlineStr">
         <is>
-          <t>passionhioe</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H576" s="11" t="inlineStr">
@@ -25732,7 +25722,7 @@
       </c>
       <c r="G577" s="10" t="inlineStr">
         <is>
-          <t>passionihsan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H577" s="11" t="inlineStr">
@@ -25774,7 +25764,7 @@
       </c>
       <c r="G578" s="10" t="inlineStr">
         <is>
-          <t>passionleonard</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H578" s="11" t="inlineStr">
@@ -25812,7 +25802,7 @@
       </c>
       <c r="G579" s="10" t="inlineStr">
         <is>
-          <t>passionlitani</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H579" s="11" t="inlineStr">
@@ -25854,7 +25844,7 @@
       </c>
       <c r="G580" s="10" t="inlineStr">
         <is>
-          <t>passionmartin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H580" s="11" t="inlineStr">
@@ -25896,7 +25886,7 @@
       </c>
       <c r="G581" s="10" t="inlineStr">
         <is>
-          <t>passionmelvrin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H581" s="11" t="inlineStr">
@@ -25934,7 +25924,7 @@
       </c>
       <c r="G582" s="10" t="inlineStr">
         <is>
-          <t>passionolivia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H582" s="11" t="inlineStr">
@@ -25976,7 +25966,7 @@
       </c>
       <c r="G583" s="10" t="inlineStr">
         <is>
-          <t>passionrafel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H583" s="11" t="inlineStr">
@@ -26018,7 +26008,7 @@
       </c>
       <c r="G584" s="10" t="inlineStr">
         <is>
-          <t>passionricky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H584" s="11" t="inlineStr">
@@ -26060,7 +26050,7 @@
       </c>
       <c r="G585" s="10" t="inlineStr">
         <is>
-          <t>passionryan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H585" s="11" t="inlineStr">
@@ -26102,7 +26092,7 @@
       </c>
       <c r="G586" s="10" t="inlineStr">
         <is>
-          <t>passionsusiana</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H586" s="11" t="inlineStr">
@@ -26140,7 +26130,7 @@
       </c>
       <c r="G587" s="10" t="inlineStr">
         <is>
-          <t>passiontheresia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H587" s="11" t="inlineStr">
@@ -26182,7 +26172,7 @@
       </c>
       <c r="G588" s="10" t="inlineStr">
         <is>
-          <t>passiontiara</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H588" s="11" t="inlineStr">
@@ -26224,7 +26214,7 @@
       </c>
       <c r="G589" s="10" t="inlineStr">
         <is>
-          <t>passionyunita</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H589" s="11" t="inlineStr">
@@ -26266,7 +26256,7 @@
       </c>
       <c r="G590" s="10" t="inlineStr">
         <is>
-          <t>pinnaclebilly</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H590" s="11" t="inlineStr">
@@ -26308,7 +26298,7 @@
       </c>
       <c r="G591" s="10" t="inlineStr">
         <is>
-          <t>pinnaclemelvin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H591" s="11" t="inlineStr">
@@ -26350,7 +26340,7 @@
       </c>
       <c r="G592" s="10" t="inlineStr">
         <is>
-          <t>pinnaclesally</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H592" s="11" t="inlineStr">
@@ -26392,7 +26382,7 @@
       </c>
       <c r="G593" s="10" t="inlineStr">
         <is>
-          <t>pinnaclestephen</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H593" s="11" t="inlineStr">
@@ -26434,7 +26424,7 @@
       </c>
       <c r="G594" s="10" t="inlineStr">
         <is>
-          <t>pioneeradam</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H594" s="11" t="inlineStr">
@@ -26476,7 +26466,7 @@
       </c>
       <c r="G595" s="10" t="inlineStr">
         <is>
-          <t>pioneerarnold</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H595" s="11" t="inlineStr">
@@ -26518,7 +26508,7 @@
       </c>
       <c r="G596" s="10" t="inlineStr">
         <is>
-          <t>pioneerbernard</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H596" s="11" t="inlineStr">
@@ -26560,7 +26550,7 @@
       </c>
       <c r="G597" s="10" t="inlineStr">
         <is>
-          <t>pioneerchia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H597" s="11" t="inlineStr">
@@ -26602,7 +26592,7 @@
       </c>
       <c r="G598" s="10" t="inlineStr">
         <is>
-          <t>pioneerdimas</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H598" s="11" t="inlineStr">
@@ -26644,7 +26634,7 @@
       </c>
       <c r="G599" s="10" t="inlineStr">
         <is>
-          <t>pioneerdody</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H599" s="11" t="inlineStr">
@@ -26686,7 +26676,7 @@
       </c>
       <c r="G600" s="10" t="inlineStr">
         <is>
-          <t>pioneergita</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H600" s="11" t="inlineStr">
@@ -26724,7 +26714,7 @@
       </c>
       <c r="G601" s="10" t="inlineStr">
         <is>
-          <t>pioneerhenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H601" s="11" t="inlineStr">
@@ -26766,7 +26756,7 @@
       </c>
       <c r="G602" s="10" t="inlineStr">
         <is>
-          <t>pioneerhenry</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H602" s="11" t="inlineStr">
@@ -26808,7 +26798,7 @@
       </c>
       <c r="G603" s="10" t="inlineStr">
         <is>
-          <t>pioneerirene</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H603" s="11" t="inlineStr">
@@ -26850,7 +26840,7 @@
       </c>
       <c r="G604" s="10" t="inlineStr">
         <is>
-          <t>pioneerjimmy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H604" s="11" t="inlineStr">
@@ -26888,7 +26878,7 @@
       </c>
       <c r="G605" s="10" t="inlineStr">
         <is>
-          <t>pioneerjohn</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H605" s="11" t="inlineStr">
@@ -26930,7 +26920,7 @@
       </c>
       <c r="G606" s="10" t="inlineStr">
         <is>
-          <t>pioneerkusno</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H606" s="11" t="inlineStr">
@@ -26972,7 +26962,7 @@
       </c>
       <c r="G607" s="10" t="inlineStr">
         <is>
-          <t>pioneermetta</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H607" s="11" t="inlineStr">
@@ -27014,7 +27004,7 @@
       </c>
       <c r="G608" s="10" t="inlineStr">
         <is>
-          <t>pioneermung</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H608" s="11" t="inlineStr">
@@ -27056,7 +27046,7 @@
       </c>
       <c r="G609" s="10" t="inlineStr">
         <is>
-          <t>pioneerraka</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H609" s="11" t="inlineStr">
@@ -27098,7 +27088,7 @@
       </c>
       <c r="G610" s="10" t="inlineStr">
         <is>
-          <t>pioneerriama</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H610" s="11" t="inlineStr">
@@ -27140,7 +27130,7 @@
       </c>
       <c r="G611" s="10" t="inlineStr">
         <is>
-          <t>pioneersamuel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H611" s="11" t="inlineStr">
@@ -27182,7 +27172,7 @@
       </c>
       <c r="G612" s="10" t="inlineStr">
         <is>
-          <t>pioneersaniah</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H612" s="11" t="inlineStr">
@@ -27224,7 +27214,7 @@
       </c>
       <c r="G613" s="10" t="inlineStr">
         <is>
-          <t>pioneersetiawati</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H613" s="11" t="inlineStr">
@@ -27266,7 +27256,7 @@
       </c>
       <c r="G614" s="10" t="inlineStr">
         <is>
-          <t>pioneersilvy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H614" s="11" t="inlineStr">
@@ -27308,7 +27298,7 @@
       </c>
       <c r="G615" s="10" t="inlineStr">
         <is>
-          <t>pioneertri</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H615" s="11" t="inlineStr">
@@ -27350,7 +27340,7 @@
       </c>
       <c r="G616" s="10" t="inlineStr">
         <is>
-          <t>pioneervivi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H616" s="11" t="inlineStr">
@@ -27388,7 +27378,7 @@
       </c>
       <c r="G617" s="10" t="inlineStr">
         <is>
-          <t>pioneerwily</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H617" s="11" t="inlineStr">
@@ -27430,7 +27420,7 @@
       </c>
       <c r="G618" s="10" t="inlineStr">
         <is>
-          <t>pioneerzelfrich</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H618" s="11" t="inlineStr">
@@ -27472,7 +27462,7 @@
       </c>
       <c r="G619" s="10" t="inlineStr">
         <is>
-          <t>pioneerfelix</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H619" s="11" t="inlineStr">
@@ -27514,7 +27504,7 @@
       </c>
       <c r="G620" s="10" t="inlineStr">
         <is>
-          <t>pioneersamuel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H620" s="11" t="inlineStr">
@@ -27556,7 +27546,7 @@
       </c>
       <c r="G621" s="10" t="inlineStr">
         <is>
-          <t>pioneertoni</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H621" s="11" t="inlineStr">
@@ -27598,7 +27588,7 @@
       </c>
       <c r="G622" s="10" t="inlineStr">
         <is>
-          <t>premierbeh</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H622" s="11" t="inlineStr">
@@ -27640,7 +27630,7 @@
       </c>
       <c r="G623" s="10" t="inlineStr">
         <is>
-          <t>premierchoon</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H623" s="11" t="inlineStr">
@@ -27682,7 +27672,7 @@
       </c>
       <c r="G624" s="10" t="inlineStr">
         <is>
-          <t>premierdr.</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H624" s="11" t="inlineStr">
@@ -27720,7 +27710,7 @@
       </c>
       <c r="G625" s="10" t="inlineStr">
         <is>
-          <t>prestigeandrew</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H625" s="11" t="inlineStr">
@@ -27758,7 +27748,7 @@
       </c>
       <c r="G626" s="10" t="inlineStr">
         <is>
-          <t>prestigecaesario</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H626" s="11" t="inlineStr">
@@ -27796,7 +27786,7 @@
       </c>
       <c r="G627" s="10" t="inlineStr">
         <is>
-          <t>prestigedarwin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H627" s="11" t="inlineStr">
@@ -27838,7 +27828,7 @@
       </c>
       <c r="G628" s="10" t="inlineStr">
         <is>
-          <t>prestigeelizabeth</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H628" s="11" t="inlineStr">
@@ -27876,7 +27866,7 @@
       </c>
       <c r="G629" s="10" t="inlineStr">
         <is>
-          <t>prestigefebrizky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H629" s="11" t="inlineStr">
@@ -27914,7 +27904,7 @@
       </c>
       <c r="G630" s="10" t="inlineStr">
         <is>
-          <t>prestigegaudensius</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H630" s="11" t="inlineStr">
@@ -27956,7 +27946,7 @@
       </c>
       <c r="G631" s="10" t="inlineStr">
         <is>
-          <t>prestigeharianto</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H631" s="11" t="inlineStr">
@@ -27994,7 +27984,7 @@
       </c>
       <c r="G632" s="10" t="inlineStr">
         <is>
-          <t>prestigeherry</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H632" s="11" t="inlineStr">
@@ -28032,7 +28022,7 @@
       </c>
       <c r="G633" s="10" t="inlineStr">
         <is>
-          <t>prestigejessica</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H633" s="11" t="inlineStr">
@@ -28074,7 +28064,7 @@
       </c>
       <c r="G634" s="10" t="inlineStr">
         <is>
-          <t>prestigejudo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H634" s="11" t="inlineStr">
@@ -28112,7 +28102,7 @@
       </c>
       <c r="G635" s="10" t="inlineStr">
         <is>
-          <t>prestigejulius</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H635" s="11" t="inlineStr">
@@ -28150,7 +28140,7 @@
       </c>
       <c r="G636" s="10" t="inlineStr">
         <is>
-          <t>prestigemaulana</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H636" s="11" t="inlineStr">
@@ -28188,7 +28178,7 @@
       </c>
       <c r="G637" s="10" t="inlineStr">
         <is>
-          <t>prestigenabiel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H637" s="11" t="inlineStr">
@@ -28226,7 +28216,7 @@
       </c>
       <c r="G638" s="10" t="inlineStr">
         <is>
-          <t>prestigeoktovianus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H638" s="11" t="inlineStr">
@@ -28264,7 +28254,7 @@
       </c>
       <c r="G639" s="10" t="inlineStr">
         <is>
-          <t>prestigerama</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H639" s="11" t="inlineStr">
@@ -28302,7 +28292,7 @@
       </c>
       <c r="G640" s="10" t="inlineStr">
         <is>
-          <t>prestigerendy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H640" s="11" t="inlineStr">
@@ -28340,7 +28330,7 @@
       </c>
       <c r="G641" s="10" t="inlineStr">
         <is>
-          <t>prestigericky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H641" s="11" t="inlineStr">
@@ -28378,7 +28368,7 @@
       </c>
       <c r="G642" s="10" t="inlineStr">
         <is>
-          <t>prestigeronald</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H642" s="11" t="inlineStr">
@@ -28416,7 +28406,7 @@
       </c>
       <c r="G643" s="10" t="inlineStr">
         <is>
-          <t>prestigeserenita</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H643" s="11" t="inlineStr">
@@ -28454,7 +28444,7 @@
       </c>
       <c r="G644" s="10" t="inlineStr">
         <is>
-          <t>prestigestevanus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H644" s="11" t="inlineStr">
@@ -28492,7 +28482,7 @@
       </c>
       <c r="G645" s="10" t="inlineStr">
         <is>
-          <t>prestigesteven</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H645" s="11" t="inlineStr">
@@ -28534,7 +28524,7 @@
       </c>
       <c r="G646" s="10" t="inlineStr">
         <is>
-          <t>prestigetitin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H646" s="11" t="inlineStr">
@@ -28576,7 +28566,7 @@
       </c>
       <c r="G647" s="10" t="inlineStr">
         <is>
-          <t>prestigeviolison</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H647" s="11" t="inlineStr">
@@ -28614,7 +28604,7 @@
       </c>
       <c r="G648" s="10" t="inlineStr">
         <is>
-          <t>prestigevioletanada</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H648" s="11" t="inlineStr">
@@ -28656,7 +28646,7 @@
       </c>
       <c r="G649" s="10" t="inlineStr">
         <is>
-          <t>riseandri</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H649" s="11" t="inlineStr">
@@ -28698,7 +28688,7 @@
       </c>
       <c r="G650" s="10" t="inlineStr">
         <is>
-          <t>riseanselmus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H650" s="11" t="inlineStr">
@@ -28740,7 +28730,7 @@
       </c>
       <c r="G651" s="10" t="inlineStr">
         <is>
-          <t>risebilly</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H651" s="11" t="inlineStr">
@@ -28782,7 +28772,7 @@
       </c>
       <c r="G652" s="10" t="inlineStr">
         <is>
-          <t>risedax</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H652" s="11" t="inlineStr">
@@ -28824,7 +28814,7 @@
       </c>
       <c r="G653" s="10" t="inlineStr">
         <is>
-          <t>risedhany</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H653" s="11" t="inlineStr">
@@ -28866,7 +28856,7 @@
       </c>
       <c r="G654" s="10" t="inlineStr">
         <is>
-          <t>risekevin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H654" s="11" t="inlineStr">
@@ -28908,7 +28898,7 @@
       </c>
       <c r="G655" s="10" t="inlineStr">
         <is>
-          <t>risemartha</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H655" s="11" t="inlineStr">
@@ -28950,7 +28940,7 @@
       </c>
       <c r="G656" s="10" t="inlineStr">
         <is>
-          <t>riseneysa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H656" s="11" t="inlineStr">
@@ -28992,7 +28982,7 @@
       </c>
       <c r="G657" s="10" t="inlineStr">
         <is>
-          <t>riserio</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H657" s="11" t="inlineStr">
@@ -29034,7 +29024,7 @@
       </c>
       <c r="G658" s="10" t="inlineStr">
         <is>
-          <t>riserizka</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H658" s="11" t="inlineStr">
@@ -29076,7 +29066,7 @@
       </c>
       <c r="G659" s="10" t="inlineStr">
         <is>
-          <t>risesilvia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H659" s="11" t="inlineStr">
@@ -29118,7 +29108,7 @@
       </c>
       <c r="G660" s="10" t="inlineStr">
         <is>
-          <t>riseteguh</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H660" s="11" t="inlineStr">
@@ -29160,7 +29150,7 @@
       </c>
       <c r="G661" s="10" t="inlineStr">
         <is>
-          <t>riseenrico</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H661" s="11" t="inlineStr">
@@ -29198,7 +29188,7 @@
       </c>
       <c r="G662" s="10" t="inlineStr">
         <is>
-          <t>shenzhenuniondereks</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H662" s="11" t="inlineStr">
@@ -29240,7 +29230,7 @@
       </c>
       <c r="G663" s="10" t="inlineStr">
         <is>
-          <t>souqarabiasharifah</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H663" s="11" t="inlineStr">
@@ -29278,7 +29268,7 @@
       </c>
       <c r="G664" s="10" t="inlineStr">
         <is>
-          <t>szalliancexiaofen</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H664" s="11" t="inlineStr">
@@ -29320,7 +29310,7 @@
       </c>
       <c r="G665" s="10" t="inlineStr">
         <is>
-          <t>shahalamdashangonlinesebastian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H665" s="11" t="inlineStr">
@@ -29362,7 +29352,7 @@
       </c>
       <c r="G666" s="10" t="inlineStr">
         <is>
-          <t>sovereignalinne</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H666" s="11" t="inlineStr">
@@ -29404,7 +29394,7 @@
       </c>
       <c r="G667" s="10" t="inlineStr">
         <is>
-          <t>sovereignangelina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H667" s="11" t="inlineStr">
@@ -29446,7 +29436,7 @@
       </c>
       <c r="G668" s="10" t="inlineStr">
         <is>
-          <t>sovereignangelina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H668" s="11" t="inlineStr">
@@ -29488,7 +29478,7 @@
       </c>
       <c r="G669" s="10" t="inlineStr">
         <is>
-          <t>sovereigndarshan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H669" s="11" t="inlineStr">
@@ -29530,7 +29520,7 @@
       </c>
       <c r="G670" s="10" t="inlineStr">
         <is>
-          <t>sovereignedhy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H670" s="11" t="inlineStr">
@@ -29572,7 +29562,7 @@
       </c>
       <c r="G671" s="10" t="inlineStr">
         <is>
-          <t>sovereignfritz</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H671" s="11" t="inlineStr">
@@ -29614,7 +29604,7 @@
       </c>
       <c r="G672" s="10" t="inlineStr">
         <is>
-          <t>sovereigngiovannia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H672" s="11" t="inlineStr">
@@ -29656,7 +29646,7 @@
       </c>
       <c r="G673" s="10" t="inlineStr">
         <is>
-          <t>sovereignira</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H673" s="11" t="inlineStr">
@@ -29698,7 +29688,7 @@
       </c>
       <c r="G674" s="10" t="inlineStr">
         <is>
-          <t>sovereigniwan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H674" s="11" t="inlineStr">
@@ -29740,7 +29730,7 @@
       </c>
       <c r="G675" s="10" t="inlineStr">
         <is>
-          <t>sovereignkenrick</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H675" s="11" t="inlineStr">
@@ -29782,7 +29772,7 @@
       </c>
       <c r="G676" s="10" t="inlineStr">
         <is>
-          <t>sovereignkeshia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H676" s="11" t="inlineStr">
@@ -29824,7 +29814,7 @@
       </c>
       <c r="G677" s="10" t="inlineStr">
         <is>
-          <t>sovereignmartin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H677" s="11" t="inlineStr">
@@ -29862,7 +29852,7 @@
       </c>
       <c r="G678" s="10" t="inlineStr">
         <is>
-          <t>sovereignmizan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H678" s="11" t="inlineStr">
@@ -29904,7 +29894,7 @@
       </c>
       <c r="G679" s="10" t="inlineStr">
         <is>
-          <t>sovereignmuliadi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H679" s="11" t="inlineStr">
@@ -29946,7 +29936,7 @@
       </c>
       <c r="G680" s="10" t="inlineStr">
         <is>
-          <t>sovereignmulyono</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H680" s="11" t="inlineStr">
@@ -29988,7 +29978,7 @@
       </c>
       <c r="G681" s="10" t="inlineStr">
         <is>
-          <t>sovereignnico</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H681" s="11" t="inlineStr">
@@ -30030,7 +30020,7 @@
       </c>
       <c r="G682" s="10" t="inlineStr">
         <is>
-          <t>sovereignsetiani</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H682" s="11" t="inlineStr">
@@ -30068,7 +30058,7 @@
       </c>
       <c r="G683" s="10" t="inlineStr">
         <is>
-          <t>sovereignsuyanti</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H683" s="11" t="inlineStr">
@@ -30110,7 +30100,7 @@
       </c>
       <c r="G684" s="10" t="inlineStr">
         <is>
-          <t>sovereignyulia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H684" s="11" t="inlineStr">
@@ -30152,7 +30142,7 @@
       </c>
       <c r="G685" s="10" t="inlineStr">
         <is>
-          <t>starandrew</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H685" s="11" t="inlineStr">
@@ -30194,7 +30184,7 @@
       </c>
       <c r="G686" s="10" t="inlineStr">
         <is>
-          <t>stararya</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H686" s="11" t="inlineStr">
@@ -30236,7 +30226,7 @@
       </c>
       <c r="G687" s="10" t="inlineStr">
         <is>
-          <t>starazhary</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H687" s="11" t="inlineStr">
@@ -30278,7 +30268,7 @@
       </c>
       <c r="G688" s="10" t="inlineStr">
         <is>
-          <t>starchristian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H688" s="11" t="inlineStr">
@@ -30320,7 +30310,7 @@
       </c>
       <c r="G689" s="10" t="inlineStr">
         <is>
-          <t>starcindy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H689" s="11" t="inlineStr">
@@ -30362,7 +30352,7 @@
       </c>
       <c r="G690" s="10" t="inlineStr">
         <is>
-          <t>stardaniel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H690" s="11" t="inlineStr">
@@ -30404,7 +30394,7 @@
       </c>
       <c r="G691" s="10" t="inlineStr">
         <is>
-          <t>stardavid</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H691" s="11" t="inlineStr">
@@ -30446,7 +30436,7 @@
       </c>
       <c r="G692" s="10" t="inlineStr">
         <is>
-          <t>starderek</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H692" s="11" t="inlineStr">
@@ -30488,7 +30478,7 @@
       </c>
       <c r="G693" s="10" t="inlineStr">
         <is>
-          <t>stardonnel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H693" s="11" t="inlineStr">
@@ -30530,7 +30520,7 @@
       </c>
       <c r="G694" s="10" t="inlineStr">
         <is>
-          <t>stardonny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H694" s="11" t="inlineStr">
@@ -30572,7 +30562,7 @@
       </c>
       <c r="G695" s="10" t="inlineStr">
         <is>
-          <t>staredward</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H695" s="11" t="inlineStr">
@@ -30614,7 +30604,7 @@
       </c>
       <c r="G696" s="10" t="inlineStr">
         <is>
-          <t>starenra</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H696" s="11" t="inlineStr">
@@ -30656,7 +30646,7 @@
       </c>
       <c r="G697" s="10" t="inlineStr">
         <is>
-          <t>starevelyn</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H697" s="11" t="inlineStr">
@@ -30698,7 +30688,7 @@
       </c>
       <c r="G698" s="10" t="inlineStr">
         <is>
-          <t>starfabianus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H698" s="11" t="inlineStr">
@@ -30740,7 +30730,7 @@
       </c>
       <c r="G699" s="10" t="inlineStr">
         <is>
-          <t>starfararine</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H699" s="11" t="inlineStr">
@@ -30782,7 +30772,7 @@
       </c>
       <c r="G700" s="10" t="inlineStr">
         <is>
-          <t>starfernando</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H700" s="11" t="inlineStr">
@@ -30824,7 +30814,7 @@
       </c>
       <c r="G701" s="10" t="inlineStr">
         <is>
-          <t>stargeraldine</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H701" s="11" t="inlineStr">
@@ -30866,7 +30856,7 @@
       </c>
       <c r="G702" s="10" t="inlineStr">
         <is>
-          <t>starjun</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H702" s="11" t="inlineStr">
@@ -30908,7 +30898,7 @@
       </c>
       <c r="G703" s="10" t="inlineStr">
         <is>
-          <t>starjames</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H703" s="11" t="inlineStr">
@@ -30950,7 +30940,7 @@
       </c>
       <c r="G704" s="10" t="inlineStr">
         <is>
-          <t>starjonathan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H704" s="11" t="inlineStr">
@@ -30988,7 +30978,7 @@
       </c>
       <c r="G705" s="10" t="inlineStr">
         <is>
-          <t>starlawrence</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H705" s="11" t="inlineStr">
@@ -31030,7 +31020,7 @@
       </c>
       <c r="G706" s="10" t="inlineStr">
         <is>
-          <t>starleo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H706" s="11" t="inlineStr">
@@ -31072,7 +31062,7 @@
       </c>
       <c r="G707" s="10" t="inlineStr">
         <is>
-          <t>starleonard</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H707" s="11" t="inlineStr">
@@ -31114,7 +31104,7 @@
       </c>
       <c r="G708" s="10" t="inlineStr">
         <is>
-          <t>starleonard</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H708" s="11" t="inlineStr">
@@ -31141,12 +31131,12 @@
       </c>
       <c r="D709" s="9" t="inlineStr">
         <is>
-          <t>171AF-25672CF85</t>
+          <t>171AF-25672D024</t>
         </is>
       </c>
       <c r="E709" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09157</t>
+          <t>NATCON-2026-09458</t>
         </is>
       </c>
       <c r="F709" s="10" t="inlineStr">
@@ -31156,7 +31146,7 @@
       </c>
       <c r="G709" s="10" t="inlineStr">
         <is>
-          <t>starleonard</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H709" s="11" t="inlineStr">
@@ -31183,12 +31173,12 @@
       </c>
       <c r="D710" s="9" t="inlineStr">
         <is>
-          <t>171AF-25672D024</t>
+          <t>171AF-25672CF85</t>
         </is>
       </c>
       <c r="E710" s="9" t="inlineStr">
         <is>
-          <t>NATCON-2026-09458</t>
+          <t>NATCON-2026-09157</t>
         </is>
       </c>
       <c r="F710" s="10" t="inlineStr">
@@ -31198,7 +31188,7 @@
       </c>
       <c r="G710" s="10" t="inlineStr">
         <is>
-          <t>starleonard</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H710" s="11" t="inlineStr">
@@ -31236,7 +31226,7 @@
       </c>
       <c r="G711" s="10" t="inlineStr">
         <is>
-          <t>starmatheo</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H711" s="11" t="inlineStr">
@@ -31278,7 +31268,7 @@
       </c>
       <c r="G712" s="10" t="inlineStr">
         <is>
-          <t>starmegahwati</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H712" s="11" t="inlineStr">
@@ -31320,7 +31310,7 @@
       </c>
       <c r="G713" s="10" t="inlineStr">
         <is>
-          <t>starnicolaas</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H713" s="11" t="inlineStr">
@@ -31362,7 +31352,7 @@
       </c>
       <c r="G714" s="10" t="inlineStr">
         <is>
-          <t>starnicolaas</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H714" s="11" t="inlineStr">
@@ -31404,7 +31394,7 @@
       </c>
       <c r="G715" s="10" t="inlineStr">
         <is>
-          <t>starolga</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H715" s="11" t="inlineStr">
@@ -31446,7 +31436,7 @@
       </c>
       <c r="G716" s="10" t="inlineStr">
         <is>
-          <t>starpuji</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H716" s="11" t="inlineStr">
@@ -31488,7 +31478,7 @@
       </c>
       <c r="G717" s="10" t="inlineStr">
         <is>
-          <t>starray</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H717" s="11" t="inlineStr">
@@ -31530,7 +31520,7 @@
       </c>
       <c r="G718" s="10" t="inlineStr">
         <is>
-          <t>starrezki</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H718" s="11" t="inlineStr">
@@ -31572,7 +31562,7 @@
       </c>
       <c r="G719" s="10" t="inlineStr">
         <is>
-          <t>starsilvie</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H719" s="11" t="inlineStr">
@@ -31614,7 +31604,7 @@
       </c>
       <c r="G720" s="10" t="inlineStr">
         <is>
-          <t>starstella</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H720" s="11" t="inlineStr">
@@ -31656,7 +31646,7 @@
       </c>
       <c r="G721" s="10" t="inlineStr">
         <is>
-          <t>starsuharlim</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H721" s="11" t="inlineStr">
@@ -31698,7 +31688,7 @@
       </c>
       <c r="G722" s="10" t="inlineStr">
         <is>
-          <t>starsylvia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H722" s="11" t="inlineStr">
@@ -31740,7 +31730,7 @@
       </c>
       <c r="G723" s="10" t="inlineStr">
         <is>
-          <t>startania</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H723" s="11" t="inlineStr">
@@ -31778,7 +31768,7 @@
       </c>
       <c r="G724" s="10" t="inlineStr">
         <is>
-          <t>starviktor</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H724" s="11" t="inlineStr">
@@ -31820,7 +31810,7 @@
       </c>
       <c r="G725" s="10" t="inlineStr">
         <is>
-          <t>starwiny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H725" s="11" t="inlineStr">
@@ -31862,7 +31852,7 @@
       </c>
       <c r="G726" s="10" t="inlineStr">
         <is>
-          <t>staryonathan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H726" s="11" t="inlineStr">
@@ -31904,7 +31894,7 @@
       </c>
       <c r="G727" s="10" t="inlineStr">
         <is>
-          <t>starfaedian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H727" s="11" t="inlineStr">
@@ -31946,7 +31936,7 @@
       </c>
       <c r="G728" s="10" t="inlineStr">
         <is>
-          <t>starfelicia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H728" s="11" t="inlineStr">
@@ -31984,7 +31974,7 @@
       </c>
       <c r="G729" s="10" t="inlineStr">
         <is>
-          <t>sunlau</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H729" s="11" t="inlineStr">
@@ -32026,7 +32016,7 @@
       </c>
       <c r="G730" s="10" t="inlineStr">
         <is>
-          <t>supremeangeline</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H730" s="11" t="inlineStr">
@@ -32068,7 +32058,7 @@
       </c>
       <c r="G731" s="10" t="inlineStr">
         <is>
-          <t>supremediana</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H731" s="11" t="inlineStr">
@@ -32110,7 +32100,7 @@
       </c>
       <c r="G732" s="10" t="inlineStr">
         <is>
-          <t>supremeeric</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H732" s="11" t="inlineStr">
@@ -32152,7 +32142,7 @@
       </c>
       <c r="G733" s="10" t="inlineStr">
         <is>
-          <t>supremeeuodia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H733" s="11" t="inlineStr">
@@ -32194,7 +32184,7 @@
       </c>
       <c r="G734" s="10" t="inlineStr">
         <is>
-          <t>supremefebriyandika</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H734" s="11" t="inlineStr">
@@ -32236,7 +32226,7 @@
       </c>
       <c r="G735" s="10" t="inlineStr">
         <is>
-          <t>supremefelix</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H735" s="11" t="inlineStr">
@@ -32278,7 +32268,7 @@
       </c>
       <c r="G736" s="10" t="inlineStr">
         <is>
-          <t>supremefiona</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H736" s="11" t="inlineStr">
@@ -32320,7 +32310,7 @@
       </c>
       <c r="G737" s="10" t="inlineStr">
         <is>
-          <t>supremegendro</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H737" s="11" t="inlineStr">
@@ -32362,7 +32352,7 @@
       </c>
       <c r="G738" s="10" t="inlineStr">
         <is>
-          <t>supremegrace</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H738" s="11" t="inlineStr">
@@ -32404,7 +32394,7 @@
       </c>
       <c r="G739" s="10" t="inlineStr">
         <is>
-          <t>supremejefferson</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H739" s="11" t="inlineStr">
@@ -32446,7 +32436,7 @@
       </c>
       <c r="G740" s="10" t="inlineStr">
         <is>
-          <t>supremekong</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H740" s="11" t="inlineStr">
@@ -32488,7 +32478,7 @@
       </c>
       <c r="G741" s="10" t="inlineStr">
         <is>
-          <t>supremerifki</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H741" s="11" t="inlineStr">
@@ -32530,7 +32520,7 @@
       </c>
       <c r="G742" s="10" t="inlineStr">
         <is>
-          <t>supremesofia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H742" s="11" t="inlineStr">
@@ -32572,7 +32562,7 @@
       </c>
       <c r="G743" s="10" t="inlineStr">
         <is>
-          <t>supremetriden</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H743" s="11" t="inlineStr">
@@ -32614,7 +32604,7 @@
       </c>
       <c r="G744" s="10" t="inlineStr">
         <is>
-          <t>synergyabyan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H744" s="11" t="inlineStr">
@@ -32656,7 +32646,7 @@
       </c>
       <c r="G745" s="10" t="inlineStr">
         <is>
-          <t>synergyagus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H745" s="11" t="inlineStr">
@@ -32698,7 +32688,7 @@
       </c>
       <c r="G746" s="10" t="inlineStr">
         <is>
-          <t>synergyahada</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H746" s="11" t="inlineStr">
@@ -32740,7 +32730,7 @@
       </c>
       <c r="G747" s="10" t="inlineStr">
         <is>
-          <t>synergyalvin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H747" s="11" t="inlineStr">
@@ -32782,7 +32772,7 @@
       </c>
       <c r="G748" s="10" t="inlineStr">
         <is>
-          <t>synergybrigitta</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H748" s="11" t="inlineStr">
@@ -32824,7 +32814,7 @@
       </c>
       <c r="G749" s="10" t="inlineStr">
         <is>
-          <t>synergydani</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H749" s="11" t="inlineStr">
@@ -32866,7 +32856,7 @@
       </c>
       <c r="G750" s="10" t="inlineStr">
         <is>
-          <t>synergyfreddy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H750" s="11" t="inlineStr">
@@ -32908,7 +32898,7 @@
       </c>
       <c r="G751" s="10" t="inlineStr">
         <is>
-          <t>synergyjessyca</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H751" s="11" t="inlineStr">
@@ -32950,7 +32940,7 @@
       </c>
       <c r="G752" s="10" t="inlineStr">
         <is>
-          <t>synergyjoshua</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H752" s="11" t="inlineStr">
@@ -32992,7 +32982,7 @@
       </c>
       <c r="G753" s="10" t="inlineStr">
         <is>
-          <t>synergyleonid</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H753" s="11" t="inlineStr">
@@ -33034,7 +33024,7 @@
       </c>
       <c r="G754" s="10" t="inlineStr">
         <is>
-          <t>synergyolpie</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H754" s="11" t="inlineStr">
@@ -33076,7 +33066,7 @@
       </c>
       <c r="G755" s="10" t="inlineStr">
         <is>
-          <t>synergyrizki</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H755" s="11" t="inlineStr">
@@ -33118,7 +33108,7 @@
       </c>
       <c r="G756" s="10" t="inlineStr">
         <is>
-          <t>synergyeric</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H756" s="11" t="inlineStr">
@@ -33156,7 +33146,7 @@
       </c>
       <c r="G757" s="10" t="inlineStr">
         <is>
-          <t>szlongtouhongliang</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H757" s="11" t="inlineStr">
@@ -33198,7 +33188,7 @@
       </c>
       <c r="G758" s="10" t="inlineStr">
         <is>
-          <t>taipeichang-ancaleb</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H758" s="11" t="inlineStr">
@@ -33240,7 +33230,7 @@
       </c>
       <c r="G759" s="10" t="inlineStr">
         <is>
-          <t>taiwanhuaoneni</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H759" s="11" t="inlineStr">
@@ -33282,7 +33272,7 @@
       </c>
       <c r="G760" s="10" t="inlineStr">
         <is>
-          <t>tenacityandre</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H760" s="11" t="inlineStr">
@@ -33324,7 +33314,7 @@
       </c>
       <c r="G761" s="10" t="inlineStr">
         <is>
-          <t>tenacityarianta</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H761" s="11" t="inlineStr">
@@ -33366,7 +33356,7 @@
       </c>
       <c r="G762" s="10" t="inlineStr">
         <is>
-          <t>tenacitydaniel</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H762" s="11" t="inlineStr">
@@ -33408,7 +33398,7 @@
       </c>
       <c r="G763" s="10" t="inlineStr">
         <is>
-          <t>tenacityferry</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H763" s="11" t="inlineStr">
@@ -33450,7 +33440,7 @@
       </c>
       <c r="G764" s="10" t="inlineStr">
         <is>
-          <t>tenacitygunalan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H764" s="11" t="inlineStr">
@@ -33492,7 +33482,7 @@
       </c>
       <c r="G765" s="10" t="inlineStr">
         <is>
-          <t>tenacityhasnil</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H765" s="11" t="inlineStr">
@@ -33534,7 +33524,7 @@
       </c>
       <c r="G766" s="10" t="inlineStr">
         <is>
-          <t>tenacityhuey</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H766" s="11" t="inlineStr">
@@ -33576,7 +33566,7 @@
       </c>
       <c r="G767" s="10" t="inlineStr">
         <is>
-          <t>tenacityjohana</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H767" s="11" t="inlineStr">
@@ -33618,7 +33608,7 @@
       </c>
       <c r="G768" s="10" t="inlineStr">
         <is>
-          <t>tenacitykhoerul</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H768" s="11" t="inlineStr">
@@ -33660,7 +33650,7 @@
       </c>
       <c r="G769" s="10" t="inlineStr">
         <is>
-          <t>tenacitymarianne</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H769" s="11" t="inlineStr">
@@ -33702,7 +33692,7 @@
       </c>
       <c r="G770" s="10" t="inlineStr">
         <is>
-          <t>tenacitymerita</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H770" s="11" t="inlineStr">
@@ -33744,7 +33734,7 @@
       </c>
       <c r="G771" s="10" t="inlineStr">
         <is>
-          <t>tenacitypaulus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H771" s="11" t="inlineStr">
@@ -33786,7 +33776,7 @@
       </c>
       <c r="G772" s="10" t="inlineStr">
         <is>
-          <t>tenacityrahmat</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H772" s="11" t="inlineStr">
@@ -33828,7 +33818,7 @@
       </c>
       <c r="G773" s="10" t="inlineStr">
         <is>
-          <t>tenacitysteven</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H773" s="11" t="inlineStr">
@@ -33870,7 +33860,7 @@
       </c>
       <c r="G774" s="10" t="inlineStr">
         <is>
-          <t>tenacitytjhin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H774" s="11" t="inlineStr">
@@ -33912,7 +33902,7 @@
       </c>
       <c r="G775" s="10" t="inlineStr">
         <is>
-          <t>tenacitydr</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H775" s="11" t="inlineStr">
@@ -33954,7 +33944,7 @@
       </c>
       <c r="G776" s="10" t="inlineStr">
         <is>
-          <t>tenacityfadhlan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H776" s="11" t="inlineStr">
@@ -33996,7 +33986,7 @@
       </c>
       <c r="G777" s="10" t="inlineStr">
         <is>
-          <t>tenacityyohanes</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H777" s="11" t="inlineStr">
@@ -34038,7 +34028,7 @@
       </c>
       <c r="G778" s="10" t="inlineStr">
         <is>
-          <t>titanscaroline</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H778" s="11" t="inlineStr">
@@ -34076,7 +34066,7 @@
       </c>
       <c r="G779" s="10" t="inlineStr">
         <is>
-          <t>titanselisabeth</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H779" s="11" t="inlineStr">
@@ -34118,7 +34108,7 @@
       </c>
       <c r="G780" s="10" t="inlineStr">
         <is>
-          <t>titansfrancis</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H780" s="11" t="inlineStr">
@@ -34160,7 +34150,7 @@
       </c>
       <c r="G781" s="10" t="inlineStr">
         <is>
-          <t>titanshandi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H781" s="11" t="inlineStr">
@@ -34202,7 +34192,7 @@
       </c>
       <c r="G782" s="10" t="inlineStr">
         <is>
-          <t>titansmaria</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H782" s="11" t="inlineStr">
@@ -34244,7 +34234,7 @@
       </c>
       <c r="G783" s="10" t="inlineStr">
         <is>
-          <t>titansmarselinus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H783" s="11" t="inlineStr">
@@ -34286,7 +34276,7 @@
       </c>
       <c r="G784" s="10" t="inlineStr">
         <is>
-          <t>titansnelson</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H784" s="11" t="inlineStr">
@@ -34328,7 +34318,7 @@
       </c>
       <c r="G785" s="10" t="inlineStr">
         <is>
-          <t>titansricco</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H785" s="11" t="inlineStr">
@@ -34370,7 +34360,7 @@
       </c>
       <c r="G786" s="10" t="inlineStr">
         <is>
-          <t>titansrichard</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H786" s="11" t="inlineStr">
@@ -34412,7 +34402,7 @@
       </c>
       <c r="G787" s="10" t="inlineStr">
         <is>
-          <t>titansroby</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H787" s="11" t="inlineStr">
@@ -34454,7 +34444,7 @@
       </c>
       <c r="G788" s="10" t="inlineStr">
         <is>
-          <t>titansruvy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H788" s="11" t="inlineStr">
@@ -34492,7 +34482,7 @@
       </c>
       <c r="G789" s="10" t="inlineStr">
         <is>
-          <t>treasurexwong</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H789" s="11" t="inlineStr">
@@ -34534,7 +34524,7 @@
       </c>
       <c r="G790" s="10" t="inlineStr">
         <is>
-          <t>unityanindya</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H790" s="11" t="inlineStr">
@@ -34576,7 +34566,7 @@
       </c>
       <c r="G791" s="10" t="inlineStr">
         <is>
-          <t>unitycelvin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H791" s="11" t="inlineStr">
@@ -34618,7 +34608,7 @@
       </c>
       <c r="G792" s="10" t="inlineStr">
         <is>
-          <t>unitychandra</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H792" s="11" t="inlineStr">
@@ -34660,7 +34650,7 @@
       </c>
       <c r="G793" s="10" t="inlineStr">
         <is>
-          <t>unitydestika</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H793" s="11" t="inlineStr">
@@ -34702,7 +34692,7 @@
       </c>
       <c r="G794" s="10" t="inlineStr">
         <is>
-          <t>unitydewi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H794" s="11" t="inlineStr">
@@ -34744,7 +34734,7 @@
       </c>
       <c r="G795" s="10" t="inlineStr">
         <is>
-          <t>unitydina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H795" s="11" t="inlineStr">
@@ -34786,7 +34776,7 @@
       </c>
       <c r="G796" s="10" t="inlineStr">
         <is>
-          <t>unityelisabeth</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H796" s="11" t="inlineStr">
@@ -34828,7 +34818,7 @@
       </c>
       <c r="G797" s="10" t="inlineStr">
         <is>
-          <t>unityjason</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H797" s="11" t="inlineStr">
@@ -34870,7 +34860,7 @@
       </c>
       <c r="G798" s="10" t="inlineStr">
         <is>
-          <t>unityjustikarini</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H798" s="11" t="inlineStr">
@@ -34908,7 +34898,7 @@
       </c>
       <c r="G799" s="10" t="inlineStr">
         <is>
-          <t>unitylayaliya</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H799" s="11" t="inlineStr">
@@ -34950,7 +34940,7 @@
       </c>
       <c r="G800" s="10" t="inlineStr">
         <is>
-          <t>unitymario</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H800" s="11" t="inlineStr">
@@ -34992,7 +34982,7 @@
       </c>
       <c r="G801" s="10" t="inlineStr">
         <is>
-          <t>unitymartha</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H801" s="11" t="inlineStr">
@@ -35034,7 +35024,7 @@
       </c>
       <c r="G802" s="10" t="inlineStr">
         <is>
-          <t>unitymeilianti</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H802" s="11" t="inlineStr">
@@ -35076,7 +35066,7 @@
       </c>
       <c r="G803" s="10" t="inlineStr">
         <is>
-          <t>unitymeriyanti</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H803" s="11" t="inlineStr">
@@ -35118,7 +35108,7 @@
       </c>
       <c r="G804" s="10" t="inlineStr">
         <is>
-          <t>unitypriscillia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H804" s="11" t="inlineStr">
@@ -35160,7 +35150,7 @@
       </c>
       <c r="G805" s="10" t="inlineStr">
         <is>
-          <t>unityraden</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H805" s="11" t="inlineStr">
@@ -35198,7 +35188,7 @@
       </c>
       <c r="G806" s="10" t="inlineStr">
         <is>
-          <t>unitysean</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H806" s="11" t="inlineStr">
@@ -35240,7 +35230,7 @@
       </c>
       <c r="G807" s="10" t="inlineStr">
         <is>
-          <t>unitytomy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H807" s="11" t="inlineStr">
@@ -35278,7 +35268,7 @@
       </c>
       <c r="G808" s="10" t="inlineStr">
         <is>
-          <t>venturaahmad</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H808" s="11" t="inlineStr">
@@ -35316,7 +35306,7 @@
       </c>
       <c r="G809" s="10" t="inlineStr">
         <is>
-          <t>venturaboy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H809" s="11" t="inlineStr">
@@ -35354,7 +35344,7 @@
       </c>
       <c r="G810" s="10" t="inlineStr">
         <is>
-          <t>venturadiana</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H810" s="11" t="inlineStr">
@@ -35392,7 +35382,7 @@
       </c>
       <c r="G811" s="10" t="inlineStr">
         <is>
-          <t>venturadiky</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H811" s="11" t="inlineStr">
@@ -35430,7 +35420,7 @@
       </c>
       <c r="G812" s="10" t="inlineStr">
         <is>
-          <t>venturaeufrasia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H812" s="11" t="inlineStr">
@@ -35468,7 +35458,7 @@
       </c>
       <c r="G813" s="10" t="inlineStr">
         <is>
-          <t>venturafrengki</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H813" s="11" t="inlineStr">
@@ -35506,7 +35496,7 @@
       </c>
       <c r="G814" s="10" t="inlineStr">
         <is>
-          <t>venturahendro</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H814" s="11" t="inlineStr">
@@ -35544,7 +35534,7 @@
       </c>
       <c r="G815" s="10" t="inlineStr">
         <is>
-          <t>venturaiwan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H815" s="11" t="inlineStr">
@@ -35582,7 +35572,7 @@
       </c>
       <c r="G816" s="10" t="inlineStr">
         <is>
-          <t>venturaromadhon</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H816" s="11" t="inlineStr">
@@ -35620,7 +35610,7 @@
       </c>
       <c r="G817" s="10" t="inlineStr">
         <is>
-          <t>venturarubhen</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H817" s="11" t="inlineStr">
@@ -35658,7 +35648,7 @@
       </c>
       <c r="G818" s="10" t="inlineStr">
         <is>
-          <t>venturas.</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H818" s="11" t="inlineStr">
@@ -35696,7 +35686,7 @@
       </c>
       <c r="G819" s="10" t="inlineStr">
         <is>
-          <t>venturasony</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H819" s="11" t="inlineStr">
@@ -35734,7 +35724,7 @@
       </c>
       <c r="G820" s="10" t="inlineStr">
         <is>
-          <t>venturayuniar</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H820" s="11" t="inlineStr">
@@ -35772,7 +35762,7 @@
       </c>
       <c r="G821" s="10" t="inlineStr">
         <is>
-          <t>venturaadrian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H821" s="11" t="inlineStr">
@@ -35814,7 +35804,7 @@
       </c>
       <c r="G822" s="10" t="inlineStr">
         <is>
-          <t>victorymonika</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H822" s="11" t="inlineStr">
@@ -35856,7 +35846,7 @@
       </c>
       <c r="G823" s="10" t="inlineStr">
         <is>
-          <t>visionamanda</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H823" s="11" t="inlineStr">
@@ -35894,7 +35884,7 @@
       </c>
       <c r="G824" s="10" t="inlineStr">
         <is>
-          <t>visionaryanti</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H824" s="11" t="inlineStr">
@@ -35936,7 +35926,7 @@
       </c>
       <c r="G825" s="10" t="inlineStr">
         <is>
-          <t>visiondeasy</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H825" s="11" t="inlineStr">
@@ -35978,7 +35968,7 @@
       </c>
       <c r="G826" s="10" t="inlineStr">
         <is>
-          <t>visiondesilia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H826" s="11" t="inlineStr">
@@ -36020,7 +36010,7 @@
       </c>
       <c r="G827" s="10" t="inlineStr">
         <is>
-          <t>visiondewina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H827" s="11" t="inlineStr">
@@ -36062,7 +36052,7 @@
       </c>
       <c r="G828" s="10" t="inlineStr">
         <is>
-          <t>visionflavia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H828" s="11" t="inlineStr">
@@ -36104,7 +36094,7 @@
       </c>
       <c r="G829" s="10" t="inlineStr">
         <is>
-          <t>visionhendra</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H829" s="11" t="inlineStr">
@@ -36146,7 +36136,7 @@
       </c>
       <c r="G830" s="10" t="inlineStr">
         <is>
-          <t>visionhery</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H830" s="11" t="inlineStr">
@@ -36188,7 +36178,7 @@
       </c>
       <c r="G831" s="10" t="inlineStr">
         <is>
-          <t>visionkevin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H831" s="11" t="inlineStr">
@@ -36226,7 +36216,7 @@
       </c>
       <c r="G832" s="10" t="inlineStr">
         <is>
-          <t>visionkin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H832" s="11" t="inlineStr">
@@ -36268,7 +36258,7 @@
       </c>
       <c r="G833" s="10" t="inlineStr">
         <is>
-          <t>visionlouis</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H833" s="11" t="inlineStr">
@@ -36310,7 +36300,7 @@
       </c>
       <c r="G834" s="10" t="inlineStr">
         <is>
-          <t>visionmartin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H834" s="11" t="inlineStr">
@@ -36352,7 +36342,7 @@
       </c>
       <c r="G835" s="10" t="inlineStr">
         <is>
-          <t>visionmelissa</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H835" s="11" t="inlineStr">
@@ -36394,7 +36384,7 @@
       </c>
       <c r="G836" s="10" t="inlineStr">
         <is>
-          <t>visionphilip</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H836" s="11" t="inlineStr">
@@ -36436,7 +36426,7 @@
       </c>
       <c r="G837" s="10" t="inlineStr">
         <is>
-          <t>visionping</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H837" s="11" t="inlineStr">
@@ -36474,7 +36464,7 @@
       </c>
       <c r="G838" s="10" t="inlineStr">
         <is>
-          <t>visionratna</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H838" s="11" t="inlineStr">
@@ -36516,7 +36506,7 @@
       </c>
       <c r="G839" s="10" t="inlineStr">
         <is>
-          <t>visionrobin</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H839" s="11" t="inlineStr">
@@ -36554,7 +36544,7 @@
       </c>
       <c r="G840" s="10" t="inlineStr">
         <is>
-          <t>visionshirley</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H840" s="11" t="inlineStr">
@@ -36596,7 +36586,7 @@
       </c>
       <c r="G841" s="10" t="inlineStr">
         <is>
-          <t>visionsofian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H841" s="11" t="inlineStr">
@@ -36638,7 +36628,7 @@
       </c>
       <c r="G842" s="10" t="inlineStr">
         <is>
-          <t>visionstephan</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H842" s="11" t="inlineStr">
@@ -36680,7 +36670,7 @@
       </c>
       <c r="G843" s="10" t="inlineStr">
         <is>
-          <t>visionstewart</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H843" s="11" t="inlineStr">
@@ -36722,7 +36712,7 @@
       </c>
       <c r="G844" s="10" t="inlineStr">
         <is>
-          <t>visionwilliam</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H844" s="11" t="inlineStr">
@@ -36764,7 +36754,7 @@
       </c>
       <c r="G845" s="10" t="inlineStr">
         <is>
-          <t>visionwina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H845" s="11" t="inlineStr">
@@ -36806,7 +36796,7 @@
       </c>
       <c r="G846" s="10" t="inlineStr">
         <is>
-          <t>visionyeremia</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H846" s="11" t="inlineStr">
@@ -36848,7 +36838,7 @@
       </c>
       <c r="G847" s="10" t="inlineStr">
         <is>
-          <t>xsri</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H847" s="11" t="inlineStr">
@@ -36886,7 +36876,7 @@
       </c>
       <c r="G848" s="10" t="inlineStr">
         <is>
-          <t>adina</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H848" s="11" t="inlineStr">
@@ -36924,7 +36914,7 @@
       </c>
       <c r="G849" s="10" t="inlineStr">
         <is>
-          <t>aida</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H849" s="11" t="inlineStr">
@@ -36962,7 +36952,7 @@
       </c>
       <c r="G850" s="10" t="inlineStr">
         <is>
-          <t>audrey</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H850" s="11" t="inlineStr">
@@ -37000,7 +36990,7 @@
       </c>
       <c r="G851" s="10" t="inlineStr">
         <is>
-          <t>bingar</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H851" s="11" t="inlineStr">
@@ -37038,7 +37028,7 @@
       </c>
       <c r="G852" s="10" t="inlineStr">
         <is>
-          <t>dayang</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H852" s="11" t="inlineStr">
@@ -37076,7 +37066,7 @@
       </c>
       <c r="G853" s="10" t="inlineStr">
         <is>
-          <t>dewi</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H853" s="11" t="inlineStr">
@@ -37118,7 +37108,7 @@
       </c>
       <c r="G854" s="10" t="inlineStr">
         <is>
-          <t>eugene</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H854" s="11" t="inlineStr">
@@ -37156,7 +37146,7 @@
       </c>
       <c r="G855" s="10" t="inlineStr">
         <is>
-          <t>fadillah</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H855" s="11" t="inlineStr">
@@ -37194,7 +37184,7 @@
       </c>
       <c r="G856" s="10" t="inlineStr">
         <is>
-          <t>fenny</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H856" s="11" t="inlineStr">
@@ -37232,7 +37222,7 @@
       </c>
       <c r="G857" s="10" t="inlineStr">
         <is>
-          <t>hendry</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H857" s="11" t="inlineStr">
@@ -37270,7 +37260,7 @@
       </c>
       <c r="G858" s="10" t="inlineStr">
         <is>
-          <t>henri</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H858" s="11" t="inlineStr">
@@ -37308,7 +37298,7 @@
       </c>
       <c r="G859" s="10" t="inlineStr">
         <is>
-          <t>jovian</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H859" s="11" t="inlineStr">
@@ -37346,7 +37336,7 @@
       </c>
       <c r="G860" s="10" t="inlineStr">
         <is>
-          <t>ming</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H860" s="11" t="inlineStr">
@@ -37384,7 +37374,7 @@
       </c>
       <c r="G861" s="10" t="inlineStr">
         <is>
-          <t>meta</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H861" s="11" t="inlineStr">
@@ -37426,7 +37416,7 @@
       </c>
       <c r="G862" s="10" t="inlineStr">
         <is>
-          <t>muhammad</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H862" s="11" t="inlineStr">
@@ -37464,7 +37454,7 @@
       </c>
       <c r="G863" s="10" t="inlineStr">
         <is>
-          <t>robby</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H863" s="11" t="inlineStr">
@@ -37502,7 +37492,7 @@
       </c>
       <c r="G864" s="10" t="inlineStr">
         <is>
-          <t>stefanus</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H864" s="11" t="inlineStr">
@@ -37540,7 +37530,7 @@
       </c>
       <c r="G865" s="10" t="inlineStr">
         <is>
-          <t>stephen</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H865" s="11" t="inlineStr">
@@ -37578,7 +37568,7 @@
       </c>
       <c r="G866" s="10" t="inlineStr">
         <is>
-          <t>tiansong</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H866" s="11" t="inlineStr">
@@ -37616,7 +37606,7 @@
       </c>
       <c r="G867" s="10" t="inlineStr">
         <is>
-          <t>vera</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H867" s="11" t="inlineStr">
@@ -37654,7 +37644,7 @@
       </c>
       <c r="G868" s="10" t="inlineStr">
         <is>
-          <t>yola</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H868" s="11" t="inlineStr">
@@ -37692,7 +37682,7 @@
       </c>
       <c r="G869" s="10" t="inlineStr">
         <is>
-          <t>yosua</t>
+          <t>natcon2026</t>
         </is>
       </c>
       <c r="H869" s="11" t="inlineStr">
